--- a/data/sampled_200.xlsx
+++ b/data/sampled_200.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I201"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,7 +367,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Combined_Text</t>
+          <t>Bewertungstext</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -391,11 +391,6 @@
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Score</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Constructivity</t>
         </is>
@@ -404,361 +399,345 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rev-12f898c1-d4eb-4af2-8d8e-85b72b287789</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>4</v>
+          <t>rev-a9adb396-07f0-4243-a1b1-73c4ca484bc5</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Titel: Top, Text: Top</t>
+          <t>Sehr lecker wie selbst gekocht nicht viel Müll</t>
         </is>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rev-78825847-23f8-4ce8-93fa-5a00876f2e53</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>3</v>
+          <t>rev-88f963af-59cb-432b-be12-4d5a617718e8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung, Text: Schnelle Lieferung</t>
+          <t>Ein echter Alltagsproblemlöser für Singles... reichhaltige Auswahl an leckeren Mahlzeiten, die frisch gekocht und schockgefrostet nach Hause kommen! Spart mir jede Menge Zeit und Nerven.</t>
         </is>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1.25</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rev-a879d777-2f0e-4c2f-b94a-e9c034b7448f</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>1</v>
+          <t>rev-04ea56f0-3d2c-45c9-8aed-4f7fbc2b7686</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Titel: Liefertermin 27.3.25 wurde nicht…, Text: Liefertermin 27.3.25 wurde nicht eingehalten...18:45 Uhr noch keine e Lieferung da ....nicht gut!!!!!</t>
+          <t>Der Kundenservice ist freundlich und ergebnisorientiert.</t>
         </is>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>3.75</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rev-ad5e7de3-90f0-48a9-bddd-303952f31f0b</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>5</v>
+          <t>rev-c3cd0425-3eff-46a9-9393-6ae476e26969</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Essen schmeckt sehr gut, Text: Essen schmeckt sehr gut, kann ich nur empfehlen._x000D__x000D_
-</t>
+          <t>Wir sind ganz begeistert.  Das Essen schmeckt super und die Portionen sind wirklich ausreichend groß</t>
         </is>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rev-cdd080f9-e08e-400e-a74c-ae61e8666d04</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>5</v>
+          <t>rev-25e605c6-9e4f-4ccb-ab8b-10e80e42085f</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Titel: Sehr gute Vetarbeitung...schmeckt sehr…, Text: Sehr gute Vetarbeitung...schmeckt sehr gut</t>
+          <t>Das Essen war zwei Tage später bei mir. Es ist sehr schmackhaft. Bin mit der Firma sehr zufrieden.</t>
         </is>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>1.25</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rev-1d343fa3-7c9d-4ef8-b223-2973150fe89f</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>5</v>
+          <t>rev-d324c4e4-9ab3-dcfe-a877-312d0bd6ac25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Titel: Sehr lecker ., Text: Sehr lecker .. und das es nicht in Aluschslen verpackt ist .</t>
+          <t>Sehr gutes Essen. Schnelle Lieferung. Alles TOP....</t>
         </is>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>2.5</v>
-      </c>
-      <c r="I7">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rev-bbc73f18-4858-7ea6-f71e-70ae9f090916</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>5</v>
+          <t>rev-79e075a7-dd39-4946-8158-0dd3a01c1065</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Titel: Immer schnelle Lieferung sehr zuverlässig gute Qualität, Text: Immer schnelle Lieferung sehr zuverlässig gute Qualität</t>
+          <t>Da ich abends keine Lust mehr habe zu kochen, sind die angebotenen Menüs perfekt für mich. Bisher war auch kein Gericht dabei, was mir gar nicht schmeckte. Verpackung ist nachhaltig. Ich werde garantiert öfter bestellen.</t>
         </is>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>1.25</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rev-0f256c42-58d0-402c-b7f3-8dd32dfa12b1</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>5</v>
+          <t>rev-d001980b-9777-4387-aac5-3b545a2e88a4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Das Essen ist absolut topp., Text: Das Essen ist absolut topp._x000D__x000D_
-Geschmacklich und was auch die Portionsgröße angeht_x000D__x000D_
-Verpackung, Versand, Aufbau Homepage auch sehr gut._x000D__x000D_
-Mir fällt absolut kein einziger negativer Punkt ein._x000D__x000D_
-Na ja,  einer fällt mir doch ein._x000D__x000D_
-Damals für mich als neuer Besteller bei Hofmanns war es etwas irritierend_x000D__x000D_
-das auf der Packung andere Zubereitungszeiten/Temperaturen stehen wie Online. Und um die Verwirrung komplett zu machen, ist bei einer Bestellung noch ein Beipackblatt beigefügt mit Zubereitungstemperatur und Zeit._x000D__x000D_
-</t>
+          <t>Zunotgeht das Essen _x000D_
+ Lieferung ,Verpackung sehr gut</t>
         </is>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>8.75</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rev-3294c420-1ec3-4dcc-ab20-8942f1bddeb1</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>4</v>
+          <t>rev-32e94aa8-2725-47de-998d-3199c5fd5c83</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Titel: Leider waren 2 Essen an der Seite offen., Text: Leider waren 2 Essen an der Seite offen.</t>
+          <t>Super</t>
         </is>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>5</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rev-c888983e-c8cc-473b-a91b-26938347c2f3</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>1</v>
+          <t>rev-bfbe028f-bc61-4c12-92b7-8cfb3261abe9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Titel: Fehlerhafte Lieferung, Text: Fehlerhafte Lieferung _x000D__x000D_
-Keine Rückmeldung nach Reklamation per Email</t>
+          <t>Sehr leckeres Essen. Die Auswahl an Gerichten ist sehr groß und alles schmeckt fantastisch. Zudem wird alles super schnell geliefert und ist sicher und gut gekühlt verpackt.</t>
         </is>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>3.75</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rev-6c77c424-8eeb-448c-b8f4-bd7ad4693640</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>5</v>
+          <t>rev-d9d18f3a-5146-454c-9d29-0d41f64a7e6e</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Titel: Das Essen schmeckt gut hat ein schönes…, Text: Das Essen schmeckt gut hat ein schönes Aroma.</t>
+          <t>Es schmeckt immer sehr gut. Es könnte auch mal Ente oder Gans geben</t>
         </is>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -767,265 +746,261 @@
         <v>1</v>
       </c>
       <c r="H12">
-        <v>1.25</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rev-c4c1f94a-44be-4673-b659-3d0a2ba2493e</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>5</v>
+          <t>rev-99d45ec7-c7ea-4508-bacc-df2723b1e0cb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Titel: Top Service, Text: Sehr gut und sicher verpackt. Habe bisher 2 Gerichte probiert und bin sehr zufrieden.. Werde sicherlich noch das ein oder andere bestellen.</t>
+          <t>Sehr umweltfreundliche Verpackung. Sehr schnelle Lieferung. Ich vermisse in ihrem sehr reichhaltigen Angebot jedoch Desserts, Kuchen, Eis.</t>
         </is>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>2.5</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rev-2e30f824-c03e-459b-b41f-bc9b0d8526f1</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>5</v>
+          <t>rev-b91d5906-8191-41cb-884f-0e4268e8485d</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Titel: Schmackhaft, Text: Schmackhaft</t>
+          <t>Sehr gute Auswahl an leckeren Mahlzeiten.</t>
         </is>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rev-f086552c-fa5b-46c5-b309-ddd58b6fb087</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>5</v>
+          <t>rev-2e4653cf-bd1e-46cf-bcc0-4287699f26c0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Titel: Bin ganz begeistert, Text: Bin ganz begeistert, das Essen schmeckt sehr gut.</t>
+          <t>Gute Qualität zu fairen Preisen.</t>
         </is>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>2.5</v>
-      </c>
-      <c r="I15">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rev-710e1965-e4e2-43fb-8f56-b78e5b853653</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>5</v>
+          <t>rev-6725556b-c941-4e06-9a2b-0f6f04df58ec</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Titel: Gute Verpackung und schnelle Lieferung, Text: Gute Verpackung und schnelle Lieferung, Kühlung super👍👍</t>
+          <t>perfekt wie immer, besten Dank!</t>
         </is>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>3.75</v>
-      </c>
-      <c r="I16">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rev-a9fe0061-42d9-45da-8d78-e7bead48e1ca</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>5</v>
+          <t>rev-28206cf8-905c-4502-999e-323c01a8d55b</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Titel: Schnelle und gute Anlieferung, Text: Schnelle und gute Anlieferung, gute Qualität der Produkte, Preis-Leistungsverhältnis okay._x000D__x000D_
-Wenn ich mir Ihre Bilder mit den Angeboten anschaue, würde mir bereits dort_x000D__x000D_
-der Hinweis gefallen, ob Heißluftofen oder Mikrowelle geeignet bzw. nicht geeignet. Würde mir als alleinlebender Witwer die Bestellung deutlich erleichtern!</t>
+          <t>Internet Werbung abschalten._x000D_
+Mir vergeht der Appetit.</t>
         </is>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>8.75</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rev-4c4e0373-57e2-4615-8924-e1b0d5202cc3</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>5</v>
+          <t>rev-fa184d7f-2803-40ef-92e2-7a37e92737df</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Titel: Toll wie immer, Text: Toll wie immer, sehr lecker. Einwandfreie Verpackung.</t>
+          <t>Im Großen und Ganzen gut. Die Lieferung war verzögert um einen Tag. Ist etwas problematisch, weil man den ganzen Tag zuhause sein muss, um die Ware gleich nach Lieferung in den Tiefkühlschrank geben muss. Das erste Essen heute war geschmacklich gut und ausreichend. Bin gespannt auf die nächsten Essen.</t>
         </is>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="H18">
-        <v>3.75</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rev-28a07241-e0cf-48a2-ac39-90c2747d5c4e</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>2</v>
+          <t>rev-0abf3d42-6f9d-4e56-ac66-8a0d45eb5185</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: ware kommt nicht ......, Text: ware kommt nicht ......_x000D__x000D_
-</t>
+          <t>Schnelle Lieferung. Leckeres Essen</t>
         </is>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>2.5</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rev-bb974138-a401-408b-a649-7fa4a8e33fc8</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>5</v>
+          <t>rev-f21f7039-9b91-4751-92fc-59e96d335926</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Titel: Superschnelle Lieferung, Text: Superschnelle Lieferung</t>
+          <t>Schnelle und gute Lieferung. _x000D_
+Das Essen schmeckt sehr gut !_x000D_
+_x000D_
+Was ich gut finden würde:_x000D_
+Die einzelnen Portionen könnten etwas größer sein . _x000D_
+_x000D_
+Ansonsten bin ich sehr zufrieden!</t>
         </is>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1034,394 +1009,380 @@
         <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rev-5042b6d2-0b2b-4cf1-9159-2b7810b0ad6c</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>5</v>
+          <t>rev-e877eddf-c3ed-4fb5-982c-361cd821a7d2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Titel: gute Bearbeitung, Text: gute Bearbeitung, Schnelle Lieferung</t>
+          <t>Pünktliche Lieferung, gute Ware.</t>
         </is>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>1.25</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rev-47e4e537-bebe-4f7d-b0fa-e7df31f4be35</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>4</v>
+          <t>rev-b082e5f1-fa77-c5ce-83d0-60266acc136e</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Verpackung schnelle Lieferung Qualität…, Text: Verpackung schnelle Lieferung Qualität der Ware_x000D__x000D_
-</t>
+          <t>Super leckeres Essen, sind rundum zufrieden.</t>
         </is>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>1.25</v>
-      </c>
-      <c r="I22">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rev-4567adb5-5e5b-401a-a0c4-ee0b6613e873</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>5</v>
+          <t>rev-bfafa733-323d-4720-af1e-c21dc23eefa8</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Titel: Geschmacklich sehr gut, Text: Geschmacklich sehr gut, Service  und Lieferzeiten sehr gut.</t>
+          <t>Vorneweg.. das Essen selbst ist wirklich gut bis sehr gut. Aber leider haben sehr viele Behälter Beschädigungen gehabt oder waren z.B. "falschherum"  verpackt (dass die Öffnungslaschen die bei Zubereitung schon geöffnet werden müssen für die Beilagen .. auf der falschen Seite waren). Und man hat eine im Hausmüll nicht zu bewältigende Menge Abfall durch die Packungen bzw. das Dämmaterial der Kisten. D.h. leider man braucht auch wieder Hilfe alles auf den Wertstoffhof zu bringen.</t>
         </is>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>1.25</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rev-a3ef7c15-e077-4609-b26c-eb495c30d7e0</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>5</v>
+          <t>rev-d26bab9f-0e0b-4d6c-b587-de8986faab85</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Titel: Leckeres Essen ohne Arbeit, Text: Leckeres Essen ohne Arbeit. Vielseitig und gesund, wir werden wieder bestellen.</t>
+          <t>Schnelle Lieferung, gut verpackt.</t>
         </is>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>2.5</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rev-85e8ed03-ad16-4741-a0a5-d53a69274ec9</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>5</v>
+          <t>rev-f2722556-dcdc-4c77-a4e1-db310f42a6cc</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Titel: Super verpackt und kam sehr gut…, Text: Super verpackt und kam sehr gut tiefgefroren bei mir an</t>
+          <t>Die Versandverpackung ist leider sehr schlecht. Das Isolationsmaterial ist Restmüll und "Verstopft" damit meine Mülltonne. Die Papierschalen Platzen regelmäßig während des Transportes auf und damit sind dann die Gerichte auch nicht mehr verzehrbar. Außerdem Öffnen sich die Pappschalen während der Zubereitung im Ofen. Dadurch trocknet oder verbrennt das Essen. Das ist sehr schade da das Essen an sich und auch die Kundenbetreuung sehr gut ist.</t>
         </is>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25">
         <v>2</v>
       </c>
       <c r="H25">
-        <v>2.5</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rev-af2c6b7d-8080-4273-88b1-1ed5f4b5fcfe</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>5</v>
+          <t>rev-f0c0f191-0321-4725-ae9c-9b8675e241db</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Titel: Wir haben auch einen anderen Anbieter…, Text: Wir haben auch einen anderen Anbieter gehabt, den wir aber nach drei Testessen wieder abgesagt haben. Der war keine Konkurrenz für Hoffmanns leckeres Essen. Auch Preis-/Leistungsverhältnis stimmen. Sehr zu empfehlen!_x000D__x000D_
-Eine Anregung: Wenn es möglich ist, die Behälter für die Portionen ein wenig kleiner gestalten, diese passen dann besser in die Heißluftfritteuse bzw in die Mikrowelle.</t>
+          <t>Schnelle Lieferung, sehr gute Verpackung</t>
         </is>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>7.5</v>
-      </c>
-      <c r="I26">
         <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>rev-bdeb5cb4-7340-404b-ae7d-b57f309dce0e</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>5</v>
+          <t>rev-ffe262d7-c5b0-4f0d-9a6b-7dc29d7b0bd7</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Titel: Geschmacklich top!, Text: Das was wir bisher probiert haben schmeckte klasse!</t>
+          <t>Gutes Essen, schnelle zuverlässige Lieferung und ein hervorragender Kundenservice runden den Eindruck an. Nur zu empfehlen.</t>
         </is>
       </c>
       <c r="D27">
         <v>2</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>2.5</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rev-cc7c7e08-6dac-48c4-ac23-360579e1d911</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>5</v>
+          <t>rev-7ee6161f-7dd7-4831-aec8-361c4d35a041</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Titel: Die Lieferung hat super geklagt, Text: Die Lieferung hat super geklagt. Habe leider noch keines der Menüs probiert.</t>
+          <t>Schmeckt gut. Preis/Leistung gut.</t>
         </is>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>rev-8167384c-b9e4-4022-95fe-adf900c0c6b9</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>5</v>
+          <t>rev-c4afe729-6c84-4f0b-811e-38a8ca3ccda6</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Titel: Bin sehr zufrieden., Text: Bin sehr zufrieden.</t>
+          <t>Die  Zustellung  lief  wie immer reibungslos und  die  Gerichte schmecken wirklich sehr gut.</t>
         </is>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>rev-5d7b2213-88e1-4776-bf5f-a4321af998ab</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>5</v>
+          <t>rev-661b7e5d-147c-44a0-af48-1b2618119b62</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: So wünscht man sich den gesamten Ablauf…, Text: So wünscht man sich den gesamten Ablauf der Bestellung_x000D__x000D_
+          <t xml:space="preserve">Wie versprochen schnelle Lieferung und geschmacklich sehr sehr gut._x000D_
 </t>
         </is>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>rev-b6dfac08-cd06-45f6-a89b-a157412998c8</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>5</v>
+          <t>rev-058f0da7-3160-466e-b52b-ecf5c8ce0917</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Titel: Alles super geklappt, Text: Alles super geklappt, Vater schmeckt es. Schnelle Lieferung. Einfaches Aufwärmen im Backofen!</t>
+          <t>Kundenservice eine Rückmeldung innerhalb 24 Stunden,  bis jetzt sind die Gerichte sehr gut man merkt das auf Frische und Qualität geachtet wird. Die Portionen sind ausreichend,  und sehr gut gewürzt .Die Gerichte sind nicht scharf und was die Auswahl betrifft sind wir sehr zufrieden. Was wir an Hofmann auch sehr mögen ist das es viele verschiedene Gerichte gibt und nicht nur eine Richtung. Ich habe schon andere Firmen probiert aber am besten ist für uns Hofmann. Meine Mutter hat Gastritis und kann vieles nicht essen weil Sie es nicht verträgt und ich habe nicht die Zeit und die Möglichkeit zu kochen weil ich schließlich Arbeiten muss. Wir sind neu hier und bis jetzt 8 Gerichte probiert und es hat sich gelohnt meine Mutter kann es essen und es schmeckt ihr auch sehr gut 👍 und vorallem hat sie kein SodbrennenundMagenschmerzen beim essen der Gerichte. Und ich bin auch sehr zufrieden deswegen haben wir wieder bestellt. Kann die Gerichte eigentlich nur empfehlen daher für mich 5 Sterne 🌟 für Gerichte,  und den Kundenservice.</t>
         </is>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <v>2</v>
       </c>
       <c r="H31">
-        <v>3.75</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>rev-df094f12-c104-4036-be8c-845222a3ffb2</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>5</v>
+          <t>rev-e9435406-93e8-4b90-b71b-29e1ce6a70fc</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Titel: Bisher immer 😋, Text: Bisher immer 😋</t>
+          <t>also Geschmacklich sind fast alle Gerichte sehr lecker. Der Reis ist manchmal ein wenig mehlig, vielleicht wäre hier eine andere sorte angebracht. was ich nicht so toll finde, sind die konsistenz der kartoffeln</t>
         </is>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -1433,391 +1394,381 @@
         <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>rev-c54a2694-3c6c-4745-822c-e37b9e075471</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>5</v>
+          <t>rev-b9b63444-f4ca-4b78-875c-f860209a4dca</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung, Text: Schnelle Lieferung</t>
+          <t>Pünktlich, sehr gut 👍 verpackt, alles bestens immer wieder gerne.</t>
         </is>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>1.25</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>rev-2b52b49f-1d7b-451c-96ef-773fcb37a711</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>5</v>
+          <t>rev-c7301646-2f4e-2620-711c-bc42411be893</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Titel: Sehr gutes Essen und gefroren…, Text: Sehr gutes Essen und gefroren angekommen, obwohl es an den Tagen heiss war.</t>
+          <t>Alles bestens und sehr lecker.</t>
         </is>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>5</v>
-      </c>
-      <c r="I34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>rev-09171df9-a35c-4e31-8526-b5af5ec2c542</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>5</v>
+          <t>rev-cf8c2be9-a057-4b30-8297-356a905d839b</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Titel: Sehr leckeres Essen ,hab Vegetarisch…, Text: Sehr leckeres Essen ,hab Vegetarisch bestellt.</t>
+          <t>Ich wollte eine Bestellung zu einem bestimmten Liefertermin bestellen was nicht möglich war. Der angerufene Mitarbeiter war nicht hilfsbereit.</t>
         </is>
       </c>
       <c r="D35">
         <v>2</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35">
-        <v>1.25</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rev-3d035472-b191-4cdd-97a2-11a6676493c5</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>5</v>
+          <t>rev-6a7bab53-22f2-45d4-ad83-fd13d11c1118</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Titel: Alles sehr gut, Text: Alles sehr gut - mehr bedarf es nicht zu sagen.</t>
+          <t>Gerichte schmecken lecker, sehen appetitlich aus, sind jedoch zu klein. _x000D_
+Man wird nicht wirklich satt und das für den Preis von 6,99 € (Penne) ist dann recht teuer.</t>
         </is>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>rev-bdec71e0-bf07-4254-8469-55d205abccf3</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>5</v>
+          <t>rev-e8754dd5-a236-4d0f-892d-8436473d4812</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Titel: schneller Versand super Essen, Text: schneller Versand super Essen_x000D__x000D_
-gerne wieder</t>
+          <t>Große Portionen, die auch sehr gut schmecken. _x000D_
+Schnelle Lieferung also alles top :-)</t>
         </is>
       </c>
       <c r="D37">
         <v>2</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37">
-        <v>1.25</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>rev-b9e0c9c9-c663-442e-939a-8b5d5af7583b</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>5</v>
+          <t>rev-59c253da-6b34-4b59-995d-e11afd912ad2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Titel: Sehr zu empfehlen, Text: Da ich beruflich sehr eingespannt bin, es nicht schaffe immer frisch zu kochen, habe ich eine Alternative gesucht und hier gefunden.  Im Gegensatz zu anderen Unternehmen hat mich die Nachhaltigkeit der Verpackung und auch das Essen selbst positiv überrascht.  Werde mit Sicherheit wieder bestellen und  es auch gerne weiterempfehlen. Danke für die leckeren Speisen und vor allem dem fairen Preis der Gerichte. Sehr lecker,nicht zu stark gewürzte Gerichte ,genauso wie ich es mag. Danke an das gesamte Team und bis bald😉</t>
+          <t>Super schnelle Lieferung, bestens verpackt. Das Essen ist wirklich lecker. Und es ist schnell zubereitet, wenn man gerade keine Zeit und oder Lust hat selbst zu kochen.</t>
         </is>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>5</v>
-      </c>
-      <c r="I38">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>rev-af953f56-3486-4a03-a05a-13dbb4ec13ea</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>5</v>
+          <t>rev-13fb67e6-07aa-4182-9e6a-574771234505</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Titel: Die Lieferung war sehr schnell  und die…, Text: Die Lieferung war sehr schnell  und die zwei Essen die ich bis jetzt probiert habe sind suuuuper lecker 😋</t>
+          <t>alles super</t>
         </is>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>2.5</v>
-      </c>
-      <c r="I39">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rev-f0502250-8605-426a-9eda-6dcdaa6c1300</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>5</v>
+          <t>rev-a27afdbb-eacb-49a5-904b-a49c73408549</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Titel: Es soll alles so bleiben, Text: Es soll alles so bleiben, wie es ist.</t>
+          <t>Perfekte Lieferung,Essen ist hervorragend, beziehe es schon seit Jahren,erst über unsere Firma,jetzt Privat</t>
         </is>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40">
         <v>1</v>
       </c>
       <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>rev-1f993e75-d560-4770-810f-a488e0c247a0</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>4</v>
+          <t>rev-4b813e3c-6cc4-4f09-99c4-26dbf38b076f</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Titel: Zuckerzusatz, Text: Die Gerichte schmecken bisher sehr gut, die Menge ist für mich auch ausreichend. Aber mir gefallen die Zuckerzusätze(Dextrose) nicht bzw. ich vertrage sie nicht. Ich merke das im Bauch. Für andere Leute die damit keine Probleme haben, sind die Gerichte top.</t>
+          <t>Perfekt</t>
         </is>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>8.75</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>rev-36c6b0b2-989a-47ea-9e71-03511c9c288a</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>5</v>
+          <t>rev-d3048a2b-df9d-4ba2-970e-5297d74ba2af</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Titel: Wir freuen uns immer über das Essen und…, Text: Wir freuen uns immer über das Essen und das ist schön wir sagen lecker essen auf 4 Reder</t>
+          <t>Pünktlich geliefert und sehr gute Qualität</t>
         </is>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rev-62a4b1a8-3acf-4e49-9a01-5551064760c1</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>1</v>
+          <t>rev-e9df1a4b-b2f4-48b8-b809-5ec86a6e9420</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Titel: Ich habe leider nichts erhalten bzw der…, Text: Ich habe leider nichts erhalten bzw der Fahrer rief mich am Vormittag an, da musste ich aber arbeiten. Es gibt noch Menschen die arbeiten._x000D__x000D_
-Habe alles gezahlt aber ich werde es nicht weiter empfehlen und auch nicht mehr bestellen._x000D__x000D_
-Das Essen wurde Mittag in eine Postfiliale gebracht in welche,tja keine Ahnung. Der Fahrer sprach leider kein Deutsch und kein Englisch</t>
+          <t>Pünktliche Lieferung und tolle Menüs, sehr lecker und nicht mit den Fertigmahlzeiten aus dem Supermarkt zu vergleichen._x000D_
+Die Menüschalen sind leider etwas groß und es passen dadurch nicht so viele in mein Tiefkühlfach aber dann bestelle ich zukünftig weniger und dafür öfter 😊</t>
         </is>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>8.75</v>
-      </c>
-      <c r="I43">
         <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rev-7c07c18c-bb0e-4331-8299-64c9515af8d3</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>2</v>
+          <t>rev-a39b599b-8679-49ca-9ca9-db780a20cc05</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Titel: Bis jetzt 4 von 10 Gerichten gegessen, Text: Bis jetzt 4 von 10 Gerichten gegessen, hat echt nichts mit Hausmannskost zu tun._x000D__x000D_
-Uns sagt das Essen überhaupt nicht zu.</t>
+          <t>Nach mehrmaliger Bestellung.Hofmann`s macht's.Kundenservice -Top._x000D_
+Die Menüs sind schmackhaft - ausreichend._x000D_
+Jedoch an der Logistik muss noch gefeilt ( Schruppfeile )._x000D_
+E.Uwe Fischer</t>
         </is>
       </c>
       <c r="D44">
@@ -1830,218 +1781,199 @@
         <v>1</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>2.5</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>rev-6f483b66-e827-417e-9a00-e381d1823e45</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>3</v>
+          <t>rev-e563db4e-f32f-4bcf-8c98-d7eddd12d283</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Titel: Lecker, aber kleine Portionen, Text: Ich finde, die Portionen sind ein wenig zu klein. Aber das Essen schmeckt gut.</t>
+          <t>Schneller Versand, sehr gute Gerichte</t>
         </is>
       </c>
       <c r="D45">
         <v>2</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>3.75</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>rev-75bb8a3f-f14d-49cc-b600-a07ca8b719c4</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>3</v>
+          <t>rev-894c1d2a-39e2-4272-af77-b6827b962ddb</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Titel: Keine sosse, Text: Keine sosse</t>
+          <t>Bei der letzten Lieferung waren ein mehrere Deckel offen , die Pommes lagen so im Karton._x000D_
+Am Karton war keine Beschädigung _x000D_
+Es muß beim verpacken übersehen worden sein das verschiedene Deckel nicht verschlossen waren _x000D_
+Grüße J. Eder</t>
         </is>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>rev-21cf269a-7b6a-4b0c-9060-d7ec3ed11e02</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>4</v>
+          <t>rev-84f1e5a9-00c8-4803-8b0c-cbf982520b3b</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Titel: Schmackhaft und günstig, Text: Schmackhaft und günstig</t>
+          <t>Received the ordered items very fast. They are very easy to store in the freezer. I have tried 2 of the meals - they were good (but not very good). At least much better to what you can get in the supermarket. I will try another package and see how they taste.</t>
         </is>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>rev-615b7fee-738e-480c-bc1c-1996b4f11873</t>
-        </is>
-      </c>
-      <c r="B48">
-        <v>4</v>
+          <t>rev-5aeaa569-4512-4af8-b097-a3b73cc0dd89</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Ich habe zum erstem mal dort bestellt…, Text: Ich habe zum erstem mal dort bestellt und mir eine 8er Box zum testen bestellt.  Und bin Positiv überrascht!_x000D__x000D_
-_x000D__x000D_
-Kurz gefasst: Super Verpackung, Gut gewürzt, Einfach Zubereitung!_x000D__x000D_
-_x000D__x000D_
-_x000D__x000D_
-Ein wenig Kritik weswegen 1 Stern Abzug:_x000D__x000D_
-_x000D__x000D_
-Das essen ist wirklich lecker, _x000D__x000D_
-aber leider hatte ich beim Gericht "Rinderhacksteak "Mediterrano" zwei dicke Knorpel im Hacksteak, was nicht so appetitlich ist. Kann passieren, muss aber nicht. :p_x000D__x000D_
-_x000D__x000D_
-Schade das die Fleischhaltigen Gerichte sehr überwiegen und es recht wenig Auswahl gibt ohne Fleisch. _x000D__x000D_
-Allerdings habe ich gesehen das ständig neue Gerichte dazukommen und ich bin gespannt ob es vielleicht in Zukunft mehr Fleischlose alternativen gibt, ich würde mich freuen! :) _x000D__x000D_
-_x000D__x000D_
-Zudem sind für mich die Portionen mit Nudel &amp; Soße ein bisschen klein, wäre schön wenn man vielleicht ein Gericht auswählen könnte mit einer größeren Portion._x000D__x000D_
-_x000D__x000D_
-_x000D__x000D_
-_x000D__x000D_
-_x000D__x000D_
-</t>
+          <t>Immer sehr gut gewürzt und nie zu trocken. _x000D_
+Schnelle Lieferung, kommt super verpackt, gefroren an._x000D_
+Mit Wunschtermin, Perfekt!_x000D_
+Ich bestelle definitiv wieder!</t>
         </is>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>8.75</v>
-      </c>
-      <c r="I48">
         <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>rev-c5cfd07b-7f92-4e16-a8b7-bb2dd24853c3</t>
-        </is>
-      </c>
-      <c r="B49">
-        <v>5</v>
+          <t>rev-053c5463-53e2-4c78-95aa-f828cd891005</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung und…, Text: Schnelle Lieferung und Abwechslungsreiche Ware. Alles was ich bis jetzt bestellt habe war super im Geschmack. Nichts was künstlich schmeckt._x000D__x000D_
-Gerne wieder!!!</t>
+          <t>Echt lecker essen Dankeschön</t>
         </is>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>5</v>
-      </c>
-      <c r="I49">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>rev-4a2a9f87-ad49-4743-b89e-f17f868f0e42</t>
-        </is>
-      </c>
-      <c r="B50">
-        <v>5</v>
+          <t>rev-528fd133-2f13-41ca-a3c1-831f86c0cdce</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Titel: Immer super lecker, Text: Immer super lecker</t>
+          <t>Es ist sehr lecker und genug für 1 Person. Manchmal könnte gerade bei Nudelgerichten etwas mehr Sauce sein. Also weiter so.</t>
         </is>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -2050,57 +1982,56 @@
         <v>1</v>
       </c>
       <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rev-5e6dfb6b-dfee-47cc-acf5-0e35662c3c09</t>
-        </is>
-      </c>
-      <c r="B51">
-        <v>5</v>
+          <t>rev-cc1b7cc8-bbe9-4af3-9da8-278c82ac4aa7</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Titel: Lieferung ging wie gewohnt ohne…, Text: Lieferung ging wie gewohnt ohne Probleme und bis jetzt sind alle Gerichte sehr lecker und ausreichend</t>
+          <t>Pünktliche Lieferungen, leckeres Essen</t>
         </is>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>2.5</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rev-976db779-594d-4b64-8605-a50809cb39d6</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>5</v>
+          <t>rev-5e82397c-70c7-422a-a2e8-f2e9227d7965</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Titel: Kompetenter Service bei Problemen, Text: Kompetenter Service bei Problemen, super Produktpalette, gute Qualität und schnelle Abwicklung und Lieferung</t>
+          <t>Die Menüs sind gut portioniert und schmackhaft._x000D_
+Lieferung sehr pünktlich und sehr gut verpackt - allerdings muss das recht umfangreiche (Öko-) Verpackungsmaterial auch entsorgt werden.</t>
         </is>
       </c>
       <c r="D52">
@@ -2116,31 +2047,30 @@
         <v>2</v>
       </c>
       <c r="H52">
-        <v>2.5</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rev-e18db993-5982-43e6-a81e-f8d6db54c1f1</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>5</v>
+          <t>rev-bc5bfcdb-74ae-41d2-954d-d2453f78dbc9</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Titel: Immer lecker, Text: Immer lecker, immer schnell und qualitativ  hochwertige Produkte</t>
+          <t>Das entfernen der Hülle um das Stroh ist aufwendig und verursacht Schmutz und Staub.</t>
         </is>
       </c>
       <c r="D53">
         <v>2</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -2149,24 +2079,28 @@
         <v>2</v>
       </c>
       <c r="H53">
-        <v>2.5</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rev-3a9a2eef-bf9e-4269-84b0-b848d8b6407f</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>5</v>
+          <t>rev-f5f6e6b7-b2bc-40fb-a780-6f7da38a537a</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Titel: Essen schmeckt gut, Text: Essen schmeckt gut, ich nehme es immer zum Dienst mit!</t>
+          <t xml:space="preserve">Hallo zu den Mitarbeitern und Mitarbeiterinnen. Jedes Essen ist sehr schmackhaft . Für die Zunge sehr gut zubereitet. Manches Mal ist mir aber ein kleiner brennender Geschmack in meinem Mund zuviel._x000D_
+Mit traumhaften Gewürzen verfeinert. Bei Ihnen arbeiten wirklich Fachleute_x000D_
+die sich auskennen um Gewürze in den einzelnen Gerichten zu verteilen und abzustimmen. Ich bin der Meinung, dass jedes Gericht mit sehr viel Liebe zubereitet wird._x000D_
+Herzliche Grüße_x000D_
+Luise Juliane Kühner Baldauf_x000D_
+</t>
         </is>
       </c>
       <c r="D54">
@@ -2176,339 +2110,340 @@
         <v>1</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>1.25</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>rev-483f1539-f897-4d4c-a373-9a8d89fc1b30</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>5</v>
+          <t>rev-6c247adf-fac8-473d-85eb-d918b96ffe15</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Die Zubereitung des Filetopfes war…, Text: Die Zubereitung des Filetopfes war geschmacklich sehr gut und war auch sehr reichlich_x000D__x000D_
-</t>
+          <t>zu geringe preisliche Abstufung bei einfachen Gerichten im Vgl. zu Fleisch- und Fischgerichten.</t>
         </is>
       </c>
       <c r="D55">
         <v>2</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>2.5</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rev-4de8d9d8-3adc-4aa0-ba95-d658f02afbb7</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>5</v>
+          <t>rev-f5312e25-c524-466e-905f-5d51ab2c7086</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Titel: Bedenken wurden revidiert, Text: Hatte Bedenken bei über 30Grad TK-Produkte zu ordern... Ware wurde im angegebenen Zeitraum geliefert und alles Top! Verpackung hat funktioniert und dabei wurde sogar an die Umwelt gedacht! Das 1. Essen war sehr gut! Bin begeistert....</t>
+          <t>Alle Essen waren bis jetzt sehr gut.</t>
         </is>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H56">
-        <v>5</v>
-      </c>
-      <c r="I56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rev-5ebb8670-6b4a-55b5-4a19-e253d15c5e13</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>5</v>
+          <t>rev-19536879-85fb-4e29-b902-1382d1cdedc9</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Titel: Sehr lecker und super schnell geliefert., Text: Sehr lecker und super schnell geliefert.</t>
+          <t>Geschmack und Qualität</t>
         </is>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>rev-95fa3d9a-bbad-467e-a5b5-2269c3eaf9e0</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>2</v>
+          <t>rev-fb0610fc-6362-429d-993d-8b7957fca8aa</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Titel: Das Problem ist nicht das Essen selbst, Text: Das Problem ist nicht das Essen selbst, aber der Transport: 2 Schachteln der 8 gelieferten waren defekt, bei einer war der Deckel eingerissen, bei der 2. war der Deckel total lose. Transportschaden !</t>
+          <t>Verpackung ohne Stereopor. Alles wie versrochen.</t>
         </is>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H58">
-        <v>7.5</v>
-      </c>
-      <c r="I58">
         <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>rev-645dcdc5-2963-4170-b03e-6ec688124e45</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>5</v>
+          <t>rev-1ec2ecc0-d6a6-4300-827f-76660cd2f91b</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Titel: Alle Menüs schmecken super gut ., Text: Alle Menüs schmecken super gut ._x000D__x000D_
-Auch das Bio Vanille Eis ist super._x000D__x000D_
-Schnelle Lieferung .alles gut ..</t>
+          <t xml:space="preserve">Ich kenne Hofmann Menü schon lange und weiß, das sie sehr gute Produkte haben. Leider konnte ich nichts dieses mal machen. Trotz dem volle Sterne da meine Rekla schnell und ohne großen aufwand erledigt worden ist._x000D_
+Großes Lob an das Team_x000D_
+G.S._x000D_
+</t>
         </is>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59">
         <v>1</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>2.5</v>
-      </c>
-      <c r="I59">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>rev-4b3d1e78-c810-45c1-90fc-a635dae05303</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>4</v>
+          <t>rev-4abf82a9-12b6-4931-b6f0-60ec63b00c83</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Titel: Die Mahlzeiten schmecken ganz gut, Text: Die Mahlzeiten schmecken ganz gut. Es ist auf der Webseite nicht so klar was Mikrowelle-fahig ist und was nicht. Meistens habe ich nicht so viel Zeit um im Backofen auf zu wärmen. Darauf sollte man auch filtern müssen können.</t>
+          <t>Diesmal ging es sehr lang._x000D_
+Freitag Morgen bis Donnerstag Morgen</t>
         </is>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>3.75</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>rev-00d1c841-4eea-4258-9348-17238eda6aef</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>5</v>
+          <t>rev-f67a92e1-7303-41c0-b8e6-2d8c4070c376</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung und die Gerichte…, Text: Schnelle Lieferung und die Gerichte waren sehr gut.</t>
+          <t>wohlschmeckende und sättigende Mahlzeiten. Ausreichende Portionen</t>
         </is>
       </c>
       <c r="D61">
         <v>2</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61">
-        <v>2.5</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>rev-8a25af03-cbad-425c-9196-e0fba64296e3</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>5</v>
+          <t>rev-c7b36eac-b1a9-4273-9fec-b94dbe72361e</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Super gutes Essen,schnelle  Lieferung …, Text: Super gutes Essen,schnelle  Lieferung  viel Auswahl _x000D__x000D_
- _x000D__x000D_
-</t>
+          <t>Für mich als Flexitarier wären Option zB für:_x000D_
+_x000D_
+- mit / ohne Fleisch _x000D_
+- für Gerichte auch vegetarische Variante_x000D_
+_x000D_
+Von meiner ersten Bestellung bis heute hat sich das Rindfleisch leider zum negativen verändert._x000D_
+_x000D_
+Anfangs waren Rindsrouladen und Sauerbraten / Gulasch meine Lieblinge, mittlerweile nicht mehr._x000D_
+_x000D_
+Fleisch ist nun ziemlich zäh. Damals hast es mit der Gabel zerdrücken können._x000D_
+_x000D_
+Rouladen waren letztes Mal nur 2 kleine, fast schwarze,bemitleidenswerte Ping-Pong-Bälle ohne Füllung (bis auf den Speck)</t>
         </is>
       </c>
       <c r="D62">
         <v>2</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62">
-        <v>1.25</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>rev-ee518974-70e3-4784-9c10-82eee72dae48</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>5</v>
+          <t>rev-14f2d643-0aac-477e-8d99-dc7fe01e073d</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung, Text: Schnelle Lieferung. Smackhaftes Essen</t>
+          <t>Die Verpackung der Menüs (Deckel / Schale) ist teilweise nicht ausreichend festgeschlossen für den Transport. Die Kartons werden beim Transport beansprucht und dadurch werden die Menüschalen stark geschüttelt, so dass Deckel und Schale sich lösen. Daraufhin fallen lose Bestandteile (z.B. Reis) aus der Schale (siehe Bild). Entsprechend beschädigt kommen die Menüschalen in den Tiefkühler. In unserem Fall zwei Menüschalen werden, wahrscheinlich ein reduziertes Geschmackserlebnis entfallten. Bitte verbessern Sie die Haftung zwischen Schale und Deckel._x000D_
+Grundsätzlich sind die Menüs sehr ansprechend und bieten eine Vielfalt.</t>
         </is>
       </c>
       <c r="D63">
         <v>2</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63">
-        <v>1.25</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>rev-b6201f57-2082-403c-bd65-ac1b85ca4cab</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>5</v>
+          <t>rev-d18d94ac-7710-57aa-0a02-d061c95ae0a1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Titel: Bin sehr zufrieden!, Text: Bin sehr zufrieden!</t>
+          <t>Einlösen des ZFZ Sommerfest-Rabatt hat nicht geklappt und ein Alternative wurde mir  leider nicht geboten . Schade</t>
         </is>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -2517,765 +2452,735 @@
         <v>1</v>
       </c>
       <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>rev-5f408a5c-257e-4104-a2a0-70e50fe87c2f</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>4</v>
+          <t>rev-068ebd42-df05-484c-a694-d08b88606862</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Titel: Es ist alles ok, Text: Es ist alles ok. Meine Frage nehmt ihr die Strohverpackung/Isolierung wieder_x000D__x000D_
-zurück?</t>
+          <t>Schnelle Lieferung</t>
         </is>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>rev-ea03c9e9-26f1-4142-b4a3-f6b931a5b8df</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>4</v>
+          <t>rev-160747ec-e564-4f38-82a6-2ccec7a1046d</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Titel: An der Bestellung und am Bestellweg…, Text: An der Bestellung und am Bestellweg gibt's nichts zu bemängeln. Alles Bestens. Die Gerichte kamen super tiefgekühlt an. Leider stimme ich nicht mit der Zubereitung überein. Die Zeiten sind zu kurz und die Temperatur zu niedrig. Im Backofen werden Kartoffelprodukte zu trocken. Ich empfehle Mikrowelle und Bratpfanne, ggf vorher auf/antauen. Die Gerichte werden dann lecker.</t>
+          <t>Schnelle Lieferung, Gutes Essen. Für mich sehr gut 👍</t>
         </is>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H66">
-        <v>8.75</v>
-      </c>
-      <c r="I66">
         <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>rev-a484062c-e5e6-4a2d-8c91-f632a93d4be4</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>5</v>
+          <t>rev-c4e0075e-6456-4618-aa43-d3f4d84b1587</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Titel: Gute Essen, Text: Die Lieferung kam gut verpackt an. Das Essen ist geschmacklich sehr gut. Immer wieder gerne.</t>
+          <t>Schnelle Lieferung noch gut Gefroren .Wahre_x000D_
+Ist sehr Gut</t>
         </is>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67">
-        <v>3.75</v>
-      </c>
-      <c r="I67">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>rev-2d45705a-6213-40d1-903c-d8f8babf26d2</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>5</v>
+          <t>rev-b9eefa79-8dac-4b2c-a234-ceb9c2a8948d</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Titel: Sehr gutes Essen., Text: Sehr gutes Essen._x000D__x000D_
-Schmeckt alles sehr gut._x000D__x000D_
-Kann ich nur Empfehlen</t>
+          <t>Schnelle und perfekt verpackte Lieferung. Qualität der Menues perfekt!</t>
         </is>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>rev-c7aa741a-7ce9-4e2d-bf7d-4514c692cf7b</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>5</v>
+          <t>rev-4489ea9b-123a-486c-af65-c02ac5fdf9ea</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Titel: Beste Gerichte, Text: Beste Gerichte, ich war schon geschäftlich in Boxberg da wird alles frisch zubereitet.</t>
+          <t>👍</t>
         </is>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>2.5</v>
-      </c>
-      <c r="I69">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>rev-4d4e844c-b37e-4807-9c2c-6960a3190070</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>5</v>
+          <t>rev-be8c4994-ed7f-48ad-8aba-83fdd5814186</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Das Essen schmeckt wie Hausgemacht,und…, Text: Das Essen schmeckt wie Hausgemacht,und das ohne selbst viel Arbeit reingesteckt zu haben.Einfach genial und lecker.Zeit gespart,und Primetime gewonnen mit gutem Geschmack_x000D__x000D_
-</t>
+          <t>Sehr leckere Gerichte !! Toller Geschmack. !! Schnelle Lieferung. !! Toller Service. !!  TOP. !!</t>
         </is>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>5</v>
-      </c>
-      <c r="I70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rev-51737886-0a84-4ecf-b5db-b6c7f2580b17</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>5</v>
+          <t>rev-f2442da3-7139-41a7-a59d-1b864f0355b4</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Verpackung wieder mitnehmen bezw, Text: Verpackung wieder mitnehmen bezw.  wieder  abholen. _x000D__x000D_
-</t>
+          <t>Schnell und zuverlässig, gerne wieder</t>
         </is>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>rev-3a73cbf2-c599-4750-b028-384cd5add7f3</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>5</v>
+          <t>rev-c7e028f8-4c62-478c-b387-091b5b4b9721</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Titel: Also ich bin  ja noch dabei es zu testen…, Text: Also ich bin  ja noch dabei es zu testen, aber bis jetzt schmeckt es wirklich sehr gut. Restaurant kann man sich sparen. Danke</t>
+          <t>Leckere Speisen in guter Qualität für Hungrige und Genießer. Ein breites Sortiment bietet jeweils bei Erstbestellungen spannende Überraschungen</t>
         </is>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>2.5</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>rev-d17af67b-ef4f-d8ef-d7fd-d6e2132a074f</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>5</v>
+          <t>rev-f78393e0-a773-4abb-ba93-24ad03e8f781</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Titel: Kundenservice konnte nicht Bewertet werden da kein Kontakt, Text: Kundenservice konnte nicht Bewertet werden da kein Kontakt</t>
+          <t>Die Lieferung kam angetaut bei mir an. Da ich kein Koch bin, was auch der Grund wäre um bei ihrer Firma nochmals zu kaufen, weiß ich natürlich nicht, was in so einem Fall getan werden muss - es gab keinen Hinweis für so einen Fall. Dass Essen ist gut und ausreichend.</t>
         </is>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>rev-2a0a8230-2faf-4cd2-a443-4e2d3abde35b</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>5</v>
+          <t>rev-4fb3b47e-c667-4a8e-a109-1f4f5384c00e</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Titel: Essen sehr gut und super schnelle liefer, Text: Essen sehr gut und super schnelle Lieferung</t>
+          <t>Alles sehr umweltfreundlich verpackt , und die Gerichte sind sehr lecker!</t>
         </is>
       </c>
       <c r="D74">
         <v>2</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74">
         <v>1</v>
       </c>
       <c r="H74">
-        <v>1.25</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>rev-067763b6-a535-443f-97aa-1175d62e727d</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>5</v>
+          <t>rev-5b974508-dc01-4d1d-bae1-36aeb2d9042e</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Titel: Hinweis auf Schärfegrad wäre toll., Text: Drauf hinweisen das ein Gericht scharf ist. Zudem wäre es schön wenn auch der schärfe Grad einzuschätzen wäre. Zum Beispiel ein Hinweis leicht scharf, mittel scharf, sehr scharf usw. Damit sich der Kunde einen Eindruck davon machen kann.</t>
+          <t>Portionen zu dem Preis zu klein zu wenig ansonsten ok</t>
         </is>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>7.5</v>
-      </c>
-      <c r="I75">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>rev-9abe95a2-e331-493d-8328-2078d3ca6eab</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>4</v>
+          <t>rev-5210464f-9046-4e4d-bf0e-92134fd2625a</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Titel: sehr gute Ware, Text: sehr gute Ware, nur die Antworten auf Fragen dauern sehr lange oder man bekommt gar keine ( warte seit Feb.auf eine )</t>
+          <t>Super frische Ware schmeckt super lecker und sehr schnelle Lieferung _x000D_
+Habe direkt nachbestellt</t>
         </is>
       </c>
       <c r="D76">
         <v>2</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76">
-        <v>5</v>
-      </c>
-      <c r="I76">
         <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>rev-29334f5d-5150-8920-844d-b950715a71d5</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>5</v>
+          <t>rev-f7c68a0e-bc28-4d68-977f-b4b91e601a43</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Titel: alles ok, Text: alles ok</t>
+          <t>Alles kaputt und offen aufgetaut kam es an....musste alles so in die Tonne schmeißen. Auf meine Beschwerde bei Hofmanns das ich mein Geld wieder bekomme,keine Reaktion.</t>
         </is>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>rev-f78aeefd-2839-4a18-9b8b-2d7616546c47</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>4</v>
+          <t>rev-1489c851-db7f-40db-b143-415f3389702b</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Titel: Das Essen ist super, Text: Das Essen ist super. LEIDER, die Lieferung ist einen Tag SPÄTER angekommen. Das Trockeneis existierte NICHT mehr und die Menüschalen waren NICHT mehr komplet gefroren - Schade, hoffe, dass man es noch essen kann.</t>
+          <t>Die meisten Essen sind sehr lecker. Wir nutzen das gern, wenn keine Zeit zum Einkaufen bleibt oder wir zu phantasielos sind ('was soll ich bloß heute wieder kochen?')</t>
         </is>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78">
         <v>2</v>
       </c>
       <c r="H78">
-        <v>6.25</v>
-      </c>
-      <c r="I78">
         <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>rev-5717c363-ea35-4c5b-af8c-5ad0d5cf48a7</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>5</v>
+          <t>rev-6fcba3a3-282c-409e-9eec-1316d85dd603</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Es ist die ideale Idee wenn man Single…, Text: Es ist die ideale Idee wenn man Single ist und ohne großen Aufwand ein leckeres Essen genießen möchte. Der einzige Kritikpunkt - das habe ich Ihrem Kundenservice mitgeteilt   dass der Expressversand Schwachstellen aufweist. Es ist kontraproduktiv wenn der Auslieferer die Bestellung vor die Haustür stellt - bei hohen Aussntemperaturen _x000D__x000D_
-Zwar klingelt - aber nicht wartet  ob der Empfänger auch die Lieferung entgegen nehmen kann ._x000D__x000D_
-Mit freundlichem Gruß Irmtraud Dippel _x000D__x000D_
-</t>
+          <t>NETTER  POSTBODE HILFSBEREICH GERNE WIEDER</t>
         </is>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H79">
-        <v>8.75</v>
-      </c>
-      <c r="I79">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>rev-d97b514a-a041-4dde-8048-dab22bf16214</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>5</v>
+          <t>rev-78df6a87-1609-44cf-824f-200db94a713c</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Titel: Zu 100% überzeugt, Text: Es war unsere erste Lieferung (24 Gerichte). Die bereits probierten Gerichte waren für „TK Essen“ großartig. Gute Portionen und geschmacklich sehr gut. Hervorheben möchten wir die extrem guten Saucen in vernünftiger Menge. Sehr gut ist auch die große Anzahl der auswählbaren Gerichte, sowie die gut zusammengestellten Boxen._x000D__x000D_
-Etwas problematisch sind Beilagen wie Pommes und Bratkartoffeln. Man reißt ein Stück des Deckels ab, so dass diese im Backofen nach oben offen sind. Kann man machen, befriedigt uns jedoch nicht so ganz (ist jedoch produktbedingt und bei weitem kein Fehler seitens Hofmanns). Wir nehmen sie aus der Schale und legen sie ausgebreitet mit in den Ofen. _x000D__x000D_
-In Summe der mit Abstand beste „Lieferservice“ unter vielen, welche wir probiert haben. Hier bleiben wir._x000D__x000D_
-Endlich ehrliche, echte, klassische Dailys und nicht nur dieses „Lifestyle-Food“.</t>
+          <t>Ich bin total zufrieden!!!</t>
         </is>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H80">
-        <v>7.5</v>
-      </c>
-      <c r="I80">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>rev-a0d29901-422f-5abf-b3f0-687f2b5fb33b</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>5</v>
+          <t>rev-7126ce55-3adb-4cb8-b16b-121a655d9d68</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Titel: Wie immer alles bestens nur zu empfehlen, Text: Wie immer alles bestens nur zu empfehlen</t>
+          <t>Tolle Gerichte und ich muss nicht selber kochen.</t>
         </is>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81">
         <v>1</v>
       </c>
       <c r="H81">
-        <v>0</v>
-      </c>
-      <c r="I81">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>rev-f1e403e6-33df-4691-aa69-c83ea17b43d4</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>5</v>
+          <t>rev-0a421fe2-bba1-48af-a32c-17a53f69903b</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Titel: Die Menüs sind Spitzenqualität, Text: Die Menüs sind Spitzenqualität. Wobei die mediterranen Gericht sehr kräftig sind im Geschmack.</t>
+          <t>Das Essen ist perfekt und die Auswahl ist super, lediglich 1 Stern Abzug für die Versandverpackung, die ist leider nicht besonders gut für den Versand, die Isolierung rutscht herum und das Paket wird nass.</t>
         </is>
       </c>
       <c r="D82">
         <v>2</v>
       </c>
       <c r="E82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G82">
         <v>2</v>
       </c>
       <c r="H82">
-        <v>2.5</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>rev-b011af7a-f328-4a86-b875-f9038d7a3d7b</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>5</v>
+          <t>rev-c48fb05f-e9b4-45e1-a94c-13ebd427ce25</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Titel: Immer wieder gerne!, Text: Immer wieder gerne!</t>
+          <t>Die Vielfalt und die Qualität _x000D_
+Leider wie überall immer teurer.</t>
         </is>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>0</v>
-      </c>
-      <c r="I83">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>rev-2c5d7f3e-797f-41b5-8c6a-e04715c45822</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>5</v>
+          <t>rev-6e47d56a-75f4-4e75-bee0-b33645d79649</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Titel: Immer gutes und leckeres Essen, Text: Immer gutes und leckeres Essen . Viel Auswahl einfach super 😉</t>
+          <t>Hofmanns Menüs sind sehr gut</t>
         </is>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>1.25</v>
-      </c>
-      <c r="I84">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>rev-663ab1e9-297d-4a92-8ff0-6af8bf979e6c</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>5</v>
+          <t>rev-ad6a2b60-f9fa-411a-9365-e02535c458dd</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Titel: Daumen hoch !!, Text: Wie immer, schnell und sehr gut, besser geht es nicht....., hier bestell ich immer wieder gerne, Daumen hoch 👍👍👍👍</t>
+          <t>Promte Lieferung.</t>
         </is>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>1.25</v>
-      </c>
-      <c r="I85">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>rev-2f289c80-b9db-482f-b7a3-deca3f4817a4</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>5</v>
+          <t>rev-182b4c4b-2ac9-402c-8d01-49c50ef68dcd</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Titel: Immer wieder gerne, Text: Immer wieder gerne! Sehr gutes Essen</t>
+          <t>Vorzügliches Essen, toller Service, superschnelle Lieferung. Wir sind absolut zufrieden.</t>
         </is>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>0</v>
-      </c>
-      <c r="I86">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>rev-01f1eb72-39e5-437c-8e2c-04a1d0ffa035</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>5</v>
+          <t>rev-9aca9131-fbad-4186-bc9a-798d012ecf7e</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Titel: Top, weil…, Text: Das Preis-leistungsverhältnis ist super...bis jetzt schmecken die Menüs der 8-Tage-Vegane Box so, als hätte ich selbst am Herd gestanden u. abgeschmeckt. Und was für mich wichtig ist, ich werde sogar satt. Die Portion-Menge ist also top...kann ich nur weiter empfehlen u. ich bedaure es, nicht schon viel eher auf "Hofmann's" gestoßen zu sein. Es hätte mir meine Arbeitstage sehr erleichtert. Danke.</t>
+          <t>Die Portionen für einen Erwachsen der regelmäßig Sport treibt sind zu klein. Ich habe zwei Essen zubereiten müssen um meinen Energie- und Hungerbedarf zu stillen. _x000D_
+Die Gerichte selbst sind lecker.</t>
         </is>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E87">
         <v>1</v>
@@ -3284,192 +3189,187 @@
         <v>1</v>
       </c>
       <c r="G87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H87">
-        <v>5</v>
-      </c>
-      <c r="I87">
         <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>rev-7ed13585-529b-452a-becd-f2ea464a5d66</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>5</v>
+          <t>rev-f3383a3a-a1b0-4316-82c9-69845be67820</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Titel: richtige hausmannskost.alles sehr gut…, Text: richtige hausmannskost.alles sehr gut abgeschmeckt.</t>
+          <t>Überdurchschnittliche und schnelle Bestellung durch gute Web seite</t>
         </is>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88">
         <v>1</v>
       </c>
       <c r="H88">
-        <v>1.25</v>
-      </c>
-      <c r="I88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>rev-b539dcf5-26d3-4bf9-a80b-a948c24542f7</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>5</v>
+          <t>rev-c08b2dbc-dff4-4396-8333-f79cd787b234</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Titel: So gut wie ich es erwartet hatte, Text: So gut wie ich es erwartet hatte. Kannte die Produkte von Hofmann schon von früher von der Arbeit. War und ist immer noch köstlich. Normalerweise sind 5 Sterne zu wenig. Macht weiter so.</t>
+          <t>Ich bin immer wieder überrascht, was Ihr für uns zubereitet. Es schmeckt so gut.</t>
         </is>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H89">
-        <v>2.5</v>
-      </c>
-      <c r="I89">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>rev-322c9634-74f7-127e-8971-ec2b86b8b537</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>5</v>
+          <t>rev-67424b1f-475c-0126-a7b5-9b8f92c02e9b</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Titel: lecker Essen,schnelle Lieferung, Text: lecker Essen,schnelle Lieferung</t>
+          <t>Unkompliziert und lecker.</t>
         </is>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>1.25</v>
-      </c>
-      <c r="I90">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>rev-0dec0e33-685a-446c-be9b-b20fda4c620e</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>5</v>
+          <t>rev-483655ad-4641-4c2c-aa93-3a7222870c7f</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Titel: Leider klappte die Zustellung nicht, Text: Leider klappte die Zustellung nicht. Obwohl ich einen Ablageort ohne Unterschrift angegeben hatte, wurde es beim Nachbarn abgegeben. Und der war erst spät ansprechbar. Da war die Ware schon leicht aufgetaut. Die Zusteller machen gerade was sie wollen...!</t>
+          <t>Sehr lecker 😋</t>
         </is>
       </c>
       <c r="D91">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E91">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H91">
-        <v>7.5</v>
-      </c>
-      <c r="I91">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>rev-f78393e0-a773-4abb-ba93-24ad03e8f781</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>3</v>
+          <t>rev-b00d0068-e77b-472d-a8e0-512d2e9da121</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Titel: Die Lieferung kam angetaut bei mir an, Text: Die Lieferung kam angetaut bei mir an. Da ich kein Koch bin, was auch der Grund wäre um bei ihrer Firma nochmals zu kaufen, weiß ich natürlich nicht, was in so einem Fall getan werden muss - es gab keinen Hinweis für so einen Fall. Dass Essen ist gut und ausreichend.</t>
+          <t>Die Menüs haben in letzter Zeit sehr häufig Gefrierbrand. Bei einer telefonischen Reklamation wollte man mir nicht weiterhelfen, auf eine schriftliche Reklamation hin habe ich seit 8. Januar keine Reaktion</t>
         </is>
       </c>
       <c r="D92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G92">
         <v>2</v>
       </c>
       <c r="H92">
-        <v>7.5</v>
-      </c>
-      <c r="I92">
         <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>rev-8001bc29-777c-48fb-91c6-c5e3860c021c</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>5</v>
+          <t>rev-05b910b7-9581-4d12-a65f-cb8bf386a884</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung und leckere Gerichte, Text: Besonders gut hat mir die schnelle Lieferung und die leckeren Gerichte gefallen.</t>
+          <t>Ich weiß nicht nicht wo meine Bestellung ist und wann Sie geliefert wird. Als Zeitfenster um Sie anzunehmen habe ich nur Samstags und Montags._x000D_
+&gt;Ich hatte einen festen Liefertermin ausgewählt. Weiß aber nicht ob meien Bestellung an dem Tag geliefert wird, Da es sich hier um TK Ware handelt wäre dies schon schön.</t>
         </is>
       </c>
       <c r="D93">
@@ -3485,91 +3385,87 @@
         <v>2</v>
       </c>
       <c r="H93">
-        <v>2.5</v>
-      </c>
-      <c r="I93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>rev-a116f241-3ced-4b5f-abeb-738d612565cc</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>4</v>
+          <t>rev-86b1c2cf-e1f9-c5a6-9e7f-51f5a2512a53</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Titel: Lecker TK Menüs, Text: Reichhaltige Auswahl an leckeren Menüs. Man schmeckt, dass hier mit Gewürzen gekocht wird. 4Peffersoße schlecht auch nach Pfeffer. Fleisch ist von guter Qualität und bisher immer butterzart. Gemüse bissfest und nicht matschig. Portionen ausreichend . Meist so um 500 Gramm. Deklaration umd Inhaltsstoffe sehr ausführlich. _x000D__x000D_
-Sehr schön finde ich die nachhaltige Verpackung. Kein Plastik. Lässt sich kom</t>
+          <t>Wie immer perfekt</t>
         </is>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H94">
-        <v>5</v>
-      </c>
-      <c r="I94">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>rev-550fec03-054a-4ace-8c67-a5eac5cfa996</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>5</v>
+          <t>rev-6c97f7c2-fa3a-4e69-ba66-efbd19d7e979</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Titel: Schnell gemacht, Text: Einfache Zubereitung und wirklich lecker 😋</t>
+          <t>Die Testbox war hervorragend. Jeder Tag ein Genus.</t>
         </is>
       </c>
       <c r="D95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H95">
-        <v>2.5</v>
-      </c>
-      <c r="I95">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>rev-1a4231d1-b81b-47d3-82cd-a88217fd61a7</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>5</v>
+          <t>rev-6b639669-2b58-4673-adbd-475de18275c0</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Titel: Hallo das Essen ist sehr lecker und gut…, Text: Hallo das Essen ist sehr lecker und gut gelungen ein lieben Dank auch an die Köche die das Essen zubereiten ganz toll gemacht bis bald 😌👍👍👍👍🤠</t>
+          <t>Ich habe noch nicht alle Gerichte gegessen, aber die die ich probiert habe waren sehr lecker und ich bin auf die anderen gespannt. Bei der Erbsensuppe waren die Würstchen nicht der Renner aber sonst war sie sehr gut. Waren bis jetzt mit Abstand die besten Fertiggerichte die ich versucht habe und es war nicht das letzte mal, dass ich bestellt habe.</t>
         </is>
       </c>
       <c r="D96">
@@ -3579,349 +3475,320 @@
         <v>1</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96">
         <v>2</v>
       </c>
       <c r="H96">
-        <v>2.5</v>
-      </c>
-      <c r="I96">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>rev-e19727bb-7d22-44e1-a72a-99d255330cc9</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>5</v>
+          <t>rev-8665485f-68ee-491e-ae47-5d68971db9a3</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Titel: Bestellt und in kürzester Zeit…, Text: Bestellt und in kürzester Zeit geliefert.Super verpackt.Essen schmeckt richtig gut.</t>
+          <t>Habe Vegetarisch bestellt und alles ist sehr lecker</t>
         </is>
       </c>
       <c r="D97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>5</v>
-      </c>
-      <c r="I97">
         <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>rev-dc4b02d5-ccd0-40da-8763-a813b8d4b9ee</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>5</v>
+          <t>rev-2ced9048-ce9c-484b-9db9-bcda38c30f9e</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Titel: Schnelle eiskalte Lieferung,bin…, Text: Schnelle eiskalte Lieferung,bin begeistert,Genuss der auch satt macht,es ist und bleibt mein Laden</t>
+          <t>Alles Super gelaufen wie immer danke</t>
         </is>
       </c>
       <c r="D98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>2.5</v>
-      </c>
-      <c r="I98">
         <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rev-014204c3-30af-e33a-6e36-ce2b87105303</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>5</v>
+          <t>rev-8e5e5985-676f-4bda-87ce-f0a0bd2de0f8</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Titel: Wir haben für meine Mutter bisher 2x bestellt, die Lieferung erfolgt durch DHL und ging beide male sehr schnell, leichte Zubereitung im Backofen und geschmacklich fand sie das Essen einwandfrei., Text: Wir haben für meine Mutter bisher 2x bestellt, die Lieferung erfolgt durch DHL und ging beide male sehr schnell, leichte Zubereitung im Backofen und geschmacklich fand sie das Essen einwandfrei.</t>
+          <t>Der Geschmack bekommt 5 sterne_x000D_
+Verpackung 2 sterne_x000D_
+Versand über DPD leider -4_x000D_
+Habe schon mal was bestellt da war alles gut</t>
         </is>
       </c>
       <c r="D99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99">
         <v>1</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H99">
-        <v>5</v>
-      </c>
-      <c r="I99">
         <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>rev-642cb4b4-c836-4318-abb9-4a329ed6fa8a</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>1</v>
+          <t>rev-855639e0-e266-41b6-902a-a89c3c555e2b</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Ich habe den ganzen Tag auf mein Packe…, Text: Ich habe den ganzen Tag auf mein Packe gewartet bis jetzt um 19:26 Uhr ist es noch nicht angekommen. Bei DPD steht man hat die  Daten erhalten. Den Text habe ich angehängt._x000D__x000D_
-_x000D__x000D_
-Ihr DPD Zusteller_x000D__x000D_
-Wir haben die Auftragsdaten zu diesem Paket erhalten._x000D__x000D_
-Ihre Änderungs-Optionen_x000D__x000D_
-Sobald der Status "Paket unterwegs" erreicht ist, können Sie hier Ihr Paket nach Ihren Wünschen steuern._x000D__x000D_
-_x000D__x000D_
-Lieferdetails_x000D__x000D_
-Versender:_x000D__x000D_
-Hofmann Menü-Manufaktur GmbH_x000D__x000D_
-Deutschland_x000D__x000D_
-Empfänger:_x000D__x000D_
-Klaus Lorch_x000D__x000D_
-Konrad-Adenauer-Str. 2_x000D__x000D_
-67459 Böhl-Iggelheim_x000D__x000D_
-Gewicht_x000D__x000D_
-20,00 kg_x000D__x000D_
-</t>
+          <t>Es wurde mir ein 20€ Gutschein versprochen. Die Email war ohne Anschreiben und sehr unpersönlich. Auf Meike Frage habe ich keine Antwort erhalten und auch keinen Gutschein</t>
         </is>
       </c>
       <c r="D100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100">
-        <v>5</v>
-      </c>
-      <c r="I100">
         <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rev-9a21a12d-8c18-45c4-8cb9-63f36d6eab57</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>4</v>
+          <t>rev-ed355075-5087-7f55-637a-a8641e38715e</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Titel: Das Essen ist echt lecker, Text: Das Essen ist echt lecker, wie bei Muttern._x000D__x000D_
-Was allerdings echt nervt, ist das man keinerlei Trackinginfos bekommt._x000D__x000D_
-So sitzt man man bei blauem Himmel und Sonnenschein zu Hause und wartet auf die Lieferung._x000D__x000D_
-Bei anderen Anbietern kann ich mir den Liefertag und Vor-oder Nachmittag aussuchen._x000D__x000D_
-VERBESSERUNGSWÜRDIG!</t>
+          <t>Sehr schnelle Lieferung und super leckeres Essen. Schade, dass es für Privatkunden nicht so viel Auswahl gibt wie für die Essen auf Rädern-Kunden.</t>
         </is>
       </c>
       <c r="D101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E101">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H101">
-        <v>10</v>
-      </c>
-      <c r="I101">
         <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>rev-173ecc4c-f6cc-4b1d-8a74-f093bb823b1a</t>
-        </is>
-      </c>
-      <c r="B102">
-        <v>4.67</v>
+          <t>rev-66c6a6f2-fb5d-4e5a-86c4-109ddcd272c1</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung, Essen hat gut geschmeckt, Text: Schnelle Lieferung, Essen hat gut geschmeckt</t>
+          <t>Sehr lecker und gefroren angekommen</t>
         </is>
       </c>
       <c r="D102">
         <v>2</v>
       </c>
       <c r="E102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102">
-        <v>1.25</v>
-      </c>
-      <c r="I102">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>rev-f01d9ee6-2dca-46fa-bbb5-abfc9efe4a3e</t>
-        </is>
-      </c>
-      <c r="B103">
-        <v>5</v>
+          <t>rev-0f4a2a8a-ed45-ce17-327a-3752baf9b3e7</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Titel: Sehr gut alles super und sehr lecker…, Text: Sehr gut alles super und sehr lecker geschmeckt Danke besser machen können sie nicht es war alles gut</t>
+          <t>Schnelle Lieferung und lecker. Super das es jezt auch in der Mikrowelle geht</t>
         </is>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103">
         <v>1</v>
       </c>
       <c r="H103">
-        <v>0</v>
-      </c>
-      <c r="I103">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rev-fea9806f-40e4-4dfa-857a-4c40bf69b21f</t>
-        </is>
-      </c>
-      <c r="B104">
-        <v>5</v>
+          <t>rev-a6a2269b-ac5f-c913-a260-3da012f64d79</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Titel: Das erste Mal bestellt und alles lief…, Text: Das erste Mal bestellt und alles lief reibungslos._x000D__x000D_
-Vielen Dank für den super Service!</t>
+          <t>Schnelle Lieferung, sicher und gut verpackt. Geschmack ist top, wie frisch gekocht. Gemüse bissfest, Fleisch zart, weder lasch noch überwürzt und ohne diesen typischen Fertiggerichte-Krankenhaus-Geschmack. Portionsgröße ist okay, kräftige Männer brauchen wahrscheinlich zwei Portionen.</t>
         </is>
       </c>
       <c r="D104">
         <v>2</v>
       </c>
       <c r="E104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H104">
-        <v>1.25</v>
-      </c>
-      <c r="I104">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>rev-04e1ec75-3f74-4fb6-9100-70073ee137ec</t>
-        </is>
-      </c>
-      <c r="B105">
-        <v>5</v>
+          <t>rev-fe75c575-4372-4b07-8bed-d8b6eda2159e</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Titel: Eine wunderbare Alternative sich gesund zu ernähren., Text: Ich habe verschiedene Gerichte ausprobiert und bin begeistert.</t>
+          <t>Das Essen schmeckt wie selbstgemacht und wird immer wieder gern gegessen wenn es mal schnell gehen muss.</t>
         </is>
       </c>
       <c r="D105">
         <v>2</v>
       </c>
       <c r="E105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105">
         <v>2</v>
       </c>
       <c r="H105">
-        <v>2.5</v>
-      </c>
-      <c r="I105">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>rev-1c4432e7-07b5-4148-bb49-47bcce44bc23</t>
-        </is>
-      </c>
-      <c r="B106">
-        <v>5</v>
+          <t>rev-f28d820c-d703-4024-85d6-ff1b154170e5</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Titel: gute, Text: gute, schmackhafte Gerichte</t>
+          <t>Tolle Gerichte guter Geschmack und Qualität mega leider bei den Gerichten mit sosse zuwenig sosse die lecker ist.</t>
         </is>
       </c>
       <c r="D106">
@@ -3937,263 +3804,255 @@
         <v>1</v>
       </c>
       <c r="H106">
-        <v>1.25</v>
-      </c>
-      <c r="I106">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>rev-62232419-55d4-4ca1-87d7-63ec031b2542</t>
-        </is>
-      </c>
-      <c r="B107">
-        <v>4</v>
+          <t>rev-b11557e0-3d76-42c9-bbc9-9bbd089828ba</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Titel: Habe in meiner Berufszeit mit Hofmann…, Text: Habe in meiner Berufszeit mit Hofmann zusammen gearbeitet daher kann ich nur gutes berichten</t>
+          <t>Trockeneis Päckchen waren bei Paketanlieferung zum Teil (2 von 4) bereits leer._x000D_
+Ware war noch gefroren - zum Glück.</t>
         </is>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H107">
-        <v>0</v>
-      </c>
-      <c r="I107">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>rev-db764e9a-699c-443d-bfaf-eee909d654c5</t>
-        </is>
-      </c>
-      <c r="B108">
-        <v>5</v>
+          <t>rev-b9bb4100-7ba5-424f-a9ff-3da08d2775e1</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Titel: Perfekt, Text: Sehr guter Shop</t>
+          <t>Alles Klasse verpackt, Bestellung kommt sehr schnell ca. 2 Tage später. Schmeckt alles wie bei Muttern</t>
         </is>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108">
         <v>1</v>
       </c>
       <c r="H108">
-        <v>0</v>
-      </c>
-      <c r="I108">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>rev-acb28987-5c6d-4cca-9e78-186b7cbaeea6</t>
-        </is>
-      </c>
-      <c r="B109">
-        <v>5</v>
+          <t>rev-adf18c52-05e2-46fd-b85c-a163b7ab16a3</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Titel: Die Menü`s sind sehr gut-und Lieferung und Verpackung super., Text: Die Menü`s sind sehr gut-und Lieferung und Verpackung super.</t>
+          <t>Schmeckt sehr gut,Portion reicht für mich</t>
         </is>
       </c>
       <c r="D109">
         <v>2</v>
       </c>
       <c r="E109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109">
         <v>1</v>
       </c>
       <c r="H109">
-        <v>1.25</v>
-      </c>
-      <c r="I109">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rev-3c763a3d-5e19-47de-b899-ffdecaa56aac</t>
-        </is>
-      </c>
-      <c r="B110">
-        <v>5</v>
+          <t>rev-7b68b4b9-3b74-0f94-6cbb-8e507fc3750e</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Titel: Bis auf Winzigkeiten, Text: Bis auf Winzigkeiten, die aber sicherlich Geschmacksache sind ist alles bestens._x000D__x000D_
-Bislang nur 2 Dinge die ich für mich nicht gut fand.</t>
+          <t>bestens. Geschmack super. gern wieder</t>
         </is>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H110">
-        <v>2.5</v>
-      </c>
-      <c r="I110">
         <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>rev-3c74fd4a-0fd9-d1bb-e0e4-916783575bd4</t>
-        </is>
-      </c>
-      <c r="B111">
-        <v>5</v>
+          <t>rev-34336869-96ee-4687-ab0e-f5aec1a9faed</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Titel: Alles bestens!, Text: Alles bestens!</t>
+          <t>Alles super. Bestellung, Lieferung, Qualität der Erzeugnisse</t>
         </is>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111">
-        <v>0</v>
-      </c>
-      <c r="I111">
         <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rev-8f539f75-1849-45c3-8263-246534d5c1f1</t>
-        </is>
-      </c>
-      <c r="B112">
-        <v>5</v>
+          <t>rev-a5eebdf3-1b64-43d2-a1b8-5a1bd3549f1d</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Titel: Die Auswahl ist groß, Text: Die Auswahl ist groß, die Gerichte sind schmackhaft</t>
+          <t>Schnelle Online Bestellung, Lieferung und das Essen ist sehr schmackhaft</t>
         </is>
       </c>
       <c r="D112">
         <v>2</v>
       </c>
       <c r="E112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H112">
-        <v>2.5</v>
-      </c>
-      <c r="I112">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>rev-f6db20ce-2f9c-4a89-95d3-45b97e41a649</t>
-        </is>
-      </c>
-      <c r="B113">
-        <v>5</v>
+          <t>rev-96d4e39d-d677-4c27-b2d7-c039b9d7f46a</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Titel: Perfektes Konzept, Text: Perfektes Konzept. Kein Plastikmüll und gut Qualität der Speisen. Klare Empfehlung!!!!</t>
+          <t>Ausgezeichnetes Essen, schnelle Lieferung</t>
         </is>
       </c>
       <c r="D113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H113">
-        <v>2.5</v>
-      </c>
-      <c r="I113">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>rev-652732bf-1404-4864-b83b-40d38089adc6</t>
-        </is>
-      </c>
-      <c r="B114">
-        <v>5</v>
+          <t>rev-5ef1cdb4-4e9d-490f-b645-03474da7541f</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Titel: Schmeckt lecker, Text: Schmeckt lecker, war pünktlich, alles gut frisch</t>
+          <t>Geschmack ist sehr gut.Beim Sauerbraten könnte ein paar Klöschen mehr sein.</t>
         </is>
       </c>
       <c r="D114">
         <v>2</v>
       </c>
       <c r="E114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114">
         <v>1</v>
@@ -4202,57 +4061,55 @@
         <v>1</v>
       </c>
       <c r="H114">
-        <v>1.25</v>
-      </c>
-      <c r="I114">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>rev-f82c4d06-1564-4222-9757-8370c0b13532</t>
-        </is>
-      </c>
-      <c r="B115">
-        <v>5</v>
+          <t>rev-5ef57c5a-9570-4bee-6c29-859480eb0cf9</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Titel: Ich habe mehrfach bei dem Shop bestellt…, Text: Ich habe mehrfach bei dem Shop bestellt und bin nie enttäuscht worden.</t>
+          <t>Ausgesprochen gutes Produkt</t>
         </is>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>0</v>
-      </c>
-      <c r="I115">
         <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>rev-2b820abc-ae60-4d4b-bc3b-489fa8471f3e</t>
-        </is>
-      </c>
-      <c r="B116">
-        <v>5</v>
+          <t>rev-4778af42-4f30-4108-921d-d7f282070489</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Titel: gut und bequem, Text: gut und bequem, leider sind nicht alle Gerichte für die Mikrowelle</t>
+          <t>Es ist für mich das erste Mal, dass ich bei Hofmanns bestellt habe. Ich fand die Idee, dass man fertiges Essen bestellen und nach Lust und Laune aufwärmen kann, gut. Meine Erfahrungen gelten nur für den vegetarischen Bereich, und da muss ich sagen, dass ich doch ziemlich enttäuscht bin. Abgesehen davon, dass wenig gewürzt wurde (das könnte man ja noch nachholen), gibt es zu den Gerichten oft eine weisse Sauce, die immer gleich schmeckt, und die den wenigen Geschmack des Essens auch noch ertränkt.</t>
         </is>
       </c>
       <c r="D116">
@@ -4268,560 +4125,546 @@
         <v>2</v>
       </c>
       <c r="H116">
-        <v>3.75</v>
-      </c>
-      <c r="I116">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>rev-fccae010-2dd9-4457-be70-6cf944bdcaa8</t>
-        </is>
-      </c>
-      <c r="B117">
-        <v>5</v>
+          <t>rev-58e0ba1d-fc94-4b87-b6c6-6fbd30b67383</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Titel: Superschnelle Lieferung alles wie…, Text: Superschnelle Lieferung alles wie bestellt und schmeckt lecker</t>
+          <t>Wir haben lange gesucht und endlich gute Fertigessen bei Hofmanns gefunden. Die Auswahl ab Gerichten ist sehr umfangreich und es schmeckt alles wirklich gut. Da wir beide selbständig sind und mittags einfach keine Zeit zum kochen haben ist das eine tolle Lösung. Auch das Stroh das zur Isolierung benutzt wird ist echt eine gute Idee und meine Hühner freuen sich darüber. Mega!</t>
         </is>
       </c>
       <c r="D117">
         <v>2</v>
       </c>
       <c r="E117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117">
         <v>2</v>
       </c>
       <c r="H117">
-        <v>2.5</v>
-      </c>
-      <c r="I117">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rev-75659e69-3f00-4c51-8930-d7d5623c6646</t>
-        </is>
-      </c>
-      <c r="B118">
-        <v>5</v>
+          <t>rev-a1099a78-8fa9-4cb2-8de1-700ade112e9d</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung, Text: Schnelle Lieferung. Tolle Verpackung. Die Ware war noch richtig gefrostet. Leckeres Essen noch dazu.</t>
+          <t>Alles wirklich perfekt. _x000D_
+Verbesserungsvorschlag: Gerichte mit Alkohol farblich auf der Packung kennzeichnen.</t>
         </is>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G118">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>5</v>
-      </c>
-      <c r="I118">
         <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>rev-900151d0-1a0b-592a-b840-a5f23b707d81</t>
-        </is>
-      </c>
-      <c r="B119">
-        <v>5</v>
+          <t>rev-401dd728-8418-442f-8dce-2a09fca49c21</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Titel: Lieferung der Ware ist schnell und zuverlässig, die Menüs sind sehr gut wie im Restaurant., Text: Lieferung der Ware ist schnell und zuverlässig, die Menüs sind sehr gut wie im Restaurant.</t>
+          <t xml:space="preserve">⭐⭐⭐⭐⭐_x000D_
+_x000D_
+Ich bin absolut begeistert von meiner Erfahrung mit Hoffmanns! Die Lieferung meines gefrorenen Essens war einwandfrei. Das Paket enthielt Trockeneis, das die Ware perfekt unter minus 18 Grad gehalten hat, selbst während eines 14-stündigen Versands. Diese Sorgfalt und Qualität im Service haben mich beeindruckt. Hoffmanns hat einen neuen Stammkunden gewonnen, und ich freue mich darauf, weiterhin von ihnen zu bestellen. Ich würde es jedem empfehlen! Bitte machen Sie darauf aufmerksam, dass sie mit Trockeneis versenden – das ist wirklich ein großer Pluspunkt!_x000D_
+_x000D_
+</t>
         </is>
       </c>
       <c r="D119">
         <v>2</v>
       </c>
       <c r="E119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H119">
-        <v>1.25</v>
-      </c>
-      <c r="I119">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>rev-b982b48e-6ff8-475a-91af-ef48ff0cd9bd</t>
-        </is>
-      </c>
-      <c r="B120">
-        <v>5</v>
+          <t>rev-b25d9078-92cf-4969-b606-409add910fd3</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Titel: Beste Fertig Essen was man im Netz…, Text: Beste Fertig Essen was man im Netz bestellen kann.</t>
+          <t>Speisen sind sehr schmackhaft_x000D_
+Fleisch wunderbar weich</t>
         </is>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120">
         <v>1</v>
       </c>
       <c r="H120">
-        <v>0</v>
-      </c>
-      <c r="I120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>rev-82f185dd-2c60-4ac4-891c-a6aae5986188</t>
-        </is>
-      </c>
-      <c r="B121">
-        <v>5</v>
+          <t>rev-3aadccbe-5d97-447d-9fba-c1fd3a7b5fea</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Titel: Das Essen ist wie bei der Mutter, Text: Das Essen ist wie bei der Mutter, geschmackvoll, gut gewürzt u. ausreichend. Ich habe mehrere Firmen ausprobiert und diese ist bis jetzt die Beste._x000D__x000D_
-Was mich aber sehr stört ist die Lieferung als solche. Die Post braucht 2-3 Tage um es auszuliefern und die Trockeneistüten sind beim auspacken leer u. unwirksam. _x000D__x000D_
-Daran müsste was geändert werden._x000D__x000D_
-Ich habe schon 2x größere Menge bestellt, muß aber überlegen ob ich es nochmals tue aber NUR WEGEN LIEFERUNG ! _x000D__x000D_
-DIE MAHLZEITEN SIND EIN GEDICHT !</t>
+          <t>Bereits 5 Werktage warte ich auf meine (erst-)Bestellung. Hatte aber  leider DHL Express vergeigt. Hofmann hatte hier gleich eine Ersatzlieferung rausgeschickt.</t>
         </is>
       </c>
       <c r="D121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H121">
-        <v>10</v>
-      </c>
-      <c r="I121">
         <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>rev-4527b3ca-a1cd-4d73-a94c-ee05bbb258df</t>
-        </is>
-      </c>
-      <c r="B122">
-        <v>5</v>
+          <t>rev-8e422716-2b8a-4475-aa60-eefe10140131</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Titel: Essen ist köstlich !, Text: Die Lieferung ging schnell, die Ware war sehr gut und durchdacht verpackt. Dass Essen schmeckt köstlich und ist von sehr guter Qualität. Kann ich nur weiterempfehlen und werde ich auch weiterhin bestellen.</t>
+          <t>Das Essen ist wie immer gut bis sehr gut, ich hatte schon mehrmals bestellt und war immer zufrieden. Schön und umweltfreundlich fand ich, dass Styropor durch Strohverpackung ersetzt wurde.Nicht so schön fand ich , dass der Paketbote das Paket einfach in das Treppenhaus unseres Mehrfamilienhauses gestellt hat und ich es erst abends gefunden habe. Zum Glück war alles noch gefroren.</t>
         </is>
       </c>
       <c r="D122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122">
         <v>1</v>
       </c>
       <c r="G122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H122">
-        <v>5</v>
-      </c>
-      <c r="I122">
         <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>rev-b55c42bb-2c2d-4f61-9b71-e5ed9678c8e7</t>
-        </is>
-      </c>
-      <c r="B123">
-        <v>4</v>
+          <t>rev-5b43ad06-c898-4947-bd25-b02051f3f2bd</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Titel: Was ich bis jetzt gegessrn habe hat…, Text: Was ich bis jetzt gegessrn habe hat geschmeckt wie bei Oma 🤗🙏👍</t>
+          <t>Krankheitsbedingt kann ich nicht kochen,dank Internet kann man „Essen auf Rädern“ eingeben, so bin ich auf diese Firma gestoßen. Das Angebot ist gut und es schmeckt. Bestellung ist unkompliziert, Lieferung schnell. Gut verpackt. Sollte ich wieder in diese Lebenssituation kommen, bestelle ich gerne wieder</t>
         </is>
       </c>
       <c r="D123">
         <v>2</v>
       </c>
       <c r="E123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123">
         <v>2</v>
       </c>
       <c r="H123">
-        <v>2.5</v>
-      </c>
-      <c r="I123">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>rev-8eba6115-c502-4f14-ae34-3875c6bd13e9</t>
-        </is>
-      </c>
-      <c r="B124">
-        <v>3</v>
+          <t>rev-74b6c7cb-3ec7-46e1-b21d-5ee7c3f90c02</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Titel: Trockeneis war verflüchtigt..., Text: Bei den bisherigen Bestellungen war das Trockeneis in den Kartons ok, also noch nicht verflüchtigt und konnte somit kühlen, dieses mal aber war es komplett leer. Die zwei obersten Essen in der Box waren auch grad noch so gefroren (- 2 Grad)</t>
+          <t>Sehr schnelle Lieferung, alles prima verpackt. Der Fahrer war sehr freundlich und hilfsbereit._x000D_
+Alles bestens, werde wieder bestellen.</t>
         </is>
       </c>
       <c r="D124">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E124">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H124">
-        <v>7.5</v>
-      </c>
-      <c r="I124">
         <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>rev-12fcae07-4e22-48a7-a777-77378b8fd8c6</t>
-        </is>
-      </c>
-      <c r="B125">
-        <v>5</v>
+          <t>rev-395ac9d8-f8d0-4f35-bedd-4e5ba30cb763</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Titel: Leckeres Essen, Text: Leckeres Essen und schnelle Lieferung. Alles top</t>
+          <t>Das Essen ist super. Wir nehmen immer die Boxen.</t>
         </is>
       </c>
       <c r="D125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>1.25</v>
-      </c>
-      <c r="I125">
         <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>rev-02226fb4-2c33-4bfd-89ed-65ab0324fea4</t>
-        </is>
-      </c>
-      <c r="B126">
-        <v>5</v>
+          <t>rev-3b98e85f-824f-3cdd-5f43-076a9f295da7</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Titel: Passt alles zusammen für uns, Text: Schnelle Lieferungen, Qualität ist super, praktisch für Homeoffice und Firma mit schlechter Mensa. Eine Mikrowelle ist immer zur Stelle. Strohmatten zur Isolierung super, wird bei uns als Einstreu bei Hasen und Hühnern verwendet. Fast keinen Müll.</t>
+          <t>Alles ok</t>
         </is>
       </c>
       <c r="D126">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H126">
-        <v>5</v>
-      </c>
-      <c r="I126">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>rev-6b096954-dbc8-4aaa-9543-1aa0d5229437</t>
-        </is>
-      </c>
-      <c r="B127">
-        <v>4</v>
+          <t>rev-d6112bd8-0973-481c-a96a-4ac7fdaac5a8</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Titel: Gut Qualität undachnelle Lieferung, Text: Gut Qualität undachnelle Lieferung</t>
+          <t>Einer von 8 Menü-Kartons/Papschalen war leider halb geöffnet - besser kleben!</t>
         </is>
       </c>
       <c r="D127">
         <v>2</v>
       </c>
       <c r="E127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H127">
-        <v>1.25</v>
-      </c>
-      <c r="I127">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>rev-4c2e738f-6005-4cd3-bf04-81a6d3e72b19</t>
-        </is>
-      </c>
-      <c r="B128">
-        <v>5</v>
+          <t>rev-2f289c80-b9db-482f-b7a3-deca3f4817a4</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Titel: Alles top!, Text: Alles top!</t>
+          <t>Immer wieder gerne! Sehr gutes Essen</t>
         </is>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128">
-        <v>0</v>
-      </c>
-      <c r="I128">
         <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rev-af2af27a-b455-47b0-a625-bcfbf56c5489</t>
-        </is>
-      </c>
-      <c r="B129">
-        <v>5</v>
+          <t>rev-381a9c12-9508-c49c-ce9c-9773ca107a81</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Titel: alle lecker, Text: alle lecker</t>
+          <t>Alles tip top</t>
         </is>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129">
-        <v>0</v>
-      </c>
-      <c r="I129">
         <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>rev-747851bf-b82a-4a35-b5f1-a11b15f994c4</t>
-        </is>
-      </c>
-      <c r="B130">
-        <v>5</v>
+          <t>rev-885fbc6a-874e-4c97-8099-a3a6e72d0a0a</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Titel: Gerne wieder, Text: Gerne wieder</t>
+          <t>Essen ist nach wie vor, aller ehren wert. Werde garantiert, nächste Monat wieder bestellen. Klasse</t>
         </is>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130">
-        <v>0</v>
-      </c>
-      <c r="I130">
         <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rev-38887799-2973-4f32-a589-724aa6cfb141</t>
-        </is>
-      </c>
-      <c r="B131">
-        <v>5</v>
+          <t>rev-cb6ea949-159a-4e58-ad92-70aad8eff378</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung, Text: Schnelle Lieferung, alles gut verpackt. Das Essen schmeckt super 👍</t>
+          <t>Schnelle Lieferung, Top verpackt, super lecker!!</t>
         </is>
       </c>
       <c r="D131">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H131">
-        <v>3.75</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>rev-761f464a-4ff1-4db8-9084-aa801293244f</t>
-        </is>
-      </c>
-      <c r="B132">
-        <v>3</v>
+          <t>rev-0c70468b-e3e6-4af6-bfc7-9be7a2347ab0</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Titel: Habe keinen Tiefkühlschrank somit ab…, Text: Habe keinen Tiefkühlschrank somit ab zwoten Tag ungenießbar</t>
+          <t>Alle Menüs sind sehr lecker, wie frisch gekocht , ich möchte HOFMANNs unbedingt weiter empfehlen . 2 Tage nach der Bestellung wurden die Menüs geliefert, bisher gab es nur 1x Probleme- das lag aber an DHL und HOFMANNs hat sofort eine neue Lieferung veranlasst. Die Kommunikation mit HOFMANNs ist vorbildlich.</t>
         </is>
       </c>
       <c r="D132">
         <v>2</v>
       </c>
       <c r="E132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132">
         <v>2</v>
       </c>
       <c r="H132">
-        <v>3.75</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rev-a6af669f-1cdf-fd16-9552-d183ca997c5d</t>
-        </is>
-      </c>
-      <c r="B133">
-        <v>5</v>
+          <t>rev-be2694ef-b199-4a91-aacf-0f0e9a217124</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Titel: Wie immer:, Text: Wie immer: Perfekter Service!</t>
+          <t>Eine neue Lieferung von 8 Gerichten in einer Kühlbox ist bei mir eingegangen. Die Qualität der Speisen ist bekanntermaßen hervorragend. Dabei bestellte ich durchweg umfängliche komplette Gerichte ("Sonntagsessen") mit Braten, Soße, Kartoffeln oder Bratkartoffeln oder Bällchen und Gemüse wie Rotkraut oder Bohnen. Diese Rezepte finde ich ausgefeilt und wohlschmeckend, sogar etwas luxuriös. Bratwürste und Nudeln/Spaghetti z. B. sind auch nicht schlecht, doch kann ich so etwas selbst zubereiten und spare den Aufwand eines gekühlten Versands.</t>
         </is>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -4830,268 +4673,262 @@
         <v>1</v>
       </c>
       <c r="G133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H133">
-        <v>0</v>
-      </c>
-      <c r="I133">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rev-2f196d23-342a-4cba-a011-acbf8ca91dd5</t>
-        </is>
-      </c>
-      <c r="B134">
-        <v>5</v>
+          <t>rev-eb5ccbcb-f533-c032-b02d-547d30004a92</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Titel: Alles top!, Text: Alles top!</t>
+          <t>Alles gut</t>
         </is>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H134">
-        <v>0</v>
-      </c>
-      <c r="I134">
         <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>rev-ad313a79-08e6-491d-a914-fef5be96d382</t>
-        </is>
-      </c>
-      <c r="B135">
-        <v>5</v>
+          <t>rev-6bc087f4-20ee-49a2-bee5-af3d4c2c6934</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Titel: Habe schon viele Essen ausprobiert, Text: Habe schon viele Essen ausprobiert, alle waren sehr gut. Immer pünktlich geliefert.</t>
+          <t xml:space="preserve">_x000D_
+Können es nur empfehlen._x000D_
+Schnelle und perfekte Lieferung. _x000D_
+Essen ist sehr gut._x000D_
+</t>
         </is>
       </c>
       <c r="D135">
         <v>2</v>
       </c>
       <c r="E135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H135">
-        <v>2.5</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rev-12e2d69a-4ff4-4573-9df2-48173ac0a66b</t>
-        </is>
-      </c>
-      <c r="B136">
-        <v>5</v>
+          <t>rev-f244b095-17cb-4cf3-9a64-ef3a17814399</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Titel: schmeckt gut, Text: schmeckt gut, schnelle lieferung</t>
+          <t>32 Gerichte am Fr. den 30.6.23 zum Wunschtermin am Di. den 4.7.23 bestellt. Es erfolgte keine Lieferung. Mehrmalige Anruf- und Email Kontaktversuche beben unbeantwortet. Dann kam am Mi. den 5.7. endlich eine Nachricht, daß am Fr. den 7.7. geliefert werden sollte. Leider Abermals Fehlanzeige. Abgesehen davon, daß wir täglich in Bereitstellung Zuhause sein mußten und zeitlich wegen der zu erwartenden Lieferung gebunden waren, finden wir diese Vorgehendsweise der Firma, in geschmeichelte Aussage, unerhört. Hoffen, daß  die Ware doch noch und vor allen Dingen, was auch nicht immer der Fall war, Tiefgefroren und noch nicht mit aufgelösten Trockeneisbeuteln und mit verbindlicher Vorankündigung, bei uns eintrifft.</t>
         </is>
       </c>
       <c r="D136">
         <v>2</v>
       </c>
       <c r="E136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136">
         <v>1</v>
       </c>
       <c r="G136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H136">
-        <v>1.25</v>
-      </c>
-      <c r="I136">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rev-7dd363a1-c152-4276-8cf5-2c749d95575b</t>
-        </is>
-      </c>
-      <c r="B137">
-        <v>5</v>
+          <t>rev-659479cd-dd96-4436-816c-6bf1890ea9df</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung und sehr leckere…, Text: Schnelle Lieferung und sehr leckere Gerichte</t>
+          <t>Alles</t>
         </is>
       </c>
       <c r="D137">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H137">
-        <v>1.25</v>
-      </c>
-      <c r="I137">
         <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>rev-6524ba71-22ff-44a8-a193-6acec2e0331c</t>
-        </is>
-      </c>
-      <c r="B138">
-        <v>5</v>
+          <t>rev-b9d514af-a14f-4004-81f9-6228ebff3ef4</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Titel: Alles super, Text: Alles super</t>
+          <t>Ich habe Hofmann Menü bereits vor über 20 Jahren kennengelernt. Damals belieferten sie eine große Hamburger Sparkasse. Das Essen war damals bereits lecker und ich freute mich um so mehr, als ich merkte, dass auch nun Privatpersonen online bestellen können. Meine Lieblingsgerichte gibt es zum großen Teil noch immer und ich freue mich darauf, meinen Kindern ein schnelles Mittagessen nach der Schule zubereiten zu können, wenn ich es selber zeitlich nicht schaffen kann. Die Lieferung erfolgte prompt und alle Gerichte waren selbstverständlich noch tiefgefroren.</t>
         </is>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>rev-12289de5-7065-4719-b3f5-eb5d44f1d33a</t>
-        </is>
-      </c>
-      <c r="B139">
-        <v>5</v>
+          <t>rev-ad82a69a-fbc5-450e-a182-f17b534d36c0</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Titel: Sehr gutes Essen, Text: Sehr gutes Essen, die Kommunikation mit dem Kundenservice ist sehr gut! Ich kann Hofmanns nur weiterempfehlen!</t>
+          <t>Lieferung ging sehr schnell. Essen war für meine Oma. Sie ist total begeistert. Bis jetzt hat ihr alles geschmeckt und sie sagt, es war super gewürzt und man merkt, es ist mit Liebe gemacht. Ich habe lange nach einer Alternative für „Essen auf Rädern“ für meine Oma gesucht und endlich Gerichte gefunden die schmecken. Wir bestellen auf jeden Fall wieder. Einfach nur top.</t>
         </is>
       </c>
       <c r="D139">
         <v>2</v>
       </c>
       <c r="E139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139">
         <v>2</v>
       </c>
       <c r="H139">
-        <v>2.5</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>rev-d0d49896-2648-4345-8234-7721e47f984f</t>
-        </is>
-      </c>
-      <c r="B140">
-        <v>5</v>
+          <t>rev-1f993e75-d560-4770-810f-a488e0c247a0</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Titel: Habe schon einige  Fertiggerichte ausprobiert, Text: Habe schon einige  Fertiggerichte ausprobiert,und muß sagen ihreGerichte_x000D__x000D_
-schmecken sehr gut. Die Auswahl der Gerichte  die zur Verfügung stehen ist sehr groß. Alles gut gewürzt und sehr schmackhaft. Auch der Preis ist in Ordnung._x000D__x000D_
-Von mir Daumen hoch, einfach prima.</t>
+          <t>Die Gerichte schmecken bisher sehr gut, die Menge ist für mich auch ausreichend. Aber mir gefallen die Zuckerzusätze(Dextrose) nicht bzw. ich vertrage sie nicht. Ich merke das im Bauch. Für andere Leute die damit keine Probleme haben, sind die Gerichte top.</t>
         </is>
       </c>
       <c r="D140">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140">
         <v>1</v>
       </c>
       <c r="G140">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H140">
-        <v>5</v>
-      </c>
-      <c r="I140">
         <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rev-7977ad46-4414-4a03-9b11-888260e45a6c</t>
-        </is>
-      </c>
-      <c r="B141">
-        <v>5</v>
+          <t>rev-55ae7418-39f5-4574-9db6-8475d3b12a8a</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Ich habe erst 2 Gerichte probiert-…, Text: Ich habe erst 2 Gerichte probiert- waren so weit ganz gut. Ausgewogen gewürzt und reichliche Portionen.  Die Kartoffel bei der Pfefferfrikadelle waren zu weich und etwas wässrig . Ich hoffe,  dass die anderen Gerichte durch das Aufwärmen nicht ihre Qualität einbüßen. Sie sind ohne großen Aufwand zuzubereiten. _x000D__x000D_
-</t>
+          <t>Am besten gefällt mir, dass man jetzt den Liefertermin wählen kann und nicht rechnen und bangen muss, dass das Paket doch nicht dann kommt, wann man eigentlich wollte. Ist in Single-Haushalten halt komplizierter._x000D_
+Die Portionsgrößen sind super, bitte nicht verkleinern.</t>
         </is>
       </c>
       <c r="D141">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E141">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -5100,521 +4937,508 @@
         <v>2</v>
       </c>
       <c r="H141">
-        <v>5</v>
-      </c>
-      <c r="I141">
         <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>rev-9c437bf9-b9a7-40a4-a318-6199caeabd5b</t>
-        </is>
-      </c>
-      <c r="B142">
-        <v>5</v>
+          <t>rev-00b87fde-7478-4529-b8ab-b50223e57946</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Titel: Bitte den zugesagten Liefertermin…, Text: Bitte den zugesagten Liefertermin einhalten</t>
+          <t>Alles super gelaufen wie immer</t>
         </is>
       </c>
       <c r="D142">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F142">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142">
-        <v>3.75</v>
-      </c>
-      <c r="I142">
         <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rev-923d0d0c-df49-4fb9-80a9-27d4c699e8a8</t>
-        </is>
-      </c>
-      <c r="B143">
-        <v>4</v>
+          <t>rev-49873335-2eb9-43b3-aeb6-802b68c2c836</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Titel: Leider kommt die Ware nicht pünktlich, Text: Leider kommt die Ware nicht pünktlich. Da ist mir jetzt schon das 2. Mail passiert._x000D__x000D_
-Das Essen ist sehr gut und hoffentlich nach der verspäteten Anlieferung noch in Ordnung, denn das Eis war bereits geschmolzen.</t>
+          <t>Meine  Bestellung für  lieferung am 24 Juli   ist noch nicht angetroffen. Ich möchte  dringend wissen wann die  gekühlte Lieferung  kommt.</t>
         </is>
       </c>
       <c r="D143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G143">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>7.5</v>
-      </c>
-      <c r="I143">
         <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rev-fa7ce7cc-9a2f-72db-b5a1-d3caacd4142b</t>
-        </is>
-      </c>
-      <c r="B144">
-        <v>5</v>
+          <t>rev-e0e9a8b2-4034-4bc8-b80e-420eeeb5e326</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Titel: Alles sehr gut !, Text: Alles sehr gut !</t>
+          <t>Fleisch teilweise nicht genießbar, Zubereitungszeit dauert zu lange</t>
         </is>
       </c>
       <c r="D144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F144">
         <v>1</v>
       </c>
       <c r="G144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144">
-        <v>0</v>
-      </c>
-      <c r="I144">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>rev-05053173-4754-4372-9ac7-be7304947a9a</t>
-        </is>
-      </c>
-      <c r="B145">
-        <v>5</v>
+          <t>rev-2e519b78-995b-3ebf-58dc-4bd038ba507c</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Titel: Alles perfekt!, Text: Alles perfekt!! danke</t>
+          <t>alles bestens</t>
         </is>
       </c>
       <c r="D145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>0</v>
-      </c>
-      <c r="I145">
         <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>rev-f5819776-e6af-4bce-9065-4f1d94e2145a</t>
-        </is>
-      </c>
-      <c r="B146">
-        <v>5</v>
+          <t>rev-4ea0b203-8f07-318f-5a58-8ee249505ec8</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Titel: Sehr gute Produkte außer die Verpackung…, Text: Sehr gute Produkte außer die Verpackung ist nicht so gut wen die war ankommt sind ein paar Schal offen</t>
+          <t>Hat alles sehr gut und schnell geklappt.</t>
         </is>
       </c>
       <c r="D146">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E146">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H146">
-        <v>3.75</v>
-      </c>
-      <c r="I146">
         <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>rev-90b2f6fb-2de1-435a-8307-f7594d3bbde9</t>
-        </is>
-      </c>
-      <c r="B147">
-        <v>5</v>
+          <t>rev-caab441b-a556-549a-78db-166ef919b639</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Titel: Superschneller Versand, Text: Superschneller Versand, top Qualität. Gerne wieder.</t>
+          <t>Hat alles super geklappt! Geschmacklich wirklich gut!</t>
         </is>
       </c>
       <c r="D147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147">
         <v>1</v>
       </c>
       <c r="H147">
-        <v>1.25</v>
-      </c>
-      <c r="I147">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>rev-b158575b-92ed-4735-a592-e27d7464b0e0</t>
-        </is>
-      </c>
-      <c r="B148">
-        <v>5</v>
+          <t>rev-aeebb11e-98bd-4383-8a37-696459bacfa1</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Wie immer alles perfekt, Text: Wie immer alles perfekt_x000D__x000D_
-</t>
+          <t>Das Paket ist nicht  da.</t>
         </is>
       </c>
       <c r="D148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148">
         <v>1</v>
       </c>
       <c r="F148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H148">
-        <v>0</v>
-      </c>
-      <c r="I148">
         <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>rev-26005969-2836-49b1-9e3f-7ccfda3f0ceb</t>
-        </is>
-      </c>
-      <c r="B149">
-        <v>5</v>
+          <t>rev-0620d547-79bd-4672-990d-83daf614be05</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Titel: Wie immer Top, Text: Wie immer Top. Schnelle Lieferung und alles im Super Zustand.</t>
+          <t>Sehr gut gemacht gut angekommen und alles bestens gelaufen</t>
         </is>
       </c>
       <c r="D149">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>2.5</v>
-      </c>
-      <c r="I149">
         <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>rev-39e8771f-e9b1-46fb-969d-4c8eaec48d83</t>
-        </is>
-      </c>
-      <c r="B150">
-        <v>5</v>
+          <t>rev-a0376b5e-ddf1-41cb-99ce-a6e45e1731ac</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Titel: Mir gefällt, Text: Mir gefällt, wie einfach es ist, die passenden Menüs zusammen zu stellen. Der Bestellvorgang ist so, wie man es sich von einem online-Shop wünscht. Werde auf jeden Fall wieder Menüs bestellen, weil sie auch sehr gut sind.</t>
+          <t>Sehr gutes Essen! Uns schmeckt es bestens und der Versand verläuft blitzschnell und reibungslos! Wir haben nichts zu beanstanden und sind froh, solch eine tolle Verköstigung gefunden zu haben. Wir sind treue Stammkunden und können Hofmanns absolut weiterempfehlen!</t>
         </is>
       </c>
       <c r="D150">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H150">
-        <v>5</v>
-      </c>
-      <c r="I150">
         <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>rev-2d319466-be90-485d-b6b4-7b11c9db422b</t>
-        </is>
-      </c>
-      <c r="B151">
-        <v>5</v>
+          <t>rev-17af33ba-3215-4cdc-ad48-52bb2ed31b17</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Titel: Korrekte Lieferung,, Text: Korrekte Lieferung,</t>
+          <t>Das Essen ist super lecker, schmeckt wie aus dem Restaurant und ist eine tolle Zeitersparnis. Wünschenswert wären noch ein paar mehr glutenfreie Gerichte zur Auswahl.</t>
         </is>
       </c>
       <c r="D151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151">
         <v>1</v>
       </c>
       <c r="G151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H151">
-        <v>0</v>
-      </c>
-      <c r="I151">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>rev-b3fd4571-5662-430e-be6a-fbe30b84bccb</t>
-        </is>
-      </c>
-      <c r="B152">
-        <v>5</v>
+          <t>rev-578b1578-63d3-486d-8a19-3718fc9b7c8f</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Titel: Die Lieferung kam ein Tag später als…, Text: Die Lieferung kam ein Tag später als angekündigt,dadurch war das Trockeneis total leer und fast warm. Vermutlich wegen Weihnachtstress.</t>
+          <t>Nach sehr schlechten Erfahrungen bei meiner ersten Bestellung hat es nun bei meiner zweiten Bestellung sehr gut geklappt. Sehr loben muss ich auch den Kundendienst von Hofmanns. Nachdem bei der ersten Lieferung alles aufgetaut ankam, hat man sich sofort entschuldigt und ein Rabattangebot für eine weitere Lieferung angeboten. Auch wurde der Kaufbetrag sofort und unkompliziert zurück erstattet. Das Essen ist sehr schmackhaft und man merkt, dass es wirklich handwerklich hergestellt ist. Die Portionen sind auch ausreichend groß. Achillesferse dieses Konzeptes ist und bleibt das Lieferkonzept. Wenn der Lieferdienstleister gut arbeitet und die Ware innerhalb von 24 Std. den Kunden erreicht, reicht die Kühlkapazität des Trockeneises gerade so aus. Dauert es länger, wird es kritisch.</t>
         </is>
       </c>
       <c r="D152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F152">
         <v>1</v>
       </c>
       <c r="G152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H152">
-        <v>7.5</v>
-      </c>
-      <c r="I152">
         <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>rev-a9ef1d94-9001-4b38-8940-9c0145e1c6bc</t>
-        </is>
-      </c>
-      <c r="B153">
-        <v>5</v>
+          <t>rev-1c7d220f-edb1-495e-8890-0b52d1e84986</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Titel: Gutes Essen, Text: Gutes Essen, gute Lieferung.</t>
+          <t>alles perfekt wie immer, besten Dank.</t>
         </is>
       </c>
       <c r="D153">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>1.25</v>
-      </c>
-      <c r="I153">
         <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>rev-232b9e08-edb9-452b-a9be-f56f06bb3d73</t>
-        </is>
-      </c>
-      <c r="B154">
-        <v>5</v>
+          <t>rev-486dffed-0576-46ea-a2a9-61c4268d6998</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Titel: Alles gut wie immer., Text: Alles gut wie immer.</t>
+          <t>Schnelle Lieferung und sehr lecker alles,kann man wirklich weiter empfehlen.</t>
         </is>
       </c>
       <c r="D154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154">
         <v>1</v>
       </c>
       <c r="H154">
-        <v>0</v>
-      </c>
-      <c r="I154">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>rev-08dd6ea4-0567-4145-b4d1-45a3bf2bff12</t>
-        </is>
-      </c>
-      <c r="B155">
-        <v>5</v>
+          <t>rev-e2db2b62-d8af-4a12-ae1c-7e05689c5dae</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Titel: Sehr guter Geschmack und vor Allem…, Text: Sehr guter Geschmack und vor Allem reichlich Soße. Super!</t>
+          <t xml:space="preserve">Gleich mit der besten Benotung zu starten, ist nicht mein Ding. Aber meine Bestellungen haben mit sehr gut geschmeckt  _x000D_
+</t>
         </is>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G155">
         <v>1</v>
       </c>
       <c r="H155">
-        <v>1.25</v>
-      </c>
-      <c r="I155">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>rev-139edba3-96b6-4924-9931-dfa417ae8789</t>
-        </is>
-      </c>
-      <c r="B156">
-        <v>5</v>
+          <t>rev-35ee6c1b-dec6-42bb-a8b7-156ecf019b33</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Titel: Leckere Gerichte, Text: Leckere Gerichte, schnell zubereitet. Preis Leistungsverhältnis passt. Lieferung schnell.</t>
+          <t>Lieferung fast eine Woche. Dies ist etwas sehr lang</t>
         </is>
       </c>
       <c r="D156">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E156">
         <v>1</v>
       </c>
       <c r="F156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H156">
-        <v>3.75</v>
-      </c>
-      <c r="I156">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>rev-231740c2-7bb9-4bfe-9b8b-ac8cd657788b</t>
-        </is>
-      </c>
-      <c r="B157">
-        <v>5</v>
+          <t>rev-3973dcfd-0fe2-4b5c-a614-cfa146334599</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Titel: Gute Qualität,schnelle Lieferung, Text: Gute Qualität,schnelle Lieferung</t>
+          <t>Ich bin begeistert von den tollen Gerichten,besonders der Sauerbraten ist mein Lieblingsgericht._x000D_
+Ebenso Bandnudeln mit Lachs,wird nicht meine letzte Bestellung sein._x000D_
+Einzig beim Jägerschnitzel wäre mir persönlich Kartoffelmus lieber statt Pommes._x000D_
+_x000D_
+MfG E.Kunze</t>
         </is>
       </c>
       <c r="D157">
@@ -5630,123 +5454,119 @@
         <v>1</v>
       </c>
       <c r="H157">
-        <v>1.25</v>
-      </c>
-      <c r="I157">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>rev-65318fbc-0148-41ad-9bef-0b828733fd3a</t>
-        </is>
-      </c>
-      <c r="B158">
-        <v>5</v>
+          <t>rev-c1ea4fdf-6cbc-4abb-a84a-9d68acdc6b61</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Titel: Alles sehr leckere Gerichte 👍👍👍👍👍🖖, Text: Alles sehr leckere Gerichte 👍👍👍👍👍🖖</t>
+          <t>Einfaches Bestellverfahren, guter Kundeservice, nette Hotline, gute Qualität des Essens</t>
         </is>
       </c>
       <c r="D158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158">
         <v>1</v>
       </c>
       <c r="H158">
-        <v>0</v>
-      </c>
-      <c r="I158">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rev-2dd05c1d-56f2-4f97-a117-4c251b28cc5c</t>
-        </is>
-      </c>
-      <c r="B159">
-        <v>4</v>
+          <t>rev-1de262f5-b073-4be8-a90e-2a7d7c5885b6</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Titel: Die Preise dürfen nicht weiter steigen, Text: Die Preise dürfen nicht weiter steigen, sonst stimmen Qualität und Größe der Portionen, insbesondere der Fleischanteil, nicht mehr.</t>
+          <t>Hatte noch nicht die Zeit alles zu testen.</t>
         </is>
       </c>
       <c r="D159">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F159">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>5</v>
-      </c>
-      <c r="I159">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rev-3c738500-72b9-44d6-9f4d-71259cc3c208</t>
-        </is>
-      </c>
-      <c r="B160">
-        <v>5</v>
+          <t>rev-e1b14d6d-6fbd-4ab8-97b8-68e0bed76484</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Titel: Top Service und leckeres Essen, Text: große Auswahl, nachhaltige Verpackung, schnelle Lieferung</t>
+          <t>Gute Qualität. Bei großer Bestellung könnte man den Rabatt etwas höher machen, z.B. anstatt 10 % bei einem Abo zwischen 15-20 %.</t>
         </is>
       </c>
       <c r="D160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G160">
         <v>1</v>
       </c>
       <c r="H160">
-        <v>2.5</v>
-      </c>
-      <c r="I160">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rev-4e0f001f-0340-419b-8da5-4675e1da255a</t>
-        </is>
-      </c>
-      <c r="B161">
-        <v>5</v>
+          <t>rev-aaf56595-ff95-4af7-9d7a-635f2a17aa15</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Titel: Schnelle und einfache Abwicklung der…, Text: Schnelle und einfache Abwicklung der Bestellung bis zur Auslieferung</t>
+          <t>Die Verpackung-nachhaltig,trotzdem alles gefroren angekommen.Die Erklärung zum entsorgen-positiv.</t>
         </is>
       </c>
       <c r="D161">
@@ -5756,331 +5576,325 @@
         <v>1</v>
       </c>
       <c r="F161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161">
         <v>1</v>
       </c>
       <c r="H161">
-        <v>1.25</v>
-      </c>
-      <c r="I161">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>rev-833ed497-a76f-459c-8289-9923650e38f6</t>
-        </is>
-      </c>
-      <c r="B162">
-        <v>5</v>
+          <t>rev-610aafd5-de30-4188-b9e2-6d0eee56de44</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Titel: Nicht viel, Text: Nicht viel. Alles super</t>
+          <t>Vielleicht noch deutlicher und farbiger für alte Menschen die Erkennung ob eine Lasche vorher abgetrennt werden muss oder nicht. Wenn nichts abgetrennt werden muss, dann sollte deutlich drauf stehen: dieses Gericht ungeöffnet in den Backofen.</t>
         </is>
       </c>
       <c r="D162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H162">
-        <v>0</v>
-      </c>
-      <c r="I162">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>rev-9ff3827f-ec83-47b4-b76b-4c8f59b9ddb1</t>
-        </is>
-      </c>
-      <c r="B163">
-        <v>5</v>
+          <t>rev-b46c26c4-0702-4568-b606-b95290b26eb5</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Titel: TOP-Menüs gebe gerne 5* 😊, Text: Danke, wieder für die schnelle Zustellung! Diese Menüs sind sehr lecker, und vielfältig! _x000D__x000D_
-Zudem das EIS; mein Favorit: Praline-Nuss! _x000D__x000D_
-Zudem finde ich es gut, diese Aufklärung/Entsorgung über das Packmaterial und, die Rezepte_x000D__x000D_
-Gerne wieder!</t>
+          <t xml:space="preserve">Besser machen geht nicht._x000D_
+Besser schmecken schon gar nicht._x000D_
+Also 5 Sterne._x000D_
+</t>
         </is>
       </c>
       <c r="D163">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>5</v>
-      </c>
-      <c r="I163">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>rev-61addb95-ab82-4b64-a545-3e8cc76b7e24</t>
-        </is>
-      </c>
-      <c r="B164">
-        <v>1</v>
+          <t>rev-c1de7443-a3f9-4d53-800b-dffab2190211</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Titel: Die Lieferung ist nicht angekommen, Text: Die Lieferung ist nicht angekommen. Es gibt weder eine Information mit eine Begründung noch eine Statusmeldung. Angeblich hängt die Lieferung seit Gestern Nachmittag in Würzburg bei DHL fest.</t>
+          <t>Sehr schnelle Lieferung</t>
         </is>
       </c>
       <c r="D164">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E164">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H164">
-        <v>7.5</v>
-      </c>
-      <c r="I164">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>rev-369bce87-0fc5-48f1-be13-2a4899fea456</t>
-        </is>
-      </c>
-      <c r="B165">
-        <v>5</v>
+          <t>rev-93745a60-ee29-4614-ab39-deefc59f6074</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung, Text: Schnelle Lieferung, leckere Gerichte, große Auswahl,  Preis/Leistungsverhältnis stimmt_x000D__x000D_
-Gerne wieder</t>
+          <t>:_x000D_
+"Ich bin mit den Gerichten bisher zufrieden gewesen, bis auf die Tatsache, dass einige Gerichte nach vorschriftsmäßiger Zubereitung aus dem Ofen nicht ganz aufgetaut waren. Was ich feststellen konnte, ist, dass die Nudelgerichte aus der Pasta-Box alle perfekt aufgewärmt waren. Das liegt wohl daran, dass Nudeln dünner sind. Insgesamt schmeckten alle Gerichte sehr gut, aber die Pasta-Gerichte sind das Highlight."_x000D_
+_x000D_
+ * "</t>
         </is>
       </c>
       <c r="D165">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E165">
         <v>1</v>
       </c>
       <c r="F165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165">
         <v>2</v>
       </c>
       <c r="H165">
-        <v>3.75</v>
-      </c>
-      <c r="I165">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>rev-548ef5c9-a066-4ffc-b180-c9b1486f9a0d</t>
-        </is>
-      </c>
-      <c r="B166">
-        <v>4</v>
+          <t>rev-6554a50f-c023-3040-f136-3d97cf9409ae</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Titel: Wie bestellt,so geliefert.Zu wenig Soße…, Text: Wie bestellt,so geliefert.Zu wenig Soße bei manchen Gerichten.</t>
+          <t>wie immer: schnelle und lorrekte Lieferung</t>
         </is>
       </c>
       <c r="D166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F166">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>3.75</v>
-      </c>
-      <c r="I166">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>rev-2f3fab42-3e39-4689-9f57-ee2695ba4019</t>
-        </is>
-      </c>
-      <c r="B167">
-        <v>5</v>
+          <t>rev-51cf265b-501d-497d-9b4e-87fa57422520</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Titel: schnelle Lieferung und leckeres Essen, Text: Sehr schnelle Lieferung, super verpackt und sehr sehr leckeres Essen</t>
+          <t>Alles passt bisher und schmeckt hervorragend......Lieferung perfekt ökologisch verpackt......wir sind begeistert  !!! Kann man sehr empfehlen !!!</t>
         </is>
       </c>
       <c r="D167">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167">
         <v>1</v>
       </c>
       <c r="H167">
-        <v>2.5</v>
-      </c>
-      <c r="I167">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>rev-44db66df-0b1d-4642-aeac-de94974cdc57</t>
-        </is>
-      </c>
-      <c r="B168">
-        <v>5</v>
+          <t>rev-4d08a40b-30ca-46e0-a93a-a1185ac636f3</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Titel: Danke war alles gut, Text: Danke war alles gut</t>
+          <t>Alles gut</t>
         </is>
       </c>
       <c r="D168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168">
-        <v>0</v>
-      </c>
-      <c r="I168">
         <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>rev-27969095-dfe2-4822-8c0e-6e95b3d1b05d</t>
-        </is>
-      </c>
-      <c r="B169">
-        <v>3</v>
+          <t>rev-7042fbb5-65f5-4c79-acb9-f2a7ece2a4b3</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Titel: 1, Text: 1. Essen hat gut geschmeckt. Leider wurde der angegebene Liefertermin nicht eingehalten, sondern einfach 1 Tag später geliefert. Etwas blöd, wenn man es so plant, dass man Home-Office hat, einen Tag später aber im Büro sitzt, wenn die Liefertung bei Nachbarn abgegeben wird und natürlich nicht direkt ins Eisfach wandert.</t>
+          <t>Schnelle Lieferung wenig Müll Essen ist lecker nicht zerkocht und einfach in der Zubereitung</t>
         </is>
       </c>
       <c r="D169">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E169">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F169">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G169">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H169">
-        <v>8.75</v>
-      </c>
-      <c r="I169">
         <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>rev-8e1d1baa-863d-4f68-927e-c76dc50f2788</t>
-        </is>
-      </c>
-      <c r="B170">
-        <v>5</v>
+          <t>rev-6d299557-5e0c-442a-be86-ebbd2a1443ac</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Titel: Sehr gut, Text: Sehr gut</t>
+          <t>Hochwertige Qualität und ausgezeichneter Geschmack erleichtern mir meinen eigenen Alltag für eine weitere selbstbestimmte Lebensführung trotz Pflegegrad und Schwerbehinderung._x000D_
+_x000D_
+Einzig die Zustellung mit DHL-Express ist weniger erfreulich, weil der Fahrer nicht an die geschäftlichen Bestimmungen der DHL hält und alle Nachfragen leider nicht zu einem Erfolg führt. Doch ist dies ein Problem der DHL und weniger der Firma Hofmann zuzuschreiben.</t>
         </is>
       </c>
       <c r="D170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H170">
-        <v>0</v>
-      </c>
-      <c r="I170">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>rev-02d76baf-be4c-4e03-9713-7b6cf8fd9281</t>
-        </is>
-      </c>
-      <c r="B171">
-        <v>5</v>
+          <t>rev-9141477f-9abb-4610-baad-3c0a901e1729</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Titel: Schmeckt immer hervorragend, Text: Schmeckt immer hervorragend</t>
+          <t>Bis jetzt alles was ich habe probiert gut geschmeckt auser bei einem menu gekochte kartoffeln paar stuck war nicht so gut,aber bei kartoffeln kann so vorkommen.Sonst alles super.Danke</t>
         </is>
       </c>
       <c r="D171">
@@ -6090,705 +5904,685 @@
         <v>1</v>
       </c>
       <c r="F171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G171">
         <v>1</v>
       </c>
       <c r="H171">
-        <v>0</v>
-      </c>
-      <c r="I171">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>rev-cf007b12-dfac-4462-a969-feec7f0fa23a</t>
-        </is>
-      </c>
-      <c r="B172">
-        <v>5</v>
+          <t>rev-ab667950-7ae5-4b4e-8702-fb3f7bbc7a6d</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Titel: Das beste Mikrowellen-Fertigessen, Text: Das beste Mikrowellen-Fertigessen, das ich je hatte. Selbst nach der Zubereitung in der Mikrowelle ist das Gemüse noch knackig und das Fleisch noch saftig. Insgesamt sehr leckere und vielseitige Menüs.</t>
+          <t>Bin rundum zufrieden mit der Lieferung</t>
         </is>
       </c>
       <c r="D172">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G172">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H172">
-        <v>5</v>
-      </c>
-      <c r="I172">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>rev-ce27e891-542c-4c25-8f02-f4dce3ff9914</t>
-        </is>
-      </c>
-      <c r="B173">
-        <v>4</v>
+          <t>rev-dac624c5-38fc-4c6b-be2f-419f6db8279d</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Titel: Vorschlag, Text: Vorschlag_x000D__x000D_
-_x000D__x000D_
-Bei den Rindsrouladen statt Salzkartoffeln  Kartoffelknödel._x000D__x000D_
-Sauerbraten ist perfekt!!</t>
+          <t>Rasche Lieferung. Vielleicht noch mehr Angebote - Piccolino, dann kleinere Portionen evtl. auch etwas kostengünstiger, für Senioren. Ansonsten passt soweit alles.</t>
         </is>
       </c>
       <c r="D173">
         <v>2</v>
       </c>
       <c r="E173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H173">
-        <v>5</v>
-      </c>
-      <c r="I173">
         <v>1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>rev-14c96b16-c8b3-4be6-85d6-87838d56c3e6</t>
-        </is>
-      </c>
-      <c r="B174">
-        <v>5</v>
+          <t>rev-efae0ce8-9190-410d-867c-c73c5ccbf703</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Titel: Immer wieder gern …Wiederholungstäter…, Text: Immer wieder gern …Wiederholungstäter und das gern. Hatte bislang keinen Anlass zur Klage, war alles lecker!</t>
+          <t>Zwei Packungen nicht sauber verschweißt und am Rand offen. Wurde sofort erstattet. Somit alles gut.</t>
         </is>
       </c>
       <c r="D174">
         <v>2</v>
       </c>
       <c r="E174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H174">
-        <v>2.5</v>
-      </c>
-      <c r="I174">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>rev-134c6e18-76cd-40c0-acf1-95e5a2132bed</t>
-        </is>
-      </c>
-      <c r="B175">
-        <v>5</v>
+          <t>rev-34a36c20-6d27-4885-9d97-d08b07f2bca2</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Titel: Grundsätzlich alles super ..., Text: Grundsätzlich alles super, dass Essen ist absolut nach meinem Geschmack und für mich sehr gut gewürzt. Lediglich bei der Lieferung kommen die Kühlpads an ihre Grenzen. Ich werde weiter bei Hofmanns bestellen ...</t>
+          <t>alles super</t>
         </is>
       </c>
       <c r="D175">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E175">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F175">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G175">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H175">
-        <v>7.5</v>
-      </c>
-      <c r="I175">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>rev-0e5d5b92-0e79-49bf-a2ad-742fc67d4cc4</t>
-        </is>
-      </c>
-      <c r="B176">
-        <v>5</v>
+          <t>rev-0ab1b8ec-b4da-441e-9a45-3409f8c155dc</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Schneller Lieferung,gutes Essen,und…, Text: Schneller Lieferung,gutes Essen,und ausreichend große Portionen _x000D__x000D_
-</t>
+          <t>Qualität und Geschmack gut bis sehr gut. _x000D_
+Versand top: Sonntagabends bestellt, Mittwochmittags geliefert. _x000D_
+Ware ist gut gekühlt verpackt - auch bei diesen sommerlich heissen Temperaturen. _x000D_
+Bisher alles tipptopp.</t>
         </is>
       </c>
       <c r="D176">
         <v>2</v>
       </c>
       <c r="E176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G176">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H176">
-        <v>1.25</v>
-      </c>
-      <c r="I176">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>rev-e8b5e878-5ccd-4435-9f6e-e2db803b40bf</t>
-        </is>
-      </c>
-      <c r="B177">
-        <v>5</v>
+          <t>rev-069a2a17-2cdc-40d5-9a6b-008a703d6adf</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung und gute Verpackung, Text: Schnelle Lieferung und gute Verpackung. Gute Qualität.</t>
+          <t>Jedes Essen war bis jetzt gut und ausreichend. Schnelle Lieferung, nur sehr viel Verpackung.</t>
         </is>
       </c>
       <c r="D177">
         <v>2</v>
       </c>
       <c r="E177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F177">
         <v>1</v>
       </c>
       <c r="G177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H177">
-        <v>2.5</v>
-      </c>
-      <c r="I177">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>rev-5263b1dd-63eb-4e01-9a53-7ea1f4e9448c</t>
-        </is>
-      </c>
-      <c r="B178">
-        <v>5</v>
+          <t>rev-9726acad-184a-4b93-9042-1f4533358a57</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung, Text: Schnelle Lieferung, leckere Menues. Hab sie bisher im Ofen mit Umluft erthitzt nach Angaben zum Heissluftverfahrem (45 min. 140°). Jetzt wurde in Internet  die Garzeit im Umluftofen eingestellt  60 min.bei 130°. _x000D__x000D_
-Ganz ehrlich, in meinem Ofen reichen mir die Angaben für Heissluftöfen völlig. Alles ist Heiß und gar.</t>
+          <t>Der Shop bietet eine gute Auswahl an Produkten. Lieferung ist immer pünktlich. Ich bin sehr zufrieden!</t>
         </is>
       </c>
       <c r="D178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G178">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H178">
-        <v>5</v>
-      </c>
-      <c r="I178">
         <v>1</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>rev-56711cbf-fa9c-4caf-b0ce-0b3dd123d89d</t>
-        </is>
-      </c>
-      <c r="B179">
-        <v>5</v>
+          <t>rev-1cbfe308-1f0d-4f9d-96d7-03d9258f9127</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Titel: alles in bester ordnung, Text: alles in bester ordnung</t>
+          <t>Sehr zuverlässig und Qualität sehr gut!</t>
         </is>
       </c>
       <c r="D179">
         <v>1</v>
       </c>
       <c r="E179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H179">
-        <v>0</v>
-      </c>
-      <c r="I179">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>rev-b9d514af-a14f-4004-81f9-6228ebff3ef4</t>
-        </is>
-      </c>
-      <c r="B180">
-        <v>5</v>
+          <t>rev-88b75173-aca0-4634-b0bd-7d8eb6e2a6e7</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Titel: Qualität zahlt sich eben aus, Text: Ich habe Hofmann Menü bereits vor über 20 Jahren kennengelernt. Damals belieferten sie eine große Hamburger Sparkasse. Das Essen war damals bereits lecker und ich freute mich um so mehr, als ich merkte, dass auch nun Privatpersonen online bestellen können. Meine Lieblingsgerichte gibt es zum großen Teil noch immer und ich freue mich darauf, meinen Kindern ein schnelles Mittagessen nach der Schule zubereiten zu können, wenn ich es selber zeitlich nicht schaffen kann. Die Lieferung erfolgte prompt und alle Gerichte waren selbstverständlich noch tiefgefroren.</t>
+          <t>Leckeres Essen, schnell geliefert und sehr nachhaltig verpackt. Immer wieder gerne 😊</t>
         </is>
       </c>
       <c r="D180">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G180">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H180">
-        <v>5</v>
-      </c>
-      <c r="I180">
         <v>1</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>rev-5c04d3eb-142d-4976-be49-590a5cdc6919</t>
-        </is>
-      </c>
-      <c r="B181">
-        <v>4</v>
+          <t>rev-3840ad46-f727-4041-9325-524cebc58a17</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Titel: Bessere Transparenz der Liefertage…, Text: Bessere Transparenz der Liefertage insbesondere im Vorfeld von Feiertagen.</t>
+          <t>Weiter so! Danke</t>
         </is>
       </c>
       <c r="D181">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F181">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H181">
-        <v>3.75</v>
-      </c>
-      <c r="I181">
         <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>rev-9e52be69-85d1-d28a-e9e8-bcee603100f1</t>
-        </is>
-      </c>
-      <c r="B182">
-        <v>5</v>
+          <t>rev-2485c9d1-beaf-4a49-a933-13a25539f910</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Titel: Sehr gut, Text: Sehr gut</t>
+          <t>Leckeres Essen, viel Abwechslung, Top Lieferung und ein klasse Kundendienst. 👍</t>
         </is>
       </c>
       <c r="D182">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182">
         <v>1</v>
       </c>
       <c r="H182">
-        <v>0</v>
-      </c>
-      <c r="I182">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>rev-73297405-ba07-4a12-b13b-6dd102be2f8a</t>
-        </is>
-      </c>
-      <c r="B183">
-        <v>5</v>
+          <t>rev-bfd830f2-c8c5-439d-b9be-ae3291afdd1f</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Titel: Schnelle Lieferung und ich bin immer hungrig :-), Text: Schnelle Lieferung und ich bin immer wieder erstaunt, wie gefroren das bei mir ankommt.    _x000D__x000D_
-Ich freue mich immer, wenn ich mir wieder ein neues Gericht aus dem Eisfach hole :-)</t>
+          <t xml:space="preserve">Immer wieder gute Gerichte. _x000D_
+</t>
         </is>
       </c>
       <c r="D183">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G183">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H183">
-        <v>5</v>
-      </c>
-      <c r="I183">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>rev-3f6be1ba-f523-4e51-b1e7-b1d24fdb4d5e</t>
-        </is>
-      </c>
-      <c r="B184">
-        <v>5</v>
+          <t>rev-f915a470-ef02-46ff-b4d3-1c5c8aad71d1</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Titel: Wie selbst gekocht, Text: Wie selbst gekocht, einfach lecker._x000D__x000D_
-_x000D__x000D_
-Lieferung am nächsten Tag, klasse.</t>
+          <t>Mit DHL alles top</t>
         </is>
       </c>
       <c r="D184">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E184">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F184">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G184">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H184">
-        <v>3.75</v>
-      </c>
-      <c r="I184">
         <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>rev-ba802199-e7ec-480e-8146-7018c7d3d92b</t>
-        </is>
-      </c>
-      <c r="B185">
-        <v>5</v>
+          <t>rev-9d29ba77-afb0-47a6-8655-6560cf497d04</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Titel: Lecker, Text: Lecker! Gute Verpackung. Beste Menübeschreibung. Leider nur ein Gericht in BIO-Qualität. Das ist aber wirklich schmackhaft. Danke! Ich habe einige "nicht-BIO"-Gerichte probiert und die waren richtig gut zu essen, "hochfein" würde mein seliger Großvater sagen. Danke an Hofmann. :-) Liebe Grüße. Klaus.</t>
+          <t>Bin zufrieden, jedenfalls besser als Essen im Krankenhaus. _x000D_
+Da ich momentan aus gesundheitlichen Gründen nicht selbst am Herd stehen kann, ist das eine große Erleichterung für mich.</t>
         </is>
       </c>
       <c r="D185">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E185">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G185">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H185">
-        <v>6.25</v>
-      </c>
-      <c r="I185">
         <v>1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>rev-09318f39-6f62-4a6d-b922-345206809a41</t>
-        </is>
-      </c>
-      <c r="B186">
-        <v>5</v>
+          <t>rev-a097f84b-c83c-4b12-bc07-3baa8f33c3fc</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Titel: Immer leckeres Essen, Text: Immer leckeres Essen, schnelle Lieferung und gute Qualität.</t>
+          <t>Das es immer pünktlich geliefert wird und es hervorragend schmeckt und das der Preis stimmt.</t>
         </is>
       </c>
       <c r="D186">
         <v>2</v>
       </c>
       <c r="E186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G186">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H186">
-        <v>2.5</v>
-      </c>
-      <c r="I186">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>rev-d42c2e74-accb-465d-9cc2-52cfd509c90c</t>
-        </is>
-      </c>
-      <c r="B187">
-        <v>1</v>
+          <t>rev-c9f75597-4dbf-484f-96a2-645073ac059b</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Titel: Versand verursacht unnötigen Stress, Text: Der Versand hat leider überhaupt nicht geklappt. Trotz extra getrennt angegebener Rechnungs- und Lieferadresse wurde an die Rechnungsadresse versandt. Und dann war es auch noch einen Tag länger unterwegs als ursprünglich geplant, wo man sich bei tiefgefrorenem Essen fragen musste, in welchem Zustand es ankommt.</t>
+          <t>alles perfekt wie immer.</t>
         </is>
       </c>
       <c r="D187">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E187">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H187">
-        <v>7.5</v>
-      </c>
-      <c r="I187">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>rev-c517420a-2188-43b0-9ccc-77fc13064f1e</t>
-        </is>
-      </c>
-      <c r="B188">
-        <v>5</v>
+          <t>rev-7cd51fdb-191c-4086-b94f-0f928895988f</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Titel: Schnell geliefert und wie immer bestes …, Text: Schnell geliefert und wie immer bestes  zufrieden mit dem Essen.</t>
+          <t xml:space="preserve">Schmeckt einfach _x000D_
+_x000D_
+</t>
         </is>
       </c>
       <c r="D188">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188">
-        <v>1.25</v>
-      </c>
-      <c r="I188">
         <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>rev-1b0026ef-d536-4a43-ab22-1f9552e3e76d</t>
-        </is>
-      </c>
-      <c r="B189">
-        <v>5</v>
+          <t>rev-ef2a0b34-9ad7-42f2-b5c6-d722579ef242</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Titel: Fertiggerichte, Text: Schnelle Lieferung in einer umweltfreundlichen Verpackung. Portionen sind reichlich bemessen, optisch gut angerichtet und geschmacklich hervorragend.</t>
+          <t>Guter und schneller Service. _x000D_
+Bei ( berechtigten ) Reklamationen schnelle und unkomplizierte Bearbeitung. _x000D_
+Das Essen ist in Ordnung, hat aber gegenüber der letzten Jahre etwas an Qualität eingebüßt.</t>
         </is>
       </c>
       <c r="D189">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E189">
         <v>1</v>
       </c>
       <c r="F189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G189">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H189">
-        <v>5</v>
-      </c>
-      <c r="I189">
         <v>1</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>rev-6596abdf-88b2-4c81-ba57-4bea837574d0</t>
-        </is>
-      </c>
-      <c r="B190">
-        <v>4</v>
+          <t>rev-f6976474-71f5-4daf-ab7e-f77c35bb30a0</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Titel: Es geht schnell und schmeckt OK, Text: Es geht schnell und schmeckt OK. Nur die Menge ist etwas klein.und etwas lieblos im tablett gelegt. Und bitte verschweißt eure Menüschalen besser und hatte schon zwei an der Seite abgelöste Schalendeckel.</t>
+          <t>Hofmann hat alles perfekt gemacht, wie immer. DHL hat letztendlich nur Ärger ausgelöst: die Lieferung kam 4 Std früher als per Mail mitgeteilt, da keiner da war, einfach beim Nachbar abgegeben, kein Hinweis für mich im Briefkasten, nur eine Mail „zugestellt „. Dann musste ich über etliche Bestätigungen u Wartezeiten am Telefon erfahren, welcher Nachbar meine Lieferung überhaupt hat. Ganz schlechter Partner von Hofmann</t>
         </is>
       </c>
       <c r="D190">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E190">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F190">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G190">
         <v>2</v>
       </c>
       <c r="H190">
-        <v>7.5</v>
-      </c>
-      <c r="I190">
         <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>rev-bdc78468-7ff4-49ce-9ec7-f9a95ad45468</t>
-        </is>
-      </c>
-      <c r="B191">
-        <v>5</v>
+          <t>rev-7aaf3b1d-9588-4b12-addb-32061e4b4e96</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Titel: Alles sehr lecker 😋, Text: Alles was ich bis jetzt gegessen habe...war sehr lecker 😋...und sehr gut abgeschmeckt...ich kann die Mahlzeiten nur Empfehlen...👍👍👍</t>
+          <t>Sehr leckeres Essen, Qualität ist sehr gut für ein TK Essen.</t>
         </is>
       </c>
       <c r="D191">
         <v>2</v>
       </c>
       <c r="E191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H191">
-        <v>2.5</v>
-      </c>
-      <c r="I191">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>rev-00e7b2af-a4e4-49fe-aabe-1a59cf52d95f</t>
-        </is>
-      </c>
-      <c r="B192">
-        <v>1</v>
+          <t>rev-f9e7d113-2bae-b798-e10b-7c22c8ea67a3</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Titel: Ich habe die Ware noch nicht erhalten!, Text: Ich habe die Ware noch nicht erhalten!</t>
+          <t>Die machen alle einen super Job das Essen ist super ich persönlich finde die Menge halt ein bisschen zu wenig</t>
         </is>
       </c>
       <c r="D192">
         <v>1</v>
       </c>
       <c r="E192">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F192">
         <v>1</v>
@@ -6797,299 +6591,285 @@
         <v>1</v>
       </c>
       <c r="H192">
-        <v>2.5</v>
-      </c>
-      <c r="I192">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>rev-0cc2430c-c6cd-4108-a8b3-f11cbe929364</t>
-        </is>
-      </c>
-      <c r="B193">
-        <v>2</v>
+          <t>rev-3ed726a3-b3d5-4b57-b9f1-b3df3e0f8b29</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Titel: Die Gerichte auf den Werbefotos…, Text: Die Gerichte auf den Werbefotos versprechen mehr als dann nach Erwärmen auf dem Teller landet.</t>
+          <t>Alle Gerichte, die ich bisher probiert habe schmecken hervorragend und dind einfach zuzubereiten.  Manche Gerichte kann ich sogar auf 2 Mahlzeiten aufteilen, weil es so viel ist.</t>
         </is>
       </c>
       <c r="D193">
         <v>2</v>
       </c>
       <c r="E193">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G193">
         <v>2</v>
       </c>
       <c r="H193">
-        <v>3.75</v>
-      </c>
-      <c r="I193">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>rev-9a749415-259c-4415-8572-95fb8777a639</t>
-        </is>
-      </c>
-      <c r="B194">
-        <v>4</v>
+          <t>rev-e18a003f-3870-459a-a598-ee434a950e6d</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Geht so, Text: Geht so_x000D__x000D_
-_x000D__x000D_
-</t>
+          <t>Esse sogar Essen die ich normalerweise überhaupt nicht mag. Warum auch immer, wir haben seitdem wir bei Hofmans bestellen, ging der Mülleimer leer aus. Bei Gloria landete das meiste Essen im Müll. Weiter so. Danke 😅.</t>
         </is>
       </c>
       <c r="D194">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H194">
-        <v>0</v>
-      </c>
-      <c r="I194">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>rev-bf86d5b4-28a0-4370-9093-5642fdda7354</t>
-        </is>
-      </c>
-      <c r="B195">
-        <v>1</v>
+          <t>rev-e16d531b-9c07-4ed5-ae97-34c20b560a6a</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Titel: Kommt nie zum vereinbarten Termin!!!, Text: Unpünktlich</t>
+          <t>Keine Ware erhalten-</t>
         </is>
       </c>
       <c r="D195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E195">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H195">
-        <v>2.5</v>
-      </c>
-      <c r="I195">
         <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>rev-ed8e7163-1e05-41cf-a290-75aebb06c1b4</t>
-        </is>
-      </c>
-      <c r="B196">
-        <v>5</v>
+          <t>rev-0fb90910-dba0-4095-b4cd-b77b0e252668</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Titel: Immer schmackhafte Gerichte, Text: Immer schmackhafte Gerichte, beste Qualität und eine perfekte Zustellung</t>
+          <t>Prompte lieferung</t>
         </is>
       </c>
       <c r="D196">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H196">
-        <v>1.25</v>
-      </c>
-      <c r="I196">
         <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>rev-79f6ba3a-fd67-4fc1-bda6-94ff38640e13</t>
-        </is>
-      </c>
-      <c r="B197">
-        <v>3</v>
+          <t>rev-575e6ce5-e81e-43bb-a49a-a1c1b6f15f76</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Titel: Nicht mein Geschmack, Text: Nicht mein Geschmack ! _x000D__x000D_
-Für zwischendurch Okay 👍 _x000D__x000D_
-Aber prompte Lieferung !</t>
+          <t>Der packetdienst hatte die Lieferung verspätet geliefert, alles aufgetaut._x000D_
+Hofmanns Angerufen, sehr netter Kontakt sofortige Nachlieferung._x000D_
+Dankeschön</t>
         </is>
       </c>
       <c r="D197">
         <v>2</v>
       </c>
       <c r="E197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F197">
         <v>1</v>
       </c>
       <c r="G197">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H197">
-        <v>2.5</v>
-      </c>
-      <c r="I197">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>rev-442cef79-16b8-4dd7-9bc2-ae996cd471bb</t>
-        </is>
-      </c>
-      <c r="B198">
-        <v>5</v>
+          <t>rev-b466acc2-8159-4c57-963e-4863353c8aed</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Titel: Die Gerichte schmecken sehr 👍., Text: Die Gerichte schmecken sehr 👍.</t>
+          <t>Lieferzeit/art top. Gerichte bis jetzt sehr ordentlich.</t>
         </is>
       </c>
       <c r="D198">
         <v>1</v>
       </c>
       <c r="E198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G198">
         <v>1</v>
       </c>
       <c r="H198">
-        <v>0</v>
-      </c>
-      <c r="I198">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>rev-f89f219d-1ba9-4bce-b685-f54c2affde03</t>
-        </is>
-      </c>
-      <c r="B199">
-        <v>5</v>
+          <t>rev-1773a3eb-e026-4b3a-bab7-babb05b2fa1e</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Titel: Zum ersten Mal bestellt und positiv…, Text: Zum ersten Mal bestellt und positiv überrascht. Die Ware wurde sehr gut verpackt und sehr schnell geliefert. Ich werde bei Gelegenheit hier wieder bestellen.</t>
+          <t>Einfache Bedienbarkeit, sehr große Auswahl,  schnelle Lieferung und sehr gute Qualität.</t>
         </is>
       </c>
       <c r="D199">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H199">
-        <v>3.75</v>
-      </c>
-      <c r="I199">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>rev-83a45aa1-ab2d-43f6-beec-6d31394621d7</t>
-        </is>
-      </c>
-      <c r="B200">
-        <v>5</v>
+          <t>rev-bcfd909e-e187-43f2-9888-760d6311a666</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titel: Sehr geschmackvoll., Text: Sehr geschmackvoll._x000D__x000D_
-Wie selbst gekocht_x000D__x000D_
-Das beste Essen von einem Lieferdienst_x000D__x000D_
-Hoffentlich bleibt es so_x000D__x000D_
-</t>
+          <t>Das Essen ist sehr lecker 😋 und vor allem  man das frisch gekocht wird. Das Essen kann man sehr gut genießen.</t>
         </is>
       </c>
       <c r="D200">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G200">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H200">
-        <v>2.5</v>
-      </c>
-      <c r="I200">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>rev-5c37a7fa-28c9-45ba-9b80-47454e3faa97</t>
-        </is>
-      </c>
-      <c r="B201">
-        <v>5</v>
+          <t>rev-a00388e4-af61-4b19-b6ff-557b421e5042</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Titel: Wir haben nur bestes Essen erhalten, Text: Wir haben nur bestes Essen erhalten_x000D__x000D_
-Bis auf Kleinigkeiten bei den Lieferanten haben wir bislang Nix zu meckern _x000D__x000D_
-Und sagen das das Essen seinen Preis wert ist oder besser Preiswert ist _x000D__x000D_
-Vielen Dank</t>
+          <t>Top, sehr zufrieden!_x000D_
+_x000D_
+Eine kleine Anregung zur Verpackung, es könnten z.B. Perforationen entlang der Kanten des Kartons eingearbeitet werden die dass zerkleinern der Verpackung und die Entsorgung doch enorm vereinfachen würden.(Gesehen bei Amazon Verpackungen). _x000D_
+_x000D_
+Leider habe ich noch keine Möglichkeit für das problemlose Entsorgen des, eigentlich perfekten nachhaltigen Isoliermaterials/Heu gefunden. Für mich als Schwerbehinderten ein echtes Problem.</t>
         </is>
       </c>
       <c r="D201">
@@ -7099,16 +6879,13 @@
         <v>1</v>
       </c>
       <c r="F201">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G201">
         <v>2</v>
       </c>
       <c r="H201">
-        <v>2.5</v>
-      </c>
-      <c r="I201">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/sampled_200.xlsx
+++ b/data/sampled_200.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -395,11 +395,16 @@
           <t>Constructivity</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_Sum</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rev-a9adb396-07f0-4243-a1b1-73c4ca484bc5</t>
+          <t>rev-85218741-30c0-4c62-87bc-5f09908c1551</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -409,11 +414,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sehr lecker wie selbst gekocht nicht viel Müll</t>
+          <t>Super leckere Gerichte</t>
         </is>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -422,16 +427,19 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rev-88f963af-59cb-432b-be12-4d5a617718e8</t>
+          <t>rev-d0013736-724f-4ca4-94ff-476c22301eff</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -441,7 +449,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ein echter Alltagsproblemlöser für Singles... reichhaltige Auswahl an leckeren Mahlzeiten, die frisch gekocht und schockgefrostet nach Hause kommen! Spart mir jede Menge Zeit und Nerven.</t>
+          <t xml:space="preserve">Lieferung zum Wunschtermin _x000D_
+Sehr gute Verpackung, die Menüschalen sind auch sehr platzsparend für meinen kleinen Gefrierschrank _x000D_
+Auch das erste Gericht schon probiert,  sehr schmackhaft, fast wie selbstgemacht_x000D_
+Werde sicher wieder bestellen _x000D_
+</t>
         </is>
       </c>
       <c r="D3">
@@ -458,26 +470,29 @@
       </c>
       <c r="H3">
         <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rev-04ea56f0-3d2c-45c9-8aed-4f7fbc2b7686</t>
+          <t>rev-6b6cfe23-8a3d-4ae6-a393-93e431ccc5cc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Der Kundenservice ist freundlich und ergebnisorientiert.</t>
+          <t>Wie immer super</t>
         </is>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -489,45 +504,51 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rev-c3cd0425-3eff-46a9-9393-6ae476e26969</t>
+          <t>rev-d3561b08-324c-4583-869e-9d3e586703b9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wir sind ganz begeistert.  Das Essen schmeckt super und die Portionen sind wirklich ausreichend groß</t>
+          <t>Das Essen hat eine gute Qualität. Nach der Beschreibung hatte ich mir noch mehr versprochen. Ist aber völlig ok. Lecker und die Portionen haben eine angemessene Größe.</t>
         </is>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5">
         <v>1</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rev-25e605c6-9e4f-4ccb-ab8b-10e80e42085f</t>
+          <t>rev-fe75c575-4372-4b07-8bed-d8b6eda2159e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -537,7 +558,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Das Essen war zwei Tage später bei mir. Es ist sehr schmackhaft. Bin mit der Firma sehr zufrieden.</t>
+          <t>Das Essen schmeckt wie selbstgemacht und wird immer wieder gern gegessen wenn es mal schnell gehen muss.</t>
         </is>
       </c>
       <c r="D6">
@@ -550,16 +571,19 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>1</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rev-d324c4e4-9ab3-dcfe-a877-312d0bd6ac25</t>
+          <t>rev-2e0b32c8-e5d5-33ea-e358-20932dd06f02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -569,7 +593,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sehr gutes Essen. Schnelle Lieferung. Alles TOP....</t>
+          <t>Wie immer, schnelle und Richtige Lieferung.</t>
         </is>
       </c>
       <c r="D7">
@@ -586,59 +610,64 @@
       </c>
       <c r="H7">
         <v>0</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rev-79e075a7-dd39-4946-8158-0dd3a01c1065</t>
+          <t>rev-88096a20-c1df-4f56-ae01-86eb993807ed</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Da ich abends keine Lust mehr habe zu kochen, sind die angebotenen Menüs perfekt für mich. Bisher war auch kein Gericht dabei, was mir gar nicht schmeckte. Verpackung ist nachhaltig. Ich werde garantiert öfter bestellen.</t>
+          <t>Das Essen war gut. Mit der Lieferzeit war etwas nicht in Ordnung, das Trockeneis war nicht mehr vorhanden, trotz 0 Grad Außentemperatur. Das haben wir im Sommer nicht gehabt.</t>
         </is>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
       <c r="H8">
         <v>1</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rev-d001980b-9777-4387-aac5-3b545a2e88a4</t>
+          <t>rev-3af397d4-3cdb-43c8-bf44-9148a771f9c5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Zunotgeht das Essen _x000D_
- Lieferung ,Verpackung sehr gut</t>
+          <t>Meine erste Bestellung und alles war zu meiner höchsten Zufriedenheit.</t>
         </is>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -650,13 +679,16 @@
         <v>0</v>
       </c>
       <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rev-32e94aa8-2725-47de-998d-3199c5fd5c83</t>
+          <t>rev-205611eb-fc63-4155-948a-8ff94d3d3b83</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -666,11 +698,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>Die Lieferung ist perfekt! Die Pakete kommen mit recyclebarem, dämmenden Verpackungsmaterial und in Trockeneis gepackt. Alle Menüs schmecken hervorragend und sind sehr lecker.</t>
         </is>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -679,10 +711,13 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -711,10 +746,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -740,13 +778,16 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
       <c r="H12">
         <v>1</v>
+      </c>
+      <c r="I12">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -780,11 +821,14 @@
       <c r="H13">
         <v>1</v>
       </c>
+      <c r="I13">
+        <v>4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rev-b91d5906-8191-41cb-884f-0e4268e8485d</t>
+          <t>rev-ccf84617-e79d-45e1-b8d6-9543d92c27f4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -794,7 +838,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sehr gute Auswahl an leckeren Mahlzeiten.</t>
+          <t>Schnelle Lieferung. Alles in Ordnung.</t>
         </is>
       </c>
       <c r="D14">
@@ -810,13 +854,16 @@
         <v>0</v>
       </c>
       <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rev-2e4653cf-bd1e-46cf-bcc0-4287699f26c0</t>
+          <t>rev-f9ccc557-f189-4d74-a426-ce5361784b8d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -826,11 +873,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gute Qualität zu fairen Preisen.</t>
+          <t>Alles andere ist unwichtig, daß Wichtigste ist aber sehr gut_x000D_
+DAS ESSEN SCHMECKT PRIMA</t>
         </is>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -842,13 +890,16 @@
         <v>0</v>
       </c>
       <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rev-6725556b-c941-4e06-9a2b-0f6f04df58ec</t>
+          <t>rev-c1b96064-5cd6-4662-a6b1-eb3d1646b35d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,11 +909,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>perfekt wie immer, besten Dank!</t>
+          <t>Geschmack, Lieferung und Zuverlässigkeit sind wie immer top und der Kundenservice ist wie immer, sehr freundlich und hilfsbereit. Bin froh, dass es so eine Möglichkeit für meine pflegebedürftige Mutter, gibt und damit die Angehörigen entlastet. Danke dafür🙏🏼</t>
         </is>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -871,27 +922,29 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rev-28206cf8-905c-4502-999e-323c01a8d55b</t>
+          <t>rev-0914945f-07f3-46c4-97f2-d7a7690f1dfb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Internet Werbung abschalten._x000D_
-Mir vergeht der Appetit.</t>
+          <t>Alles okay 🙆‍♂️</t>
         </is>
       </c>
       <c r="D17">
@@ -901,51 +954,57 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rev-fa184d7f-2803-40ef-92e2-7a37e92737df</t>
+          <t>rev-f0ad819f-658b-4a8c-8e04-fdbacc820f64</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Im Großen und Ganzen gut. Die Lieferung war verzögert um einen Tag. Ist etwas problematisch, weil man den ganzen Tag zuhause sein muss, um die Ware gleich nach Lieferung in den Tiefkühlschrank geben muss. Das erste Essen heute war geschmacklich gut und ausreichend. Bin gespannt auf die nächsten Essen.</t>
+          <t>Ja da wo das essen drin ist die sind als bei der lieferung zum Teil alle fast schon offen. Und die Angabe finde ich auch nicht ok auf der Verpackung steht 45 Min und auf der Beilagezettel steht über eine Stunde das sollte man dich schon einig sein. Für ältere Menschen ist das verwirrend.</t>
         </is>
       </c>
       <c r="D18">
         <v>2</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="H18">
         <v>1</v>
+      </c>
+      <c r="I18">
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rev-0abf3d42-6f9d-4e56-ac66-8a0d45eb5185</t>
+          <t>rev-4a330133-1fca-4cec-915a-71be4843c117</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -955,11 +1014,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Schnelle Lieferung. Leckeres Essen</t>
+          <t>Die Vielfalt an Gerichten.</t>
         </is>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -971,36 +1030,36 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rev-f21f7039-9b91-4751-92fc-59e96d335926</t>
+          <t>rev-8bfe1f21-a391-40eb-9771-75da2f8fd56a</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Schnelle und gute Lieferung. _x000D_
-Das Essen schmeckt sehr gut !_x000D_
-_x000D_
-Was ich gut finden würde:_x000D_
-Die einzelnen Portionen könnten etwas größer sein . _x000D_
-_x000D_
-Ansonsten bin ich sehr zufrieden!</t>
+          <t>Ich habe das Paket bei der Post abgeholt. Zuhause musste ich feststellen, dass das Trockeneis schon verdunstet war und die oberen drei Essenschalen schon_x000D_
+leicht angetaut waren. Das fand ich nicht so schön. Jetzt weiß ich natürlich nicht, ob ich wieder bestellen soll, oder einen anderen Anbieter ausprobiere._x000D_
+Das Essen war soweit ganz gut._x000D_
+Gruß Peter Schilling</t>
         </is>
       </c>
       <c r="D20">
         <v>2</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1010,12 +1069,15 @@
       </c>
       <c r="H20">
         <v>1</v>
+      </c>
+      <c r="I20">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rev-e877eddf-c3ed-4fb5-982c-361cd821a7d2</t>
+          <t>rev-fceb50d8-7b4d-43ab-8498-af75c6ee4856</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1025,11 +1087,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pünktliche Lieferung, gute Ware.</t>
+          <t>Ich habe noch kein Essen gekostet. Bis jetzt aber alleine schon die Verpackung der Transport und das kühlen fand ich genial</t>
         </is>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1038,16 +1100,19 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>1</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rev-b082e5f1-fa77-c5ce-83d0-60266acc136e</t>
+          <t>rev-d1c49d40-fe06-7f43-100a-6d0a112c5a9f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1057,7 +1122,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Super leckeres Essen, sind rundum zufrieden.</t>
+          <t>Alles bestens , sehr zu empfehlen.</t>
         </is>
       </c>
       <c r="D22">
@@ -1073,45 +1138,51 @@
         <v>0</v>
       </c>
       <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rev-bfafa733-323d-4720-af1e-c21dc23eefa8</t>
+          <t>rev-0d527521-2fb8-49fe-a3c1-fe8f87bbbe7b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vorneweg.. das Essen selbst ist wirklich gut bis sehr gut. Aber leider haben sehr viele Behälter Beschädigungen gehabt oder waren z.B. "falschherum"  verpackt (dass die Öffnungslaschen die bei Zubereitung schon geöffnet werden müssen für die Beilagen .. auf der falschen Seite waren). Und man hat eine im Hausmüll nicht zu bewältigende Menge Abfall durch die Packungen bzw. das Dämmaterial der Kisten. D.h. leider man braucht auch wieder Hilfe alles auf den Wertstoffhof zu bringen.</t>
+          <t>Sowas von lecker alle waren richtig begeistert</t>
         </is>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rev-d26bab9f-0e0b-4d6c-b587-de8986faab85</t>
+          <t>rev-1615a908-c1b5-49a0-9218-02eae6520778</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1121,11 +1192,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Schnelle Lieferung, gut verpackt.</t>
+          <t>Wie immer sehr Lecker gute Qualität</t>
         </is>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1137,7 +1208,10 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1171,11 +1245,14 @@
       <c r="H25">
         <v>1</v>
       </c>
+      <c r="I25">
+        <v>8</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rev-f0c0f191-0321-4725-ae9c-9b8675e241db</t>
+          <t>rev-00782fb9-b33a-4ca7-88d5-880b1e173ce3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1185,7 +1262,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Schnelle Lieferung, sehr gute Verpackung</t>
+          <t>Mega lecker. Lieferung top. Portion genau richtig. Ich werde Stammkundin.</t>
         </is>
       </c>
       <c r="D26">
@@ -1201,7 +1278,10 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1230,16 +1310,19 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rev-7ee6161f-7dd7-4831-aec8-361c4d35a041</t>
+          <t>rev-3eac59d6-841f-4f38-9d99-3a4d927fb46b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1249,11 +1332,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Schmeckt gut. Preis/Leistung gut.</t>
+          <t>Lebensmittel sind größtenteils okay ich warte auf weitere</t>
         </is>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1262,16 +1345,19 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
         <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>rev-c4afe729-6c84-4f0b-811e-38a8ca3ccda6</t>
+          <t>rev-78cf0f1f-1093-4498-a4f6-1214948ac8cf</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1281,7 +1367,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Die  Zustellung  lief  wie immer reibungslos und  die  Gerichte schmecken wirklich sehr gut.</t>
+          <t>Ich habe ca.30 Gerichte ausprobiert. Es war keins dabei, was nicht geschmeckt hat. Der Preis der Gerichte ist auch in Ordnung. Am Anfang kann man mir die Gerichte ziemlich klein vor, aber mittlerweile habe ich mich dran gewöhnt. Alles in allem bin ich sehr zufrieden.</t>
         </is>
       </c>
       <c r="D29">
@@ -1298,12 +1384,15 @@
       </c>
       <c r="H29">
         <v>1</v>
+      </c>
+      <c r="I29">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>rev-661b7e5d-147c-44a0-af48-1b2618119b62</t>
+          <t>rev-d12d7e30-fd24-419d-9d63-4e4880555233</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1313,8 +1402,8 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wie versprochen schnelle Lieferung und geschmacklich sehr sehr gut._x000D_
-</t>
+          <t>Jeder Geschmack ist anders, ich habe mittlerweile meine Lieblingsgerichte gefunden. Ich bestelle hier gerne, weil ich es nicht immer schaffe zu kochen. Die Portionen sind für mich (w) ausreichend, ein Mann könnte da aber eventuell Schwierigkeiten bekommen._x000D_
+Gut gewürzt, gut gekocht, bringt einem eine warme Mahlzeit in den Magen. Ich werde auch weiterhin hier bestellen!</t>
         </is>
       </c>
       <c r="D30">
@@ -1327,48 +1416,54 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30">
         <v>1</v>
+      </c>
+      <c r="I30">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>rev-058f0da7-3160-466e-b52b-ecf5c8ce0917</t>
+          <t>rev-553948bc-78da-4199-bb77-f8ecb977fbc5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kundenservice eine Rückmeldung innerhalb 24 Stunden,  bis jetzt sind die Gerichte sehr gut man merkt das auf Frische und Qualität geachtet wird. Die Portionen sind ausreichend,  und sehr gut gewürzt .Die Gerichte sind nicht scharf und was die Auswahl betrifft sind wir sehr zufrieden. Was wir an Hofmann auch sehr mögen ist das es viele verschiedene Gerichte gibt und nicht nur eine Richtung. Ich habe schon andere Firmen probiert aber am besten ist für uns Hofmann. Meine Mutter hat Gastritis und kann vieles nicht essen weil Sie es nicht verträgt und ich habe nicht die Zeit und die Möglichkeit zu kochen weil ich schließlich Arbeiten muss. Wir sind neu hier und bis jetzt 8 Gerichte probiert und es hat sich gelohnt meine Mutter kann es essen und es schmeckt ihr auch sehr gut 👍 und vorallem hat sie kein SodbrennenundMagenschmerzen beim essen der Gerichte. Und ich bin auch sehr zufrieden deswegen haben wir wieder bestellt. Kann die Gerichte eigentlich nur empfehlen daher für mich 5 Sterne 🌟 für Gerichte,  und den Kundenservice.</t>
+          <t>Das Essen ist dabei nicht bewertet, da ich es noch nicht gegessen habe. Mir auch nicht sicher bin ob ich das tun sollte. Habe acht Gerichte bestellt und sieben davon sind bei mir beschädigt angekommen ( waren offen ) somit wahrscheinlich mit dem Trockeneis in Verbindung gekommen. Habe den Kundendienst umgehend, mit Fotos, kontaktiert. Nach fünf Tagen immer noch keine Rückmeldung.</t>
         </is>
       </c>
       <c r="D31">
         <v>2</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31">
         <v>2</v>
       </c>
       <c r="H31">
         <v>1</v>
+      </c>
+      <c r="I31">
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>rev-e9435406-93e8-4b90-b71b-29e1ce6a70fc</t>
+          <t>rev-93d8e4f7-99e9-40d6-88f5-201ad866edb8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1378,29 +1473,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>also Geschmacklich sind fast alle Gerichte sehr lecker. Der Reis ist manchmal ein wenig mehlig, vielleicht wäre hier eine andere sorte angebracht. was ich nicht so toll finde, sind die konsistenz der kartoffeln</t>
+          <t>Gut portioniert und gekocht.</t>
         </is>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
         <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>rev-b9b63444-f4ca-4b78-875c-f860209a4dca</t>
+          <t>rev-9136d5ea-168e-4c6b-96c8-2d8d090a9a48</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1410,11 +1508,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pünktlich, sehr gut 👍 verpackt, alles bestens immer wieder gerne.</t>
+          <t>Es ist alles  so wie es sein sollte</t>
         </is>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1426,23 +1524,26 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>rev-c7301646-2f4e-2620-711c-bc42411be893</t>
+          <t>rev-aca485ff-338f-4836-501f-09a08b72a595</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alles bestens und sehr lecker.</t>
+          <t>Gute Produkte</t>
         </is>
       </c>
       <c r="D34">
@@ -1458,23 +1559,26 @@
         <v>0</v>
       </c>
       <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>rev-cf8c2be9-a057-4b30-8297-356a905d839b</t>
+          <t>rev-71170b65-25d9-4ea1-a58a-0b2aec98da13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ich wollte eine Bestellung zu einem bestimmten Liefertermin bestellen was nicht möglich war. Der angerufene Mitarbeiter war nicht hilfsbereit.</t>
+          <t>Geschmacklich gut. Leider mehrere Verpackungen offen gewesen.</t>
         </is>
       </c>
       <c r="D35">
@@ -1487,49 +1591,54 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>1</v>
+      </c>
+      <c r="I35">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rev-6a7bab53-22f2-45d4-ad83-fd13d11c1118</t>
+          <t>rev-fb94041d-18df-4c64-8ec7-fd107de786d4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gerichte schmecken lecker, sehen appetitlich aus, sind jedoch zu klein. _x000D_
-Man wird nicht wirklich satt und das für den Preis von 6,99 € (Penne) ist dann recht teuer.</t>
+          <t>Probiert und ich werde weiter bestellen.</t>
         </is>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>rev-e8754dd5-a236-4d0f-892d-8436473d4812</t>
+          <t>rev-ad691d23-fd3d-450a-8c94-a61384d412ea</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1539,12 +1648,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Große Portionen, die auch sehr gut schmecken. _x000D_
-Schnelle Lieferung also alles top :-)</t>
+          <t>Lecker schnelle Lieferung</t>
         </is>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1553,16 +1661,19 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>rev-59c253da-6b34-4b59-995d-e11afd912ad2</t>
+          <t>rev-8854b696-f36c-4d49-b78c-e44459664d47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1572,11 +1683,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Super schnelle Lieferung, bestens verpackt. Das Essen ist wirklich lecker. Und es ist schnell zubereitet, wenn man gerade keine Zeit und oder Lust hat selbst zu kochen.</t>
+          <t>Alles ist bestens gelaufen.</t>
         </is>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1585,16 +1696,19 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>rev-13fb67e6-07aa-4182-9e6a-574771234505</t>
+          <t>rev-3a0d37c3-f9c5-4878-8a4c-915c8b026dfc</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1604,7 +1718,8 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>alles super</t>
+          <t xml:space="preserve">Bin sehr zufrieden gerne wieder das Essen ist sehr gut _x000D_
+</t>
         </is>
       </c>
       <c r="D39">
@@ -1620,45 +1735,51 @@
         <v>0</v>
       </c>
       <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rev-a27afdbb-eacb-49a5-904b-a49c73408549</t>
+          <t>rev-68aba63f-fa31-4d36-8521-4f20733333a6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Perfekte Lieferung,Essen ist hervorragend, beziehe es schon seit Jahren,erst über unsere Firma,jetzt Privat</t>
+          <t>Gute Auswahl schnelle Lieferung leider keine Auswahl im Shop nach Allergenen möglich. Sehr fleischlastig.</t>
         </is>
       </c>
       <c r="D40">
         <v>2</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40">
         <v>1</v>
       </c>
       <c r="H40">
         <v>1</v>
+      </c>
+      <c r="I40">
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>rev-4b813e3c-6cc4-4f09-99c4-26dbf38b076f</t>
+          <t>rev-9903e4e7-48e2-4d24-adfe-942a6a55590e</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1668,11 +1789,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Perfekt</t>
+          <t>Hochwertige Gerichte, die sehr schmackhaft sind. Die Lieferung erfolgte sehr zügig und sehr gut verpackt, so dass die Tiefkühltemperatur problemlos gehalten wurde.</t>
         </is>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1681,16 +1802,19 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>rev-d3048a2b-df9d-4ba2-970e-5297d74ba2af</t>
+          <t>rev-a9a030f6-d42d-4e28-bfd7-a68099de6bff</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1700,11 +1824,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pünktlich geliefert und sehr gute Qualität</t>
+          <t>Leckere Gerichte zu einem sehr fairen Preis. Verpackung und Versand top, gut durchdachtes Gesamtkonzept. Werde wieder bestellen!</t>
         </is>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1713,16 +1837,19 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42">
         <v>1</v>
+      </c>
+      <c r="I42">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rev-e9df1a4b-b2f4-48b8-b809-5ec86a6e9420</t>
+          <t>rev-14b6ae30-33b0-467c-9557-d08158c433ef</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1732,65 +1859,70 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pünktliche Lieferung und tolle Menüs, sehr lecker und nicht mit den Fertigmahlzeiten aus dem Supermarkt zu vergleichen._x000D_
-Die Menüschalen sind leider etwas groß und es passen dadurch nicht so viele in mein Tiefkühlfach aber dann bestelle ich zukünftig weniger und dafür öfter 😊</t>
+          <t>Schnelle Lieferung, erstklassige Verpackung,_x000D_
+Preis-Leistungs-Verhältnis _x000D_
+⭐️⭐️⭐️⭐️⭐️</t>
         </is>
       </c>
       <c r="D43">
         <v>2</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rev-a39b599b-8679-49ca-9ca9-db780a20cc05</t>
+          <t>rev-a4d49186-edd2-49e2-9e56-1e4b97eb296d</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nach mehrmaliger Bestellung.Hofmann`s macht's.Kundenservice -Top._x000D_
-Die Menüs sind schmackhaft - ausreichend._x000D_
-Jedoch an der Logistik muss noch gefeilt ( Schruppfeile )._x000D_
-E.Uwe Fischer</t>
+          <t>Besser machen:_x000D_
+Internetseite</t>
         </is>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44">
         <v>1</v>
+      </c>
+      <c r="I44">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>rev-e563db4e-f32f-4bcf-8c98-d7eddd12d283</t>
+          <t>rev-8d700f7d-e866-4ec5-bea2-8f32ec1cbe51</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1800,11 +1932,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Schneller Versand, sehr gute Gerichte</t>
+          <t>Alles bestens wie immer, vielen Dank!</t>
         </is>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1816,26 +1948,27 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>rev-894c1d2a-39e2-4272-af77-b6827b962ddb</t>
+          <t>rev-faa2f189-b63b-452d-88e7-2f59e3ef6ac8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bei der letzten Lieferung waren ein mehrere Deckel offen , die Pommes lagen so im Karton._x000D_
-Am Karton war keine Beschädigung _x000D_
-Es muß beim verpacken übersehen worden sein das verschiedene Deckel nicht verschlossen waren _x000D_
-Grüße J. Eder</t>
+          <t>Bis jetzt hat mir jedes Gericht geschmeckt. Ich bin sehr zufrieden. Da mein Mann Diabetiker ist können wir auch gut berechnen was er spritzen muß._x000D_
+Bei Lieferungen immer nachschauen ob der Deckel sitzt. Bei mir ist eine Schale wieder aufgegangen als ich sie aus dem Gefrierfach nahm.</t>
         </is>
       </c>
       <c r="D46">
@@ -1852,29 +1985,34 @@
       </c>
       <c r="H46">
         <v>1</v>
+      </c>
+      <c r="I46">
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>rev-84f1e5a9-00c8-4803-8b0c-cbf982520b3b</t>
+          <t>rev-459ee1ff-26ee-4816-9443-3e065ceb7408</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Received the ordered items very fast. They are very easy to store in the freezer. I have tried 2 of the meals - they were good (but not very good). At least much better to what you can get in the supermarket. I will try another package and see how they taste.</t>
+          <t xml:space="preserve">Meine Bestellung ist noch nicht angekommen, obwohl 12.06.24 angegeben war_x000D_
+Ich bestellte dort nie wieder_x000D_
+</t>
         </is>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -1883,13 +2021,16 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>rev-5aeaa569-4512-4af8-b097-a3b73cc0dd89</t>
+          <t>rev-a66cd2a1-83a4-4aea-9a96-602f761c242a</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1899,26 +2040,26 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Immer sehr gut gewürzt und nie zu trocken. _x000D_
-Schnelle Lieferung, kommt super verpackt, gefroren an._x000D_
-Mit Wunschtermin, Perfekt!_x000D_
-Ich bestelle definitiv wieder!</t>
+          <t>Ich kann nur positives sagen.der Kaiserschmarren allerdings schmeckt gar nicht.viel zu süß.ansonsten alles gut.</t>
         </is>
       </c>
       <c r="D48">
         <v>2</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -1952,43 +2093,49 @@
       <c r="H49">
         <v>0</v>
       </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>rev-528fd133-2f13-41ca-a3c1-831f86c0cdce</t>
+          <t>rev-95d6f5c8-a997-493f-812e-999110da1a2f</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Es ist sehr lecker und genug für 1 Person. Manchmal könnte gerade bei Nudelgerichten etwas mehr Sauce sein. Also weiter so.</t>
+          <t>Alles Bestens</t>
         </is>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rev-cc1b7cc8-bbe9-4af3-9da8-278c82ac4aa7</t>
+          <t>rev-ab51ef98-2057-4c2b-922d-e75c27fc1b8e</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1998,7 +2145,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pünktliche Lieferungen, leckeres Essen</t>
+          <t>Der Support ist gut das Essen lecker, was will man mehr.</t>
         </is>
       </c>
       <c r="D51">
@@ -2014,24 +2161,26 @@
         <v>0</v>
       </c>
       <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
         <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rev-5e82397c-70c7-422a-a2e8-f2e9227d7965</t>
+          <t>rev-e790e323-75a8-4c1c-9818-b2f3e4340b4e</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Die Menüs sind gut portioniert und schmackhaft._x000D_
-Lieferung sehr pünktlich und sehr gut verpackt - allerdings muss das recht umfangreiche (Öko-) Verpackungsmaterial auch entsorgt werden.</t>
+          <t>Die Kartoffeln/Kartoffelbrei haben einen merkwürdigen Eigengeschmack.Bei der Bratwurst mit Sauerkraut hatten zu wenig Sosse.Sonst sind die Gerichte meistens sehr schmackhaft.</t>
         </is>
       </c>
       <c r="D52">
@@ -2044,16 +2193,19 @@
         <v>1</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>1</v>
+      </c>
+      <c r="I52">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rev-bc5bfcdb-74ae-41d2-954d-d2453f78dbc9</t>
+          <t>rev-6e4ff4f7-8fdc-4128-9f9e-043972aad7bb</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2063,29 +2215,32 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Das entfernen der Hülle um das Stroh ist aufwendig und verursacht Schmutz und Staub.</t>
+          <t>Alles in bester Ordnung,keine Beschwerde.</t>
         </is>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rev-f5f6e6b7-b2bc-40fb-a780-6f7da38a537a</t>
+          <t>rev-b8a0d0d9-0fc4-409b-8624-fbb5aaf0dc31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2095,92 +2250,97 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hallo zu den Mitarbeitern und Mitarbeiterinnen. Jedes Essen ist sehr schmackhaft . Für die Zunge sehr gut zubereitet. Manches Mal ist mir aber ein kleiner brennender Geschmack in meinem Mund zuviel._x000D_
-Mit traumhaften Gewürzen verfeinert. Bei Ihnen arbeiten wirklich Fachleute_x000D_
-die sich auskennen um Gewürze in den einzelnen Gerichten zu verteilen und abzustimmen. Ich bin der Meinung, dass jedes Gericht mit sehr viel Liebe zubereitet wird._x000D_
-Herzliche Grüße_x000D_
-Luise Juliane Kühner Baldauf_x000D_
-</t>
+          <t>Sehr leckere Gerichte, schnelle Lieferung, große Auswahl.</t>
         </is>
       </c>
       <c r="D54">
         <v>2</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>rev-6c247adf-fac8-473d-85eb-d918b96ffe15</t>
+          <t>rev-a9ef1d94-9001-4b38-8940-9c0145e1c6bc</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>zu geringe preisliche Abstufung bei einfachen Gerichten im Vgl. zu Fleisch- und Fischgerichten.</t>
+          <t>Gutes Essen, gute Lieferung.</t>
         </is>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
         <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rev-f5312e25-c524-466e-905f-5d51ab2c7086</t>
+          <t>rev-dfc9baa7-a1db-4e69-abbc-e683e176f9c6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alle Essen waren bis jetzt sehr gut.</t>
+          <t xml:space="preserve">Bei den Gerichten, bei denen man den Deckel öffnen muss um Pommes, Rösti oder ähnliches zu garen, sollte die Schale so aufgebaut sein, das das Gemüse, bzw die Nudeln soweit getrennt sind das sie nicht vertrocknen _x000D_
+</t>
         </is>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I56">
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -2214,78 +2374,85 @@
       <c r="H57">
         <v>0</v>
       </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>rev-fb0610fc-6362-429d-993d-8b7957fca8aa</t>
+          <t>rev-0b420aa0-94f9-41df-93ac-6413c827d6c1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Verpackung ohne Stereopor. Alles wie versrochen.</t>
+          <t>Es wurden Artikel einfach ausgetauscht, weil sie angeblich nicht lieferbar waren. Jedoch wurde dies vorher überhaupt nicht mit mir kommuniziert.</t>
         </is>
       </c>
       <c r="D58">
         <v>2</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58">
         <v>1</v>
+      </c>
+      <c r="I58">
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>rev-1ec2ecc0-d6a6-4300-827f-76660cd2f91b</t>
+          <t>rev-4cb4b341-6dd0-4396-8f91-2075211bb08e</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ich kenne Hofmann Menü schon lange und weiß, das sie sehr gute Produkte haben. Leider konnte ich nichts dieses mal machen. Trotz dem volle Sterne da meine Rekla schnell und ohne großen aufwand erledigt worden ist._x000D_
-Großes Lob an das Team_x000D_
-G.S._x000D_
-</t>
+          <t>Die kloesse waren grottenschlecht beim Sauerbraten wie gepresste saegemehl_x000D_
+Leider</t>
         </is>
       </c>
       <c r="D59">
         <v>1</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
         <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>rev-4abf82a9-12b6-4931-b6f0-60ec63b00c83</t>
+          <t>rev-0dea019e-da08-4fa7-81aa-b8ef7d202945</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2295,12 +2462,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Diesmal ging es sehr lang._x000D_
-Freitag Morgen bis Donnerstag Morgen</t>
+          <t>Wieder alles prima!! Schnelle Lieferung 🚚 und leckeres Essen 🍱 Hatten zum ersten Mal Eis dabei war sehr gut 👍</t>
         </is>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2312,7 +2478,10 @@
         <v>0</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -2346,119 +2515,119 @@
       <c r="H61">
         <v>1</v>
       </c>
+      <c r="I61">
+        <v>3</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>rev-c7b36eac-b1a9-4273-9fec-b94dbe72361e</t>
+          <t>rev-41fefd01-670b-46e4-bea4-ecb29ffec8ce</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Für mich als Flexitarier wären Option zB für:_x000D_
-_x000D_
-- mit / ohne Fleisch _x000D_
-- für Gerichte auch vegetarische Variante_x000D_
-_x000D_
-Von meiner ersten Bestellung bis heute hat sich das Rindfleisch leider zum negativen verändert._x000D_
-_x000D_
-Anfangs waren Rindsrouladen und Sauerbraten / Gulasch meine Lieblinge, mittlerweile nicht mehr._x000D_
-_x000D_
-Fleisch ist nun ziemlich zäh. Damals hast es mit der Gabel zerdrücken können._x000D_
-_x000D_
-Rouladen waren letztes Mal nur 2 kleine, fast schwarze,bemitleidenswerte Ping-Pong-Bälle ohne Füllung (bis auf den Speck)</t>
+          <t>Top Essen... Alles lecker</t>
         </is>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>rev-14f2d643-0aac-477e-8d99-dc7fe01e073d</t>
+          <t>rev-092947ff-dbba-4d8c-88e4-66ee212a4d4b</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Die Verpackung der Menüs (Deckel / Schale) ist teilweise nicht ausreichend festgeschlossen für den Transport. Die Kartons werden beim Transport beansprucht und dadurch werden die Menüschalen stark geschüttelt, so dass Deckel und Schale sich lösen. Daraufhin fallen lose Bestandteile (z.B. Reis) aus der Schale (siehe Bild). Entsprechend beschädigt kommen die Menüschalen in den Tiefkühler. In unserem Fall zwei Menüschalen werden, wahrscheinlich ein reduziertes Geschmackserlebnis entfallten. Bitte verbessern Sie die Haftung zwischen Schale und Deckel._x000D_
-Grundsätzlich sind die Menüs sehr ansprechend und bieten eine Vielfalt.</t>
+          <t>Alles perfekt gelaufen, Essen schmeckt sehr gut</t>
         </is>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>rev-d18d94ac-7710-57aa-0a02-d061c95ae0a1</t>
+          <t>rev-2ed013d5-24e3-e187-8f62-ea519e8a0789</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Einlösen des ZFZ Sommerfest-Rabatt hat nicht geklappt und ein Alternative wurde mir  leider nicht geboten . Schade</t>
+          <t>Leckere Gerichte, zuverlässige Lieferung!</t>
         </is>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
         <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>rev-068ebd42-df05-484c-a694-d08b88606862</t>
+          <t>rev-2a4ac6e8-cb56-4bd9-945f-88157b71ed41</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2468,11 +2637,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Schnelle Lieferung</t>
+          <t>Super schnelle Lieferung,gute Qualität,vielseitige Auswahl</t>
         </is>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2485,55 +2654,61 @@
       </c>
       <c r="H65">
         <v>0</v>
+      </c>
+      <c r="I65">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>rev-160747ec-e564-4f38-82a6-2ccec7a1046d</t>
+          <t>rev-6b537c73-6d7b-40e1-836f-85eac07b3018</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Schnelle Lieferung, Gutes Essen. Für mich sehr gut 👍</t>
+          <t>Bei meiner vorletzten Lieferung habe ich die sehr schlechte Versiegelung der Verpackungen reklamiert und auch Fotos geschickt und danach nie mehr etwas gehört. Die versprochene Gutschrift habe ich auch nicht erhalten._x000D_
+Bei der letzte Lieferung waren immer noch Packungen schlecht verschlossen, so dass der Reis zum Teil im Versandkarton lag.</t>
         </is>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H66">
         <v>1</v>
+      </c>
+      <c r="I66">
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>rev-c4e0075e-6456-4618-aa43-d3f4d84b1587</t>
+          <t>rev-6b096954-dbc8-4aaa-9543-1aa0d5229437</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Schnelle Lieferung noch gut Gefroren .Wahre_x000D_
-Ist sehr Gut</t>
+          <t>Gut Qualität undachnelle Lieferung</t>
         </is>
       </c>
       <c r="D67">
@@ -2550,12 +2725,15 @@
       </c>
       <c r="H67">
         <v>0</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>rev-b9eefa79-8dac-4b2c-a234-ceb9c2a8948d</t>
+          <t>rev-4f5e4182-612e-4e0b-8819-482c027d1c17</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2565,29 +2743,34 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Schnelle und perfekt verpackte Lieferung. Qualität der Menues perfekt!</t>
+          <t>Tolle Gerichte, tolle Auswahl, super Kundenservice sehr freundlich und hilfsbereit. _x000D_
+Leider hatte ich Probleme/Schwierigkeiten mit dem Versandpartner. _x000D_
+Aber alles was das Essen betrifft war einfach super! 👍🏻</t>
         </is>
       </c>
       <c r="D68">
         <v>2</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68">
         <v>0</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68">
         <v>1</v>
+      </c>
+      <c r="I68">
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>rev-4489ea9b-123a-486c-af65-c02ac5fdf9ea</t>
+          <t>rev-90d35a28-5e50-4b2d-b125-f96569bb1680</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2597,7 +2780,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>👍</t>
+          <t>die Essen sind klasse,</t>
         </is>
       </c>
       <c r="D69">
@@ -2613,45 +2796,51 @@
         <v>0</v>
       </c>
       <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>rev-be8c4994-ed7f-48ad-8aba-83fdd5814186</t>
+          <t>rev-59ec43e8-f411-40e3-a50b-af8acf482aa3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sehr leckere Gerichte !! Toller Geschmack. !! Schnelle Lieferung. !! Toller Service. !!  TOP. !!</t>
+          <t>Die Bestellung war einen Tag länger unterwegs. Trockeneis war schon nicht mehr vorhanden. Unten war der Karton feucht. Das essen ist lecker.  Werde aber wenn es so heiss ist nicht mehr bestellen. Dann kühlere Monate</t>
         </is>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rev-f2442da3-7139-41a7-a59d-1b864f0355b4</t>
+          <t>rev-9c923daa-4210-435a-8f83-6e0a9a85e189</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2661,11 +2850,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Schnell und zuverlässig, gerne wieder</t>
+          <t>Wir haben jetzt das 2. Mal bestellt. Die Lieferung erfolgt innerhalb von 2 Tagen. Die Kühlung der Ware ist perfekt und nachhaltig. Das Essen ist echt lecker, hat eine sehr gute Qualität.  Zudem hat man sehr viel Auswahl, so dass für Jeden was dabei ist. Wir werden auf jeden Fall wieder bestellen.</t>
         </is>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2674,10 +2863,13 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I71">
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -2711,6 +2903,9 @@
       <c r="H72">
         <v>1</v>
       </c>
+      <c r="I72">
+        <v>2</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2738,42 +2933,50 @@
         <v>1</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73">
         <v>1</v>
+      </c>
+      <c r="I73">
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>rev-4fb3b47e-c667-4a8e-a109-1f4f5384c00e</t>
+          <t>rev-fc4eb71b-b6db-4790-aa6a-f23eb78fafa6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Alles sehr umweltfreundlich verpackt , und die Gerichte sind sehr lecker!</t>
+          <t>Bestehlung habe ich zwei Tage nach vereinbarte  Termin  bekommen. Leider war nicht mehr angefroren._x000D_
+Jetzt habe ich ein Problem, nämlich   weiß ich nicht ob die Gerichte essbar sind ._x000D_
+Wir sind sehr enttäuscht</t>
         </is>
       </c>
       <c r="D74">
         <v>2</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74">
         <v>1</v>
+      </c>
+      <c r="I74">
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -2807,26 +3010,28 @@
       <c r="H75">
         <v>0</v>
       </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>rev-5210464f-9046-4e4d-bf0e-92134fd2625a</t>
+          <t>rev-bdfd2d15-4e41-463c-837a-f05b6cc9f4dc</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Super frische Ware schmeckt super lecker und sehr schnelle Lieferung _x000D_
-Habe direkt nachbestellt</t>
+          <t>Gut und einfache schnelle Zubereitung</t>
         </is>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2835,9 +3040,12 @@
         <v>0</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
         <v>1</v>
       </c>
     </row>
@@ -2872,11 +3080,14 @@
       <c r="H77">
         <v>1</v>
       </c>
+      <c r="I77">
+        <v>7</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>rev-1489c851-db7f-40db-b143-415f3389702b</t>
+          <t>rev-a7e5393c-e61b-4529-9370-0b9e7ec0d949</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2886,61 +3097,68 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Die meisten Essen sind sehr lecker. Wir nutzen das gern, wenn keine Zeit zum Einkaufen bleibt oder wir zu phantasielos sind ('was soll ich bloß heute wieder kochen?')</t>
+          <t>Essen ist soweit ok. Wenn’s schnell gehen muss in die Mikro und wenn lange dauern soll in den Heißluft. Manchmal könnte es ein wenig mehr sein vom Inhalt, aber als Zwischensnack ganz gut 😀 Lieferung war gut verpackt, allerdings  ein kleiner Teil war schon angetaut. Habe dennoch gleich noch mal bestellt. Nächste Lieferung kommt im September . Im großen Ganzen durchaus weiter zu empfehlen. 👍🏻( PS: Schnitzel jeglicher Art sind klasse.)</t>
         </is>
       </c>
       <c r="D78">
         <v>2</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78">
         <v>2</v>
       </c>
       <c r="H78">
         <v>1</v>
+      </c>
+      <c r="I78">
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>rev-6fcba3a3-282c-409e-9eec-1316d85dd603</t>
+          <t>rev-e431db3c-2b1c-4629-bcb3-49ed78d1ff59</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NETTER  POSTBODE HILFSBEREICH GERNE WIEDER</t>
+          <t>_x000D_
+ich empfehle silberfolie auf die essensschale zu geben und dann in den ofen</t>
         </is>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79">
         <v>0</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G79">
         <v>0</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>rev-78df6a87-1609-44cf-824f-200db94a713c</t>
+          <t>rev-ee5eb9fc-35f7-4d2e-b6d2-f42d19ac7bd4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2950,11 +3168,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ich bin total zufrieden!!!</t>
+          <t>Pünktliche Lieferung und "wie bei Muttern "</t>
         </is>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2967,12 +3185,15 @@
       </c>
       <c r="H80">
         <v>0</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>rev-7126ce55-3adb-4cb8-b16b-121a655d9d68</t>
+          <t>rev-e07396a6-8cbc-4037-ae46-e9afcbf926f2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2982,11 +3203,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tolle Gerichte und ich muss nicht selber kochen.</t>
+          <t>Gutes essen</t>
         </is>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2995,42 +3216,50 @@
         <v>0</v>
       </c>
       <c r="G81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>rev-0a421fe2-bba1-48af-a32c-17a53f69903b</t>
+          <t>rev-6e0a82bd-04ca-4d6b-a1ff-8d4349612b9e</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Das Essen ist perfekt und die Auswahl ist super, lediglich 1 Stern Abzug für die Versandverpackung, die ist leider nicht besonders gut für den Versand, die Isolierung rutscht herum und das Paket wird nass.</t>
+          <t xml:space="preserve">Einfache Bestellung, habe bis jetzt zwei der Menüs verkostet._x000D_
+Ordentliche Portionen und sehr lecker._x000D_
+</t>
         </is>
       </c>
       <c r="D82">
         <v>2</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G82">
         <v>2</v>
       </c>
       <c r="H82">
         <v>1</v>
+      </c>
+      <c r="I82">
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -3065,11 +3294,14 @@
       <c r="H83">
         <v>0</v>
       </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>rev-6e47d56a-75f4-4e75-bee0-b33645d79649</t>
+          <t>rev-c2c0aa9b-a903-4035-a218-fcdae503bb19</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3079,7 +3311,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hofmanns Menüs sind sehr gut</t>
+          <t>Alles perfekt</t>
         </is>
       </c>
       <c r="D84">
@@ -3095,13 +3327,16 @@
         <v>0</v>
       </c>
       <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>rev-ad6a2b60-f9fa-411a-9365-e02535c458dd</t>
+          <t>rev-c2d7db11-5d89-42f2-938a-65a7b578779d</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3111,7 +3346,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Promte Lieferung.</t>
+          <t>Gibt es eine andere Dämmung, außer die Strohplatten? Weil man halt jedes mal die Entsorgung im "Grünabfall" hat. Nur ne Frage. Sonst ist alles super.</t>
         </is>
       </c>
       <c r="D85">
@@ -3128,6 +3363,9 @@
       </c>
       <c r="H85">
         <v>0</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -3147,7 +3385,7 @@
         </is>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3159,7 +3397,10 @@
         <v>0</v>
       </c>
       <c r="H86">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -3183,7 +3424,7 @@
         <v>2</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -3193,12 +3434,15 @@
       </c>
       <c r="H87">
         <v>1</v>
+      </c>
+      <c r="I87">
+        <v>7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>rev-f3383a3a-a1b0-4316-82c9-69845be67820</t>
+          <t>rev-6edc9ecd-4c81-4c5d-85b6-d0f3969178a8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3208,7 +3452,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Überdurchschnittliche und schnelle Bestellung durch gute Web seite</t>
+          <t>Schnelle Lieferung - super Qualität!</t>
         </is>
       </c>
       <c r="D88">
@@ -3221,9 +3465,12 @@
         <v>0</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
         <v>1</v>
       </c>
     </row>
@@ -3258,11 +3505,14 @@
       <c r="H89">
         <v>0</v>
       </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>rev-67424b1f-475c-0126-a7b5-9b8f92c02e9b</t>
+          <t>rev-a3969826-91bd-8fd1-fe99-6a1e46a9ff54</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3272,7 +3522,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Unkompliziert und lecker.</t>
+          <t>Alles okay</t>
         </is>
       </c>
       <c r="D90">
@@ -3288,13 +3538,16 @@
         <v>0</v>
       </c>
       <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>rev-483655ad-4641-4c2c-aa93-3a7222870c7f</t>
+          <t>rev-01831fa0-c798-47d6-80e1-720550939fb7</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3304,7 +3557,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sehr lecker 😋</t>
+          <t>Sehr leckeres Essen. Es lohnt sich dort zu bestellen. Ich werde glaube ich Wiederholungstäter</t>
         </is>
       </c>
       <c r="D91">
@@ -3320,39 +3573,47 @@
         <v>0</v>
       </c>
       <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>rev-b00d0068-e77b-472d-a8e0-512d2e9da121</t>
+          <t>rev-0970ffbf-c319-4b79-8b38-4a6ee4f57975</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Die Menüs haben in letzter Zeit sehr häufig Gefrierbrand. Bei einer telefonischen Reklamation wollte man mir nicht weiterhelfen, auf eine schriftliche Reklamation hin habe ich seit 8. Januar keine Reaktion</t>
+          <t>Alle Essen sind super, danke, wie immer._x000D_
+_x000D_
+R.Reinl , Arnstadt</t>
         </is>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -3382,16 +3643,19 @@
         <v>1</v>
       </c>
       <c r="G93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <v>1</v>
+      </c>
+      <c r="I93">
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>rev-86b1c2cf-e1f9-c5a6-9e7f-51f5a2512a53</t>
+          <t>rev-bbc0f6de-7d31-e6c0-ee2a-ed71db98fcdc</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3401,7 +3665,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wie immer perfekt</t>
+          <t>super Essen!</t>
         </is>
       </c>
       <c r="D94">
@@ -3417,13 +3681,16 @@
         <v>0</v>
       </c>
       <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>rev-6c97f7c2-fa3a-4e69-ba66-efbd19d7e979</t>
+          <t>rev-945b4928-cd24-4cf3-b592-fd06831e2017</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3433,11 +3700,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Die Testbox war hervorragend. Jeder Tag ein Genus.</t>
+          <t>Große Auswahl an Gerichten. Geschmacklich war bisher alles sehr gut. Der Versand ist richtig schnell. Heute bestellt, am nächsten Vormittag gehen die Gerichte schon raus.</t>
         </is>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3446,42 +3713,48 @@
         <v>0</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H95">
         <v>1</v>
+      </c>
+      <c r="I95">
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>rev-6b639669-2b58-4673-adbd-475de18275c0</t>
+          <t>rev-93262846-ca21-46d8-83d8-5ea9dfc49089</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ich habe noch nicht alle Gerichte gegessen, aber die die ich probiert habe waren sehr lecker und ich bin auf die anderen gespannt. Bei der Erbsensuppe waren die Würstchen nicht der Renner aber sonst war sie sehr gut. Waren bis jetzt mit Abstand die besten Fertiggerichte die ich versucht habe und es war nicht das letzte mal, dass ich bestellt habe.</t>
+          <t>Entsprach den Erwartungen...</t>
         </is>
       </c>
       <c r="D96">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96">
         <v>0</v>
       </c>
       <c r="G96">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -3513,13 +3786,16 @@
         <v>0</v>
       </c>
       <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
         <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>rev-2ced9048-ce9c-484b-9db9-bcda38c30f9e</t>
+          <t>rev-011fe2b0-92ec-4525-945c-c26684dc5cf1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3529,7 +3805,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Alles Super gelaufen wie immer danke</t>
+          <t>Hofmann Menü‘s super lecker 😋</t>
         </is>
       </c>
       <c r="D98">
@@ -3545,6 +3821,9 @@
         <v>0</v>
       </c>
       <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
         <v>0</v>
       </c>
     </row>
@@ -3582,43 +3861,49 @@
       <c r="H99">
         <v>1</v>
       </c>
+      <c r="I99">
+        <v>4</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>rev-855639e0-e266-41b6-902a-a89c3c555e2b</t>
+          <t>rev-5f072088-c694-4b18-b293-89baa2aa60c4</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Es wurde mir ein 20€ Gutschein versprochen. Die Email war ohne Anschreiben und sehr unpersönlich. Auf Meike Frage habe ich keine Antwort erhalten und auch keinen Gutschein</t>
+          <t>Super Verpackung - sehr schnelle Lieferung zum Wunschdatum - mit Sicherheit immer wieder ;)</t>
         </is>
       </c>
       <c r="D100">
         <v>2</v>
       </c>
       <c r="E100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H100">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rev-ed355075-5087-7f55-637a-a8641e38715e</t>
+          <t>rev-65d17601-a1be-ec5f-bf97-9d6b381175dd</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3628,23 +3913,26 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sehr schnelle Lieferung und super leckeres Essen. Schade, dass es für Privatkunden nicht so viel Auswahl gibt wie für die Essen auf Rädern-Kunden.</t>
+          <t>Super</t>
         </is>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>0</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -3676,13 +3964,16 @@
         <v>0</v>
       </c>
       <c r="H102">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>rev-0f4a2a8a-ed45-ce17-327a-3752baf9b3e7</t>
+          <t>rev-bc3d7f67-1643-a728-efac-6e9eb3f0dee6</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3692,7 +3983,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Schnelle Lieferung und lecker. Super das es jezt auch in der Mikrowelle geht</t>
+          <t>Lecker, lecker, lecker! Man schmeckt die Individualität der Gewürze, das hochwertige Fleisch in allen Produkten, und die Frische des verarbeiteten Material. Teilweise wie selbstgemacht von einer guten Köchin, teilweise auch wie von einem Sternekoch. Super!</t>
         </is>
       </c>
       <c r="D103">
@@ -3705,16 +3996,19 @@
         <v>0</v>
       </c>
       <c r="G103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rev-a6a2269b-ac5f-c913-a260-3da012f64d79</t>
+          <t>rev-e3a7dedf-d954-ba27-a4bf-43ac5d27deef</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3724,7 +4018,9 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Schnelle Lieferung, sicher und gut verpackt. Geschmack ist top, wie frisch gekocht. Gemüse bissfest, Fleisch zart, weder lasch noch überwürzt und ohne diesen typischen Fertiggerichte-Krankenhaus-Geschmack. Portionsgröße ist okay, kräftige Männer brauchen wahrscheinlich zwei Portionen.</t>
+          <t>Schnell und sicher geliefert. _x000D_
+Sehr schmackhaft und leicht zuzubereiten. _x000D_
+Deckel sind leicht zu öffnen. Speziell für ältere Menschen.</t>
         </is>
       </c>
       <c r="D104">
@@ -3741,12 +4037,15 @@
       </c>
       <c r="H104">
         <v>1</v>
+      </c>
+      <c r="I104">
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>rev-fe75c575-4372-4b07-8bed-d8b6eda2159e</t>
+          <t>rev-86317aff-7662-48e6-968a-8e7f24bcc4df</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3756,7 +4055,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Das Essen schmeckt wie selbstgemacht und wird immer wieder gern gegessen wenn es mal schnell gehen muss.</t>
+          <t>Schnelle gut geplante Lieferung. Sehr gut und Umweltfreundlich verpackt.</t>
         </is>
       </c>
       <c r="D105">
@@ -3769,10 +4068,13 @@
         <v>0</v>
       </c>
       <c r="G105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H105">
         <v>1</v>
+      </c>
+      <c r="I105">
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -3806,6 +4108,9 @@
       <c r="H106">
         <v>1</v>
       </c>
+      <c r="I106">
+        <v>5</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3839,11 +4144,14 @@
       <c r="H107">
         <v>1</v>
       </c>
+      <c r="I107">
+        <v>7</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>rev-b9bb4100-7ba5-424f-a9ff-3da08d2775e1</t>
+          <t>rev-91a0463d-ff4c-4015-85b0-ada4ba90b492</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3853,11 +4161,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Alles Klasse verpackt, Bestellung kommt sehr schnell ca. 2 Tage später. Schmeckt alles wie bei Muttern</t>
+          <t>Die von mir bestellten Boxen haben meinen Geschmack voll und ganz getroffen. Ich werde weiter bei Ihnen bestellen._x000D_
+Es schmeckt hervorragend.</t>
         </is>
       </c>
       <c r="D108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3866,16 +4175,19 @@
         <v>0</v>
       </c>
       <c r="G108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
         <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>rev-adf18c52-05e2-46fd-b85c-a163b7ab16a3</t>
+          <t>rev-ef4f237f-3fef-4905-bab0-eb458321b0e2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3885,11 +4197,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Schmeckt sehr gut,Portion reicht für mich</t>
+          <t>Die gute Qualität und schnelle und sichere Lieferung</t>
         </is>
       </c>
       <c r="D109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3898,16 +4210,19 @@
         <v>0</v>
       </c>
       <c r="G109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
         <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rev-7b68b4b9-3b74-0f94-6cbb-8e507fc3750e</t>
+          <t>rev-c20c6467-bd83-ac56-ceed-f1d57663ca3f</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3917,7 +4232,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>bestens. Geschmack super. gern wieder</t>
+          <t>Alles bestens, sehr gerne wieder...</t>
         </is>
       </c>
       <c r="D110">
@@ -3933,13 +4248,16 @@
         <v>0</v>
       </c>
       <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
         <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>rev-34336869-96ee-4687-ab0e-f5aec1a9faed</t>
+          <t>rev-271095c8-6769-497e-9d8e-e71362010baa</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3949,11 +4267,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Alles super. Bestellung, Lieferung, Qualität der Erzeugnisse</t>
+          <t xml:space="preserve">Ich bestelle für meine pflegebedürftige Mutter regelmäßig. Sie hat früher immer selbst gekocht und daher relativ hohe Ansprüche. Wir haben die Themenboxen alle ausprobiert und ihr haben sämtliche Gerichte gut geschmeckt._x000D_
+Darüberhinaus war die Lieferung immer zeitnah und gut gekühlt. _x000D_
+Die Preise finde ich angemessen._x000D_
+</t>
         </is>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3962,16 +4283,19 @@
         <v>0</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <v>4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rev-a5eebdf3-1b64-43d2-a1b8-5a1bd3549f1d</t>
+          <t>rev-e2fc0712-44c9-4866-9597-51e364552181</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3981,11 +4305,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Schnelle Online Bestellung, Lieferung und das Essen ist sehr schmackhaft</t>
+          <t>Alles bestens und wenn mal Kleinigkeiten nicht ok sind , dann sehr kulant.</t>
         </is>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3997,7 +4321,10 @@
         <v>0</v>
       </c>
       <c r="H112">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -4017,7 +4344,7 @@
         </is>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -4029,7 +4356,10 @@
         <v>0</v>
       </c>
       <c r="H113">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -4058,16 +4388,19 @@
         <v>1</v>
       </c>
       <c r="G114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114">
         <v>1</v>
+      </c>
+      <c r="I114">
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>rev-5ef57c5a-9570-4bee-6c29-859480eb0cf9</t>
+          <t>rev-4de2bbdc-0506-69a7-715d-4c197e82579e</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4077,11 +4410,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ausgesprochen gutes Produkt</t>
+          <t>Alles lecker , Lieferung sehr gut.</t>
         </is>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4094,38 +4427,44 @@
       </c>
       <c r="H115">
         <v>0</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>rev-4778af42-4f30-4108-921d-d7f282070489</t>
+          <t>rev-4b18a468-bf5b-447f-b7a1-dbeb6557f9e5</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Es ist für mich das erste Mal, dass ich bei Hofmanns bestellt habe. Ich fand die Idee, dass man fertiges Essen bestellen und nach Lust und Laune aufwärmen kann, gut. Meine Erfahrungen gelten nur für den vegetarischen Bereich, und da muss ich sagen, dass ich doch ziemlich enttäuscht bin. Abgesehen davon, dass wenig gewürzt wurde (das könnte man ja noch nachholen), gibt es zu den Gerichten oft eine weisse Sauce, die immer gleich schmeckt, und die den wenigen Geschmack des Essens auch noch ertränkt.</t>
+          <t>Soße zu wenig</t>
         </is>
       </c>
       <c r="D116">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E116">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H116">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -4159,11 +4498,14 @@
       <c r="H117">
         <v>1</v>
       </c>
+      <c r="I117">
+        <v>4</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>rev-a1099a78-8fa9-4cb2-8de1-700ade112e9d</t>
+          <t>rev-81bd7c97-4d2e-409b-a981-7ceeaf482e48</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4173,8 +4515,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Alles wirklich perfekt. _x000D_
-Verbesserungsvorschlag: Gerichte mit Alkohol farblich auf der Packung kennzeichnen.</t>
+          <t>Bestelle dort schon seit über einem Jahr. Sehr leckere Speisen, Expresslieferung, umweltfreundliche Verpackung und preislich angemessen.</t>
         </is>
       </c>
       <c r="D118">
@@ -4184,19 +4525,22 @@
         <v>0</v>
       </c>
       <c r="F118">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H118">
         <v>1</v>
+      </c>
+      <c r="I118">
+        <v>4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>rev-401dd728-8418-442f-8dce-2a09fca49c21</t>
+          <t>rev-71d08cea-d7d9-4ab4-90fb-941de1b8df4e</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4206,175 +4550,197 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">⭐⭐⭐⭐⭐_x000D_
+          <t>Schnelle Lieferung, Größe passt wie angegeben, ein toller Schuh. LG</t>
+        </is>
+      </c>
+      <c r="D119">
+        <v>2</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>rev-ab974976-cd1d-4353-abac-13f6e4ce7dff</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Es schmeckt sehr gut 👍 und für jedermann sollte etwas Leckeres dabei sein, zumal es viele Gerichte gibt 😊…</t>
+        </is>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>rev-45abd2e8-5c1d-471a-9aba-c0bd36d6cb59</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Es wurde sehr schnell alles geliefert schön umweltbewusst mit Papier bzw Pappe man konnte danach alles einfach recyceln in die papiertonne die Menüs waren sehr abwechslungsreich und schmecken einfach nur Bombe außerdem machen sie satt und man braucht nicht kochen und man bekommt jeden Tag ein anderes Menü</t>
+        </is>
+      </c>
+      <c r="D121">
+        <v>2</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>2</v>
+      </c>
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="I121">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>rev-8e422716-2b8a-4475-aa60-eefe10140131</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Das Essen ist wie immer gut bis sehr gut, ich hatte schon mehrmals bestellt und war immer zufrieden. Schön und umweltfreundlich fand ich, dass Styropor durch Strohverpackung ersetzt wurde.Nicht so schön fand ich , dass der Paketbote das Paket einfach in das Treppenhaus unseres Mehrfamilienhauses gestellt hat und ich es erst abends gefunden habe. Zum Glück war alles noch gefroren.</t>
+        </is>
+      </c>
+      <c r="D122">
+        <v>2</v>
+      </c>
+      <c r="E122">
+        <v>2</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="G122">
+        <v>2</v>
+      </c>
+      <c r="H122">
+        <v>1</v>
+      </c>
+      <c r="I122">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>rev-23ee968d-c4f1-4b6e-a25d-309a1c1db5e0</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Schnelle Lieferung, innerhalb von 1 Tag. Alles bestens verpackt und noch tiefgefroren. Sehr gute Essensmenge und Geschmack. Würde allerdings bei manchen Essen statt Pommes Bratkartoffeln vorziehen.</t>
+        </is>
+      </c>
+      <c r="D123">
+        <v>2</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123">
+        <v>2</v>
+      </c>
+      <c r="H123">
+        <v>1</v>
+      </c>
+      <c r="I123">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>rev-c0653fba-83b3-40b6-acef-caeb7d4b459c</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die V_x000D_
 _x000D_
-Ich bin absolut begeistert von meiner Erfahrung mit Hoffmanns! Die Lieferung meines gefrorenen Essens war einwandfrei. Das Paket enthielt Trockeneis, das die Ware perfekt unter minus 18 Grad gehalten hat, selbst während eines 14-stündigen Versands. Diese Sorgfalt und Qualität im Service haben mich beeindruckt. Hoffmanns hat einen neuen Stammkunden gewonnen, und ich freue mich darauf, weiterhin von ihnen zu bestellen. Ich würde es jedem empfehlen! Bitte machen Sie darauf aufmerksam, dass sie mit Trockeneis versenden – das ist wirklich ein großer Pluspunkt!_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+Die Verpackung war perfekt,alles kam gut gekühlt an._x000D_
+Die Gerichte sind alle sehr wohlschmeckend._x000D_
+Bestelle gerne wieder._x000D_
+_x000D_
+_x000D_
+_x000D_
 _x000D_
 </t>
         </is>
       </c>
-      <c r="D119">
-        <v>2</v>
-      </c>
-      <c r="E119">
-        <v>0</v>
-      </c>
-      <c r="F119">
-        <v>0</v>
-      </c>
-      <c r="G119">
-        <v>2</v>
-      </c>
-      <c r="H119">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>rev-b25d9078-92cf-4969-b606-409add910fd3</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Speisen sind sehr schmackhaft_x000D_
-Fleisch wunderbar weich</t>
-        </is>
-      </c>
-      <c r="D120">
-        <v>2</v>
-      </c>
-      <c r="E120">
-        <v>0</v>
-      </c>
-      <c r="F120">
-        <v>0</v>
-      </c>
-      <c r="G120">
-        <v>1</v>
-      </c>
-      <c r="H120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>rev-3aadccbe-5d97-447d-9fba-c1fd3a7b5fea</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Bereits 5 Werktage warte ich auf meine (erst-)Bestellung. Hatte aber  leider DHL Express vergeigt. Hofmann hatte hier gleich eine Ersatzlieferung rausgeschickt.</t>
-        </is>
-      </c>
-      <c r="D121">
-        <v>2</v>
-      </c>
-      <c r="E121">
-        <v>1</v>
-      </c>
-      <c r="F121">
-        <v>1</v>
-      </c>
-      <c r="G121">
-        <v>2</v>
-      </c>
-      <c r="H121">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>rev-8e422716-2b8a-4475-aa60-eefe10140131</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Das Essen ist wie immer gut bis sehr gut, ich hatte schon mehrmals bestellt und war immer zufrieden. Schön und umweltfreundlich fand ich, dass Styropor durch Strohverpackung ersetzt wurde.Nicht so schön fand ich , dass der Paketbote das Paket einfach in das Treppenhaus unseres Mehrfamilienhauses gestellt hat und ich es erst abends gefunden habe. Zum Glück war alles noch gefroren.</t>
-        </is>
-      </c>
-      <c r="D122">
-        <v>2</v>
-      </c>
-      <c r="E122">
-        <v>2</v>
-      </c>
-      <c r="F122">
-        <v>1</v>
-      </c>
-      <c r="G122">
-        <v>2</v>
-      </c>
-      <c r="H122">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>rev-5b43ad06-c898-4947-bd25-b02051f3f2bd</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Krankheitsbedingt kann ich nicht kochen,dank Internet kann man „Essen auf Rädern“ eingeben, so bin ich auf diese Firma gestoßen. Das Angebot ist gut und es schmeckt. Bestellung ist unkompliziert, Lieferung schnell. Gut verpackt. Sollte ich wieder in diese Lebenssituation kommen, bestelle ich gerne wieder</t>
-        </is>
-      </c>
-      <c r="D123">
-        <v>2</v>
-      </c>
-      <c r="E123">
-        <v>0</v>
-      </c>
-      <c r="F123">
-        <v>0</v>
-      </c>
-      <c r="G123">
-        <v>2</v>
-      </c>
-      <c r="H123">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>rev-74b6c7cb-3ec7-46e1-b21d-5ee7c3f90c02</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Sehr schnelle Lieferung, alles prima verpackt. Der Fahrer war sehr freundlich und hilfsbereit._x000D_
-Alles bestens, werde wieder bestellen.</t>
-        </is>
-      </c>
       <c r="D124">
         <v>2</v>
       </c>
@@ -4385,10 +4751,13 @@
         <v>0</v>
       </c>
       <c r="G124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H124">
         <v>1</v>
+      </c>
+      <c r="I124">
+        <v>4</v>
       </c>
     </row>
     <row r="125">
@@ -4422,11 +4791,14 @@
       <c r="H125">
         <v>0</v>
       </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>rev-3b98e85f-824f-3cdd-5f43-076a9f295da7</t>
+          <t>rev-0f6c7fa9-fa47-ef61-e445-f5fbe37d5b45</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4436,7 +4808,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Alles ok</t>
+          <t>alles wunderbar wie immer, vielen Dank!</t>
         </is>
       </c>
       <c r="D126">
@@ -4452,39 +4824,45 @@
         <v>0</v>
       </c>
       <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
         <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>rev-d6112bd8-0973-481c-a96a-4ac7fdaac5a8</t>
+          <t>rev-c7abae58-81d1-426a-be22-ccde35aa7209</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Einer von 8 Menü-Kartons/Papschalen war leider halb geöffnet - besser kleben!</t>
+          <t>Sehr Leckeres Essen</t>
         </is>
       </c>
       <c r="D127">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E127">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F127">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G127">
         <v>0</v>
       </c>
       <c r="H127">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -4518,25 +4896,28 @@
       <c r="H128">
         <v>0</v>
       </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>rev-381a9c12-9508-c49c-ce9c-9773ca107a81</t>
+          <t>rev-cbec9e3c-9a8f-7438-ebdd-41d6877756df</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Alles tip top</t>
+          <t>Preis und Leistung ist gut.</t>
         </is>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4549,6 +4930,9 @@
       </c>
       <c r="H129">
         <v>0</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -4582,43 +4966,49 @@
       <c r="H130">
         <v>0</v>
       </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>rev-cb6ea949-159a-4e58-ad92-70aad8eff378</t>
+          <t>rev-59eeb8ef-1e27-43ef-8761-31560fca1944</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Schnelle Lieferung, Top verpackt, super lecker!!</t>
+          <t>Eine gutes Angebotsspektrum, geschmacklich nichts Besonderes aber gute Qualität, Zuberreitung der Speisen funktioniert entsprechend der Anleitung. für mich persönlich sind die Portionen zu klein.</t>
         </is>
       </c>
       <c r="D131">
         <v>2</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131">
         <v>1</v>
+      </c>
+      <c r="I131">
+        <v>5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>rev-0c70468b-e3e6-4af6-bfc7-9be7a2347ab0</t>
+          <t>rev-c2ff0b81-c926-4e98-a5e0-435dfb7de944</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4628,29 +5018,35 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Alle Menüs sind sehr lecker, wie frisch gekocht , ich möchte HOFMANNs unbedingt weiter empfehlen . 2 Tage nach der Bestellung wurden die Menüs geliefert, bisher gab es nur 1x Probleme- das lag aber an DHL und HOFMANNs hat sofort eine neue Lieferung veranlasst. Die Kommunikation mit HOFMANNs ist vorbildlich.</t>
+          <t>Schnelle Lieferung._x000D_
+Die Gerichte schmecken sehr gut._x000D_
+Super die große Auswahl._x000D_
+Gerne wieder.</t>
         </is>
       </c>
       <c r="D132">
         <v>2</v>
       </c>
       <c r="E132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F132">
         <v>0</v>
       </c>
       <c r="G132">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>rev-be2694ef-b199-4a91-aacf-0f0e9a217124</t>
+          <t>rev-eade86cf-1160-47f8-bedb-1a438042cc07</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4660,39 +5056,42 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Eine neue Lieferung von 8 Gerichten in einer Kühlbox ist bei mir eingegangen. Die Qualität der Speisen ist bekanntermaßen hervorragend. Dabei bestellte ich durchweg umfängliche komplette Gerichte ("Sonntagsessen") mit Braten, Soße, Kartoffeln oder Bratkartoffeln oder Bällchen und Gemüse wie Rotkraut oder Bohnen. Diese Rezepte finde ich ausgefeilt und wohlschmeckend, sogar etwas luxuriös. Bratwürste und Nudeln/Spaghetti z. B. sind auch nicht schlecht, doch kann ich so etwas selbst zubereiten und spare den Aufwand eines gekühlten Versands.</t>
+          <t>Alles top. Schnelle Lieferung. Essen gut.</t>
         </is>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
         <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>rev-eb5ccbcb-f533-c032-b02d-547d30004a92</t>
+          <t>rev-3c969829-b988-be3d-907f-770b05e820b0</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Alles gut</t>
+          <t>Alles bestens!</t>
         </is>
       </c>
       <c r="D134">
@@ -4708,13 +5107,16 @@
         <v>0</v>
       </c>
       <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
         <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>rev-6bc087f4-20ee-49a2-bee5-af3d4c2c6934</t>
+          <t>rev-b48b38bb-866b-4fda-a052-131e057c14d7</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4724,15 +5126,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">_x000D_
-Können es nur empfehlen._x000D_
-Schnelle und perfekte Lieferung. _x000D_
-Essen ist sehr gut._x000D_
-</t>
+          <t>Also habe bis jetzt drei Essen ausprobiert und muss sagen alle drei sehr gut👍_x000D_
+Hoffe die anderen fünf sind genauso 😉</t>
         </is>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4744,45 +5143,51 @@
         <v>0</v>
       </c>
       <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
         <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rev-f244b095-17cb-4cf3-9a64-ef3a17814399</t>
+          <t>rev-aefda81b-bbc8-4f85-8912-1bc03dbe7d81</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>32 Gerichte am Fr. den 30.6.23 zum Wunschtermin am Di. den 4.7.23 bestellt. Es erfolgte keine Lieferung. Mehrmalige Anruf- und Email Kontaktversuche beben unbeantwortet. Dann kam am Mi. den 5.7. endlich eine Nachricht, daß am Fr. den 7.7. geliefert werden sollte. Leider Abermals Fehlanzeige. Abgesehen davon, daß wir täglich in Bereitstellung Zuhause sein mußten und zeitlich wegen der zu erwartenden Lieferung gebunden waren, finden wir diese Vorgehendsweise der Firma, in geschmeichelte Aussage, unerhört. Hoffen, daß  die Ware doch noch und vor allen Dingen, was auch nicht immer der Fall war, Tiefgefroren und noch nicht mit aufgelösten Trockeneisbeuteln und mit verbindlicher Vorankündigung, bei uns eintrifft.</t>
+          <t>Da ich schon so einiges getestet habe, kann ich nur sagen(für mich persönlich) ist es bis Jetzt das Beste ! Die Portionen sind ausreichend und geschmacklich(für mich persönlich) sehr wohlschmeckend ! Bin froh dass ich gleich 2 Boxen bestellte. Gerne immer wieder ! Das Preisniveau ist absolut gerechtfertigt, man schmeckt die Qualität! Zu Beginn war ich etwas skeptisch, doch die Menüs haben mich überzeugt!</t>
         </is>
       </c>
       <c r="D136">
         <v>2</v>
       </c>
       <c r="E136">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H136">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>3</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rev-659479cd-dd96-4436-816c-6bf1890ea9df</t>
+          <t>rev-bd42a7a4-cec9-4260-a69c-53dcdbc53601</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4792,11 +5197,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Alles</t>
+          <t>Die Speisen sind durchweg wohlschmeckend und bekömmlich.Was ich besonders zu schätzen weis ist daß mit der Zugabe von Zucker sparsam (normal) umgegangen wird.</t>
         </is>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4805,48 +5210,55 @@
         <v>0</v>
       </c>
       <c r="G137">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H137">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I137">
+        <v>4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>rev-b9d514af-a14f-4004-81f9-6228ebff3ef4</t>
+          <t>rev-7bf04b2c-169a-47ef-8f69-152d8086f5cb</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ich habe Hofmann Menü bereits vor über 20 Jahren kennengelernt. Damals belieferten sie eine große Hamburger Sparkasse. Das Essen war damals bereits lecker und ich freute mich um so mehr, als ich merkte, dass auch nun Privatpersonen online bestellen können. Meine Lieblingsgerichte gibt es zum großen Teil noch immer und ich freue mich darauf, meinen Kindern ein schnelles Mittagessen nach der Schule zubereiten zu können, wenn ich es selber zeitlich nicht schaffen kann. Die Lieferung erfolgte prompt und alle Gerichte waren selbstverständlich noch tiefgefroren.</t>
+          <t xml:space="preserve">Ware bei Lieferung aufgetaut _x000D_
+</t>
         </is>
       </c>
       <c r="D138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F138">
         <v>0</v>
       </c>
       <c r="G138">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H138">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>3</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>rev-ad82a69a-fbc5-450e-a182-f17b534d36c0</t>
+          <t>rev-ef4015d9-fb30-40b4-ace7-00c56e3c04c0</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4856,11 +5268,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Lieferung ging sehr schnell. Essen war für meine Oma. Sie ist total begeistert. Bis jetzt hat ihr alles geschmeckt und sie sagt, es war super gewürzt und man merkt, es ist mit Liebe gemacht. Ich habe lange nach einer Alternative für „Essen auf Rädern“ für meine Oma gesucht und endlich Gerichte gefunden die schmecken. Wir bestellen auf jeden Fall wieder. Einfach nur top.</t>
+          <t>Alles immer super lecker</t>
         </is>
       </c>
       <c r="D139">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4869,81 +5281,90 @@
         <v>0</v>
       </c>
       <c r="G139">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>rev-1f993e75-d560-4770-810f-a488e0c247a0</t>
+          <t>rev-f765b939-d15a-43e7-8679-e67870cf0f67</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Die Gerichte schmecken bisher sehr gut, die Menge ist für mich auch ausreichend. Aber mir gefallen die Zuckerzusätze(Dextrose) nicht bzw. ich vertrage sie nicht. Ich merke das im Bauch. Für andere Leute die damit keine Probleme haben, sind die Gerichte top.</t>
+          <t>Super Produkte.</t>
         </is>
       </c>
       <c r="D140">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E140">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H140">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>rev-55ae7418-39f5-4574-9db6-8475d3b12a8a</t>
+          <t>rev-6b24ca27-0dca-4491-be72-26740706510b</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Am besten gefällt mir, dass man jetzt den Liefertermin wählen kann und nicht rechnen und bangen muss, dass das Paket doch nicht dann kommt, wann man eigentlich wollte. Ist in Single-Haushalten halt komplizierter._x000D_
-Die Portionsgrößen sind super, bitte nicht verkleinern.</t>
+          <t>Bei vielen Gerichten wird mit Kümmel gewürzt, (Sauerkraut und auch im Gulasch) das ist nicht mein Geschmack._x000D_
+Und die Nockerln sind knochenhart, wenn man Sie direkt in die Soße machen würde, könnte man dies verhindern.</t>
         </is>
       </c>
       <c r="D141">
         <v>2</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G141">
         <v>2</v>
       </c>
       <c r="H141">
         <v>1</v>
+      </c>
+      <c r="I141">
+        <v>8</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>rev-00b87fde-7478-4529-b8ab-b50223e57946</t>
+          <t>rev-14ce0140-deb4-4575-a1ca-597f96a9cd58</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4953,11 +5374,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Alles super gelaufen wie immer</t>
+          <t xml:space="preserve">...Die Menüs sind einfach köstlich 😋... Lieferung und Verpackung einwandfrei!... alles in allem eine Eis🥶kalte Sache!😀👍🍀_x000D_
+</t>
         </is>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4970,6 +5392,9 @@
       </c>
       <c r="H142">
         <v>0</v>
+      </c>
+      <c r="I142">
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -4992,7 +5417,7 @@
         <v>2</v>
       </c>
       <c r="E143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -5002,76 +5427,85 @@
       </c>
       <c r="H143">
         <v>1</v>
+      </c>
+      <c r="I143">
+        <v>4</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rev-e0e9a8b2-4034-4bc8-b80e-420eeeb5e326</t>
+          <t>rev-ab938b5e-200c-434d-80e0-ce0cb30e0ebd</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Fleisch teilweise nicht genießbar, Zubereitungszeit dauert zu lange</t>
+          <t>schnelle Lieferung der gekühlten Ware!</t>
         </is>
       </c>
       <c r="D144">
         <v>2</v>
       </c>
       <c r="E144">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144">
         <v>0</v>
       </c>
       <c r="H144">
         <v>1</v>
+      </c>
+      <c r="I144">
+        <v>2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>rev-2e519b78-995b-3ebf-58dc-4bd038ba507c</t>
+          <t>rev-e83ab343-fafd-8c3d-d9a6-6758f6210a7b</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>alles bestens</t>
+          <t>Portionen könnten größer sein.</t>
         </is>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145">
         <v>0</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145">
         <v>0</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I145">
+        <v>2</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>rev-4ea0b203-8f07-318f-5a58-8ee249505ec8</t>
+          <t>rev-e4e21555-dbde-1f27-a79a-24851e33dffa</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5081,11 +5515,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Hat alles sehr gut und schnell geklappt.</t>
+          <t>wie immer: schnelle und korrekte Lieferung, insgesamt empfehlenswert</t>
         </is>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5098,26 +5532,29 @@
       </c>
       <c r="H146">
         <v>0</v>
+      </c>
+      <c r="I146">
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>rev-caab441b-a556-549a-78db-166ef919b639</t>
+          <t>rev-c1c18ce8-437c-de94-5bac-6a4da8bfb719</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Hat alles super geklappt! Geschmacklich wirklich gut!</t>
+          <t>alles in Ordnung</t>
         </is>
       </c>
       <c r="D147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5126,10 +5563,13 @@
         <v>0</v>
       </c>
       <c r="G147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -5152,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="E148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -5161,6 +5601,9 @@
         <v>0</v>
       </c>
       <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
         <v>0</v>
       </c>
     </row>
@@ -5195,75 +5638,85 @@
       <c r="H149">
         <v>0</v>
       </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>rev-a0376b5e-ddf1-41cb-99ce-a6e45e1731ac</t>
+          <t>rev-5f1c9ee9-5a36-4af8-9bd9-81b7dc17d848</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sehr gutes Essen! Uns schmeckt es bestens und der Versand verläuft blitzschnell und reibungslos! Wir haben nichts zu beanstanden und sind froh, solch eine tolle Verköstigung gefunden zu haben. Wir sind treue Stammkunden und können Hofmanns absolut weiterempfehlen!</t>
+          <t>Besser würzen_x000D_
+Gemüse dazu</t>
         </is>
       </c>
       <c r="D150">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E150">
         <v>0</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150">
         <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>rev-17af33ba-3215-4cdc-ad48-52bb2ed31b17</t>
+          <t>rev-a4947044-96ba-4c05-aeb0-4bd92329c3c8</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Das Essen ist super lecker, schmeckt wie aus dem Restaurant und ist eine tolle Zeitersparnis. Wünschenswert wären noch ein paar mehr glutenfreie Gerichte zur Auswahl.</t>
+          <t>Entsprach den Erwartungen...</t>
         </is>
       </c>
       <c r="D151">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E151">
         <v>0</v>
       </c>
       <c r="F151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G151">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H151">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>rev-578b1578-63d3-486d-8a19-3718fc9b7c8f</t>
+          <t>rev-50bdec2e-f1ed-4cef-a8a6-cf844c994e87</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5273,29 +5726,32 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Nach sehr schlechten Erfahrungen bei meiner ersten Bestellung hat es nun bei meiner zweiten Bestellung sehr gut geklappt. Sehr loben muss ich auch den Kundendienst von Hofmanns. Nachdem bei der ersten Lieferung alles aufgetaut ankam, hat man sich sofort entschuldigt und ein Rabattangebot für eine weitere Lieferung angeboten. Auch wurde der Kaufbetrag sofort und unkompliziert zurück erstattet. Das Essen ist sehr schmackhaft und man merkt, dass es wirklich handwerklich hergestellt ist. Die Portionen sind auch ausreichend groß. Achillesferse dieses Konzeptes ist und bleibt das Lieferkonzept. Wenn der Lieferdienstleister gut arbeitet und die Ware innerhalb von 24 Std. den Kunden erreicht, reicht die Kühlkapazität des Trockeneises gerade so aus. Dauert es länger, wird es kritisch.</t>
+          <t>Essen gut, Lieferung  na na</t>
         </is>
       </c>
       <c r="D152">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E152">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G152">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
         <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>rev-1c7d220f-edb1-495e-8890-0b52d1e84986</t>
+          <t>rev-95266688-2a8f-439c-8229-baf3011a54ec</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5305,11 +5761,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>alles perfekt wie immer, besten Dank.</t>
+          <t>Sehr gut gefallen hat uns die Verpackung der Menüschalen mit den Strohmatten.</t>
         </is>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5321,13 +5777,16 @@
         <v>0</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I153">
+        <v>2</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>rev-486dffed-0576-46ea-a2a9-61c4268d6998</t>
+          <t>rev-8a9a69fe-374d-4a9c-a0cc-dd1d3a035d5f</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5337,7 +5796,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Schnelle Lieferung und sehr lecker alles,kann man wirklich weiter empfehlen.</t>
+          <t>Immer schnelle Lieferung,  gut verpackt. Die Produkte sind sehr lecker.</t>
         </is>
       </c>
       <c r="D154">
@@ -5350,27 +5809,29 @@
         <v>0</v>
       </c>
       <c r="G154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H154">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>rev-e2db2b62-d8af-4a12-ae1c-7e05689c5dae</t>
+          <t>rev-e387a48b-5a64-467c-a528-9913b3d68d17</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gleich mit der besten Benotung zu starten, ist nicht mein Ding. Aber meine Bestellungen haben mit sehr gut geschmeckt  _x000D_
-</t>
+          <t>Hat alles gepasst, auch der Wunschtermin.</t>
         </is>
       </c>
       <c r="D155">
@@ -5383,42 +5844,48 @@
         <v>0</v>
       </c>
       <c r="G155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
         <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>rev-35ee6c1b-dec6-42bb-a8b7-156ecf019b33</t>
+          <t>rev-e273c3fa-11f6-4a19-a705-af05539e8981</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Lieferung fast eine Woche. Dies ist etwas sehr lang</t>
+          <t>Die Gerichte sind extrem lecker, vor allem, wenn man nicht die Zeit und Lust hat etwas zu kochen, sind sie sehr praktisch. </t>
         </is>
       </c>
       <c r="D156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F156">
         <v>0</v>
       </c>
       <c r="G156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H156">
         <v>1</v>
+      </c>
+      <c r="I156">
+        <v>4</v>
       </c>
     </row>
     <row r="157">
@@ -5448,51 +5915,57 @@
         <v>1</v>
       </c>
       <c r="F157">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G157">
         <v>1</v>
       </c>
       <c r="H157">
         <v>1</v>
+      </c>
+      <c r="I157">
+        <v>6</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>rev-c1ea4fdf-6cbc-4abb-a84a-9d68acdc6b61</t>
+          <t>rev-c106d14e-06e0-4b71-94cd-3efc5b7a10c1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Einfaches Bestellverfahren, guter Kundeservice, nette Hotline, gute Qualität des Essens</t>
+          <t>Das essen ist an sich echt lecker. Nur habe ich bei einigen speisen mit gemüse mehrfach auf sand gebissen. Das war nicht so witzig. Und sollte bei dem preis auch nicht sein..</t>
         </is>
       </c>
       <c r="D158">
         <v>2</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H158">
         <v>1</v>
+      </c>
+      <c r="I158">
+        <v>7</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rev-1de262f5-b073-4be8-a90e-2a7d7c5885b6</t>
+          <t>rev-5be59673-fd02-4c0a-ab40-b0646e62676b</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5502,11 +5975,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Hatte noch nicht die Zeit alles zu testen.</t>
+          <t>War alles gut verpackt, Ware ist alles in Ordnung.</t>
         </is>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5519,44 +5992,50 @@
       </c>
       <c r="H159">
         <v>0</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rev-e1b14d6d-6fbd-4ab8-97b8-68e0bed76484</t>
+          <t>rev-156baf46-9502-46ef-9989-a6f1981f9793</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Gute Qualität. Bei großer Bestellung könnte man den Rabatt etwas höher machen, z.B. anstatt 10 % bei einem Abo zwischen 15-20 %.</t>
+          <t>schnelle lieferung</t>
         </is>
       </c>
       <c r="D160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E160">
         <v>0</v>
       </c>
       <c r="F160">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160">
         <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rev-aaf56595-ff95-4af7-9d7a-635f2a17aa15</t>
+          <t>rev-37347fa6-0a6f-42ec-823c-cf0990eda00f</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5566,29 +6045,32 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Die Verpackung-nachhaltig,trotzdem alles gefroren angekommen.Die Erklärung zum entsorgen-positiv.</t>
+          <t>Das Essen ist wirklich lecker  Schnelle Lieferung.</t>
         </is>
       </c>
       <c r="D161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F161">
         <v>0</v>
       </c>
       <c r="G161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161">
         <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>rev-610aafd5-de30-4188-b9e2-6d0eee56de44</t>
+          <t>rev-a375fcd3-e9ef-4a02-afc0-25b96189cd48</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5598,7 +6080,8 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Vielleicht noch deutlicher und farbiger für alte Menschen die Erkennung ob eine Lasche vorher abgetrennt werden muss oder nicht. Wenn nichts abgetrennt werden muss, dann sollte deutlich drauf stehen: dieses Gericht ungeöffnet in den Backofen.</t>
+          <t>Bisher war ich mit den gelieferten, verschiedenen Essen immer total zufrieden. Kein "Misch-Masch" sondern handwerklich gute Restaurant-Qualität. Aber auch_x000D_
+der Service hat meine Erwartungen voll und ganz erfüllt !</t>
         </is>
       </c>
       <c r="D162">
@@ -5608,19 +6091,22 @@
         <v>0</v>
       </c>
       <c r="F162">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G162">
         <v>2</v>
       </c>
       <c r="H162">
         <v>1</v>
+      </c>
+      <c r="I162">
+        <v>4</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>rev-b46c26c4-0702-4568-b606-b95290b26eb5</t>
+          <t>rev-860bee67-19d0-463e-9502-15859f4e8680</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5630,14 +6116,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Besser machen geht nicht._x000D_
-Besser schmecken schon gar nicht._x000D_
-Also 5 Sterne._x000D_
-</t>
+          <t>Essen ist gut abgeschmeckt</t>
         </is>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -5650,12 +6133,15 @@
       </c>
       <c r="H163">
         <v>0</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>rev-c1de7443-a3f9-4d53-800b-dffab2190211</t>
+          <t>rev-8e5e37b8-3956-41da-84ab-41c7c0f637ca</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5665,11 +6151,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Sehr schnelle Lieferung</t>
+          <t>Bestellung, Lieferung und Kommunikation klappt bestens. Manche Gerichte sind "Geschmackssache" - aber von guter Qualität. Sehr große Auswahl.</t>
         </is>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -5678,16 +6164,19 @@
         <v>0</v>
       </c>
       <c r="G164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I164">
+        <v>3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>rev-93745a60-ee29-4614-ab39-deefc59f6074</t>
+          <t>rev-3dafa4c6-c0cd-63d2-d671-300127ab2625</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5697,32 +6186,32 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>:_x000D_
-"Ich bin mit den Gerichten bisher zufrieden gewesen, bis auf die Tatsache, dass einige Gerichte nach vorschriftsmäßiger Zubereitung aus dem Ofen nicht ganz aufgetaut waren. Was ich feststellen konnte, ist, dass die Nudelgerichte aus der Pasta-Box alle perfekt aufgewärmt waren. Das liegt wohl daran, dass Nudeln dünner sind. Insgesamt schmeckten alle Gerichte sehr gut, aber die Pasta-Gerichte sind das Highlight."_x000D_
-_x000D_
- * "</t>
+          <t>Super schnell und ordentlich verpackt und schmeckt wie bei Müttern echt top</t>
         </is>
       </c>
       <c r="D165">
         <v>2</v>
       </c>
       <c r="E165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F165">
         <v>0</v>
       </c>
       <c r="G165">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>2</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>rev-6554a50f-c023-3040-f136-3d97cf9409ae</t>
+          <t>rev-8442ccda-76e2-35f1-3c6c-88641dc9bb2d</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5732,7 +6221,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>wie immer: schnelle und lorrekte Lieferung</t>
+          <t>Sehr appetitlich, geschmacklich sehr gut. Ich werde auf jedem Fall wieder bestellt.</t>
         </is>
       </c>
       <c r="D166">
@@ -5748,45 +6237,51 @@
         <v>0</v>
       </c>
       <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
         <v>1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>rev-51cf265b-501d-497d-9b4e-87fa57422520</t>
+          <t>rev-00644528-7302-496c-bd70-4929857b5e56</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Alles passt bisher und schmeckt hervorragend......Lieferung perfekt ökologisch verpackt......wir sind begeistert  !!! Kann man sehr empfehlen !!!</t>
+          <t>Schnelle Lieferung. Wäre ist sicher verpackt ( Trockeneis ). Gerichte sind überwiegend sehr lecker. Ein Stern Abzug wegen Wechsel von DHL zu DPD. Ich fand DHL besser.</t>
         </is>
       </c>
       <c r="D167">
         <v>2</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H167">
         <v>1</v>
+      </c>
+      <c r="I167">
+        <v>6</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>rev-4d08a40b-30ca-46e0-a93a-a1185ac636f3</t>
+          <t>rev-b7d9eb6c-1b16-4a67-b536-65e5bae0eafb</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5796,11 +6291,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Alles gut</t>
+          <t>Sehr lecker und schnell geliefert.</t>
         </is>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5813,26 +6308,29 @@
       </c>
       <c r="H168">
         <v>0</v>
+      </c>
+      <c r="I168">
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>rev-7042fbb5-65f5-4c79-acb9-f2a7ece2a4b3</t>
+          <t>rev-1318f8b6-91a7-4fa6-83ff-1deffec9ae78</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Schnelle Lieferung wenig Müll Essen ist lecker nicht zerkocht und einfach in der Zubereitung</t>
+          <t>Das Essen ist sehr gut der Kundenservice Miserabel</t>
         </is>
       </c>
       <c r="D169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5841,16 +6339,19 @@
         <v>0</v>
       </c>
       <c r="G169">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
         <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>rev-6d299557-5e0c-442a-be86-ebbd2a1443ac</t>
+          <t>rev-3ccbe7d0-488b-4f51-bae1-a4b190590c39</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5860,31 +6361,32 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Hochwertige Qualität und ausgezeichneter Geschmack erleichtern mir meinen eigenen Alltag für eine weitere selbstbestimmte Lebensführung trotz Pflegegrad und Schwerbehinderung._x000D_
-_x000D_
-Einzig die Zustellung mit DHL-Express ist weniger erfreulich, weil der Fahrer nicht an die geschäftlichen Bestimmungen der DHL hält und alle Nachfragen leider nicht zu einem Erfolg führt. Doch ist dies ein Problem der DHL und weniger der Firma Hofmann zuzuschreiben.</t>
+          <t>Ich finde das Essen sehr lecker. Man kann sich ja das aussuchen was man gerne mag. Es ist schnell erwärmt. Kann es zum ausprobieren weiterempfehlen.</t>
         </is>
       </c>
       <c r="D170">
         <v>2</v>
       </c>
       <c r="E170">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F170">
         <v>1</v>
       </c>
       <c r="G170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H170">
         <v>1</v>
+      </c>
+      <c r="I170">
+        <v>4</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>rev-9141477f-9abb-4610-baad-3c0a901e1729</t>
+          <t>rev-65a61710-ef91-4225-a1f3-8ac9e9efa4bb</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5894,29 +6396,32 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bis jetzt alles was ich habe probiert gut geschmeckt auser bei einem menu gekochte kartoffeln paar stuck war nicht so gut,aber bei kartoffeln kann so vorkommen.Sonst alles super.Danke</t>
+          <t>Das Essen ist einfach zu lecker für den Preis kann man für eine Einzelperson nicht kochen.</t>
         </is>
       </c>
       <c r="D171">
         <v>1</v>
       </c>
       <c r="E171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F171">
         <v>0</v>
       </c>
       <c r="G171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
         <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>rev-ab667950-7ae5-4b4e-8702-fb3f7bbc7a6d</t>
+          <t>rev-89bc0b9b-bb53-40e2-8bbe-4f288f3de0c0</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5926,11 +6431,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bin rundum zufrieden mit der Lieferung</t>
+          <t>Die Verpackung ist genial sowohl vom Paket, damit der Inhalt gekühlt ankommt,  als auch von den Gerichten, die statt in Plastikschalen in Pappe kommen.  Keine Splitter mehr vom Transport. Schmeckt sehr lecker.</t>
         </is>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5939,16 +6444,19 @@
         <v>0</v>
       </c>
       <c r="G172">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H172">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I172">
+        <v>4</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>rev-dac624c5-38fc-4c6b-be2f-419f6db8279d</t>
+          <t>rev-e18a003f-3870-459a-a598-ee434a950e6d</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5958,7 +6466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Rasche Lieferung. Vielleicht noch mehr Angebote - Piccolino, dann kleinere Portionen evtl. auch etwas kostengünstiger, für Senioren. Ansonsten passt soweit alles.</t>
+          <t>Esse sogar Essen die ich normalerweise überhaupt nicht mag. Warum auch immer, wir haben seitdem wir bei Hofmans bestellen, ging der Mülleimer leer aus. Bei Gloria landete das meiste Essen im Müll. Weiter so. Danke 😅.</t>
         </is>
       </c>
       <c r="D173">
@@ -5968,19 +6476,22 @@
         <v>0</v>
       </c>
       <c r="F173">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G173">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H173">
         <v>1</v>
+      </c>
+      <c r="I173">
+        <v>4</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>rev-efae0ce8-9190-410d-867c-c73c5ccbf703</t>
+          <t>rev-c04a8b56-31d7-42d1-a5f1-833bc53e4180</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5990,29 +6501,32 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Zwei Packungen nicht sauber verschweißt und am Rand offen. Wurde sofort erstattet. Somit alles gut.</t>
+          <t>Sehr zufrieden</t>
         </is>
       </c>
       <c r="D174">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E174">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F174">
         <v>0</v>
       </c>
       <c r="G174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H174">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>rev-34a36c20-6d27-4885-9d97-d08b07f2bca2</t>
+          <t>rev-ea176b3d-e31b-4c7a-8ebc-d19c1867b394</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6022,14 +6536,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>alles super</t>
+          <t>Noch nix bekommen trotz Bestellung letzten Jahres</t>
         </is>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -6038,48 +6552,51 @@
         <v>0</v>
       </c>
       <c r="H175">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I175">
+        <v>4</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>rev-0ab1b8ec-b4da-441e-9a45-3409f8c155dc</t>
+          <t>rev-8a7454fc-4c30-4c40-98e2-f19706432991</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Qualität und Geschmack gut bis sehr gut. _x000D_
-Versand top: Sonntagabends bestellt, Mittwochmittags geliefert. _x000D_
-Ware ist gut gekühlt verpackt - auch bei diesen sommerlich heissen Temperaturen. _x000D_
-Bisher alles tipptopp.</t>
+          <t>Bohnen leider immer noch fast roh, mehrere Menüschalen offen und bereits angetaut geliefert, Trockeneis bereits verdampft, Außenkarton mehrfach beschädigt und eingerissen. Kein sorgfältiger Umgang seitens DPD mit Essen. Karton wird während des Transports wohl dauernd rumgeschmissen. Schade, war vorher besser!</t>
         </is>
       </c>
       <c r="D176">
         <v>2</v>
       </c>
       <c r="E176">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F176">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G176">
         <v>2</v>
       </c>
       <c r="H176">
         <v>1</v>
+      </c>
+      <c r="I176">
+        <v>8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>rev-069a2a17-2cdc-40d5-9a6b-008a703d6adf</t>
+          <t>rev-8f9bcf2a-af40-4ea8-b5e2-b61bdbbc1877</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6089,29 +6606,32 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Jedes Essen war bis jetzt gut und ausreichend. Schnelle Lieferung, nur sehr viel Verpackung.</t>
+          <t>Super schnell geliefert. Tolles Essen.</t>
         </is>
       </c>
       <c r="D177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177">
         <v>0</v>
       </c>
       <c r="F177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H177">
+        <v>0</v>
+      </c>
+      <c r="I177">
         <v>1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>rev-9726acad-184a-4b93-9042-1f4533358a57</t>
+          <t>rev-a5635aad-6747-4e0d-8c58-5786085e2728</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6121,11 +6641,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Der Shop bietet eine gute Auswahl an Produkten. Lieferung ist immer pünktlich. Ich bin sehr zufrieden!</t>
+          <t>Sehr kompetent. Sehr leckeres Essen</t>
         </is>
       </c>
       <c r="D178">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -6134,16 +6654,19 @@
         <v>0</v>
       </c>
       <c r="G178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H178">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>rev-1cbfe308-1f0d-4f9d-96d7-03d9258f9127</t>
+          <t>rev-f2cf6d60-fd9a-435e-b8f1-d519064f1e3c</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6153,11 +6676,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Sehr zuverlässig und Qualität sehr gut!</t>
+          <t>Super Qualität,  fairer Preis, schnelle Lieferung</t>
         </is>
       </c>
       <c r="D179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -6169,13 +6692,16 @@
         <v>0</v>
       </c>
       <c r="H179">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I179">
+        <v>2</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>rev-88b75173-aca0-4634-b0bd-7d8eb6e2a6e7</t>
+          <t>rev-4125d113-3692-4174-82a2-68cc48cd4015</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6185,29 +6711,32 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Leckeres Essen, schnell geliefert und sehr nachhaltig verpackt. Immer wieder gerne 😊</t>
+          <t>Alles das essen ist Top nur mit der Beschreibung der Dauer des zubereiten da weis man nicht was man machen soll. Auf den Speisen steht 140 Grad auf dem Zettel steht 150 grad und dann noch mal plus 10 grad mehr und 15 Minuten länger. Was soll ich jetzt nehmen. Für einen jungen Menschen ist das verständlich aber für ältere Menschen die Wissen bestimmt nicht was sie machen sollen. Und ich wusste es auch nicht und ich bin erst 40 jahre.</t>
         </is>
       </c>
       <c r="D180">
         <v>2</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F180">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G180">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H180">
         <v>1</v>
+      </c>
+      <c r="I180">
+        <v>8</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>rev-3840ad46-f727-4041-9325-524cebc58a17</t>
+          <t>rev-0b0e4278-f418-4f13-8aa2-34ee30996ec5</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6217,7 +6746,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Weiter so! Danke</t>
+          <t>Alles Bestens wie immer</t>
         </is>
       </c>
       <c r="D181">
@@ -6233,13 +6762,16 @@
         <v>0</v>
       </c>
       <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
         <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>rev-2485c9d1-beaf-4a49-a933-13a25539f910</t>
+          <t>rev-ef2a0b34-9ad7-42f2-b5c6-d722579ef242</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6248,260 +6780,286 @@
         </is>
       </c>
       <c r="C182" t="inlineStr">
-        <is>
-          <t>Leckeres Essen, viel Abwechslung, Top Lieferung und ein klasse Kundendienst. 👍</t>
-        </is>
-      </c>
-      <c r="D182">
-        <v>2</v>
-      </c>
-      <c r="E182">
-        <v>0</v>
-      </c>
-      <c r="F182">
-        <v>0</v>
-      </c>
-      <c r="G182">
-        <v>1</v>
-      </c>
-      <c r="H182">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>rev-bfd830f2-c8c5-439d-b9be-ae3291afdd1f</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Immer wieder gute Gerichte. _x000D_
-</t>
-        </is>
-      </c>
-      <c r="D183">
-        <v>0</v>
-      </c>
-      <c r="E183">
-        <v>0</v>
-      </c>
-      <c r="F183">
-        <v>0</v>
-      </c>
-      <c r="G183">
-        <v>0</v>
-      </c>
-      <c r="H183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>rev-f915a470-ef02-46ff-b4d3-1c5c8aad71d1</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Mit DHL alles top</t>
-        </is>
-      </c>
-      <c r="D184">
-        <v>0</v>
-      </c>
-      <c r="E184">
-        <v>0</v>
-      </c>
-      <c r="F184">
-        <v>0</v>
-      </c>
-      <c r="G184">
-        <v>0</v>
-      </c>
-      <c r="H184">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>rev-9d29ba77-afb0-47a6-8655-6560cf497d04</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Bin zufrieden, jedenfalls besser als Essen im Krankenhaus. _x000D_
-Da ich momentan aus gesundheitlichen Gründen nicht selbst am Herd stehen kann, ist das eine große Erleichterung für mich.</t>
-        </is>
-      </c>
-      <c r="D185">
-        <v>1</v>
-      </c>
-      <c r="E185">
-        <v>0</v>
-      </c>
-      <c r="F185">
-        <v>0</v>
-      </c>
-      <c r="G185">
-        <v>2</v>
-      </c>
-      <c r="H185">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>rev-a097f84b-c83c-4b12-bc07-3baa8f33c3fc</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Das es immer pünktlich geliefert wird und es hervorragend schmeckt und das der Preis stimmt.</t>
-        </is>
-      </c>
-      <c r="D186">
-        <v>2</v>
-      </c>
-      <c r="E186">
-        <v>0</v>
-      </c>
-      <c r="F186">
-        <v>0</v>
-      </c>
-      <c r="G186">
-        <v>1</v>
-      </c>
-      <c r="H186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>rev-c9f75597-4dbf-484f-96a2-645073ac059b</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>alles perfekt wie immer.</t>
-        </is>
-      </c>
-      <c r="D187">
-        <v>0</v>
-      </c>
-      <c r="E187">
-        <v>0</v>
-      </c>
-      <c r="F187">
-        <v>0</v>
-      </c>
-      <c r="G187">
-        <v>0</v>
-      </c>
-      <c r="H187">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>rev-7cd51fdb-191c-4086-b94f-0f928895988f</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Schmeckt einfach _x000D_
-_x000D_
-</t>
-        </is>
-      </c>
-      <c r="D188">
-        <v>0</v>
-      </c>
-      <c r="E188">
-        <v>0</v>
-      </c>
-      <c r="F188">
-        <v>0</v>
-      </c>
-      <c r="G188">
-        <v>0</v>
-      </c>
-      <c r="H188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>rev-ef2a0b34-9ad7-42f2-b5c6-d722579ef242</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
         <is>
           <t>Guter und schneller Service. _x000D_
 Bei ( berechtigten ) Reklamationen schnelle und unkomplizierte Bearbeitung. _x000D_
 Das Essen ist in Ordnung, hat aber gegenüber der letzten Jahre etwas an Qualität eingebüßt.</t>
         </is>
       </c>
+      <c r="D182">
+        <v>2</v>
+      </c>
+      <c r="E182">
+        <v>1</v>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182">
+        <v>1</v>
+      </c>
+      <c r="H182">
+        <v>1</v>
+      </c>
+      <c r="I182">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>rev-bfd830f2-c8c5-439d-b9be-ae3291afdd1f</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Immer wieder gute Gerichte. _x000D_
+</t>
+        </is>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="E183">
+        <v>0</v>
+      </c>
+      <c r="F183">
+        <v>0</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>rev-f915a470-ef02-46ff-b4d3-1c5c8aad71d1</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Mit DHL alles top</t>
+        </is>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>rev-9d29ba77-afb0-47a6-8655-6560cf497d04</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Bin zufrieden, jedenfalls besser als Essen im Krankenhaus. _x000D_
+Da ich momentan aus gesundheitlichen Gründen nicht selbst am Herd stehen kann, ist das eine große Erleichterung für mich.</t>
+        </is>
+      </c>
+      <c r="D185">
+        <v>1</v>
+      </c>
+      <c r="E185">
+        <v>0</v>
+      </c>
+      <c r="F185">
+        <v>0</v>
+      </c>
+      <c r="G185">
+        <v>2</v>
+      </c>
+      <c r="H185">
+        <v>1</v>
+      </c>
+      <c r="I185">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>rev-0b4d3b7a-edb0-4a87-9fce-19dd116ae9ff</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>👍 😃</t>
+        </is>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="E186">
+        <v>0</v>
+      </c>
+      <c r="F186">
+        <v>0</v>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>rev-f9fbcda0-269d-4bc3-a9d3-29b1535f5787</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Habe bisher nur 1 Gericht gegessen und kann sagen es schmeckt sehr lecker._x000D_
+_x000D_
+Leider ist das mit dem Versand etwas schwieriger.Erst wollte Dhl einen Tag zuvor alles bringen.Dann sollte das Essen zwischen 12-16uhr kommen.Kam aber schon gegen 10:30Uhr._x000D_
+Doch das Trockeneis hat alles gerettet._x000D_
+</t>
+        </is>
+      </c>
+      <c r="D187">
+        <v>2</v>
+      </c>
+      <c r="E187">
+        <v>2</v>
+      </c>
+      <c r="F187">
+        <v>1</v>
+      </c>
+      <c r="G187">
+        <v>2</v>
+      </c>
+      <c r="H187">
+        <v>1</v>
+      </c>
+      <c r="I187">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>rev-1e70e6b5-840f-480e-b353-d6535ed8647f</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Das Gulasch ist sehr zäh. Die Spinatknödel hatten einige sehr trockene Stücke, es ist für mich eher unglaubwürdig, dass sie frisch gekocht und eingefroren waren, eher wie trockene Kartoffelklöße... Letztlich hatte ich Atemprobleme wie bei manchen Fertiggerichten mit Geschmacksverstärkern. Bin ziemlich enttäuscht.</t>
+        </is>
+      </c>
+      <c r="D188">
+        <v>2</v>
+      </c>
+      <c r="E188">
+        <v>2</v>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
+      <c r="G188">
+        <v>2</v>
+      </c>
+      <c r="H188">
+        <v>1</v>
+      </c>
+      <c r="I188">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>rev-29a05558-7073-4582-92c0-6525faca85f6</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Ich finde die Verpackung sehr umweltfreundlich.  ABER 3 essensverpackungen waren leider nicht mehr verschlossen.  Schade.</t>
+        </is>
+      </c>
       <c r="D189">
         <v>2</v>
       </c>
       <c r="E189">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G189">
         <v>1</v>
       </c>
       <c r="H189">
         <v>1</v>
+      </c>
+      <c r="I189">
+        <v>6</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>rev-f6976474-71f5-4daf-ab7e-f77c35bb30a0</t>
+          <t>rev-ebe9a7a2-6fcd-4ec9-a5f3-9783b5ad5fe6</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6511,29 +7069,34 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Hofmann hat alles perfekt gemacht, wie immer. DHL hat letztendlich nur Ärger ausgelöst: die Lieferung kam 4 Std früher als per Mail mitgeteilt, da keiner da war, einfach beim Nachbar abgegeben, kein Hinweis für mich im Briefkasten, nur eine Mail „zugestellt „. Dann musste ich über etliche Bestätigungen u Wartezeiten am Telefon erfahren, welcher Nachbar meine Lieferung überhaupt hat. Ganz schlechter Partner von Hofmann</t>
+          <t>Alles Bestens._x000D_
+Kaufe immer wieder._x000D_
+    Danke.</t>
         </is>
       </c>
       <c r="D190">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E190">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G190">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H190">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>rev-7aaf3b1d-9588-4b12-addb-32061e4b4e96</t>
+          <t>rev-f7cb83fa-d49e-4df9-a335-ffcc9f8a41bb</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6543,11 +7106,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Sehr leckeres Essen, Qualität ist sehr gut für ein TK Essen.</t>
+          <t>Lecker Essen!</t>
         </is>
       </c>
       <c r="D191">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -6556,16 +7119,19 @@
         <v>0</v>
       </c>
       <c r="G191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H191">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>rev-f9e7d113-2bae-b798-e10b-7c22c8ea67a3</t>
+          <t>rev-3e8ebea6-a57a-b754-4417-bf136800e134</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6575,61 +7141,68 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Die machen alle einen super Job das Essen ist super ich persönlich finde die Menge halt ein bisschen zu wenig</t>
+          <t>Alles i.O.</t>
         </is>
       </c>
       <c r="D192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192">
         <v>0</v>
       </c>
       <c r="F192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H192">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>rev-3ed726a3-b3d5-4b57-b9f1-b3df3e0f8b29</t>
+          <t>rev-8d543a75-fc67-4a17-9f95-4537af7f04d4</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Alle Gerichte, die ich bisher probiert habe schmecken hervorragend und dind einfach zuzubereiten.  Manche Gerichte kann ich sogar auf 2 Mahlzeiten aufteilen, weil es so viel ist.</t>
+          <t>Die Menu's an sich kannte ich schon seitens meiner Arbeitstelle,die uns eine Auswahl an Menu's anbot.Und die Qualität ist vorhanden,kein Zweifel daran._x000D_
+Was mich persöhnlich stört,ist die Tatsache,dass ich die,im Karton mit verpackten Isoliermatten aus Stroh,NICHT bei uns in der BIO-Tonne entsorgen kann,warum auch immer?ich bin da überfragt,bekam aber diese Antwort,NEIN,von der A.R.T.Also,in die Restmüll-Tonne,was ich schade finde.Ich kann verstehen,das HOFMANN's diese Strohmatten nicht zurück nimmt,und wiederverwertet(aus hygienischen und finanziellen Gründen?)was aber eine Lösung wäre?</t>
         </is>
       </c>
       <c r="D193">
         <v>2</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193">
         <v>2</v>
       </c>
       <c r="H193">
         <v>1</v>
+      </c>
+      <c r="I193">
+        <v>7</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>rev-e18a003f-3870-459a-a598-ee434a950e6d</t>
+          <t>rev-4126aa70-7b5f-433c-bf51-b3b9f87b05ca</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6639,11 +7212,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Esse sogar Essen die ich normalerweise überhaupt nicht mag. Warum auch immer, wir haben seitdem wir bei Hofmans bestellen, ging der Mülleimer leer aus. Bei Gloria landete das meiste Essen im Müll. Weiter so. Danke 😅.</t>
+          <t>Schnelle Lieferung</t>
         </is>
       </c>
       <c r="D194">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -6652,48 +7225,63 @@
         <v>0</v>
       </c>
       <c r="G194">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194">
         <v>1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>rev-e16d531b-9c07-4ed5-ae97-34c20b560a6a</t>
+          <t>rev-fbef36a9-d8d0-4b97-aa89-c198d3d091dd</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Keine Ware erhalten-</t>
+          <t>Alle ca. 30 verschiedenen Gerichte die ich bisher gegessen habe waren sehr lecker, und von der Portion her gut ausreichend._x000D_
+Bei einigen Gerichten würde ich mir allerdings wünschen wenn etwas mehr Soße drauf wär._x000D_
+Ich würde mich auch sehr über ein Gericht mit Blumenkohl freuen, zb. einen Kartoffel, Blumenkohl Auflauf mit Hähnchenbrust._x000D_
+_x000D_
+Was auch sehr verbesserungswürdig wär, ist die Verpackung und Anlieferung._x000D_
+Die Sache selbst funktioniert zwar sehr gut und die Ware bleibt noch lange nach der Lieferung gefroren, so das noch alles gefroren ist wenn man erst später am Tag nach hause kommt._x000D_
+Aber es kommt immer eine sehr große Menge an Verpackungsmaterial zusammen welches man entsorgen muß._x000D_
+Die Entsorgung klappt zwar Problemlos, denn noch ist es eine große Verschwendung an Material und erzeugt unnötige Kosten die man anderweitig nutzen könnte. _x000D_
+Da würde ich mir feste wieder verwendbare Kühlboxen aus Kunststoff wünschen, die dann im Rahmen eines Pfandsystem für Stammkunden und Folgebesteller auch wieder zurück gegeben werden können, bzw. bei einer neuen Lieferung ausgetauscht werden können._x000D_
+Damit ein Austausch dieser Kühlboxen überhaupt möglich ist, wär auch einen Hauseigener Lieferdienst vom Vorteil, bei dem man ein genaueres Zustellfenster von ca. 2 Std. vereinbaren kann, und per GPS verfolgen kann. Ähnlich wie zb. beim Rewe Lieferdienst.</t>
         </is>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E195">
         <v>2</v>
       </c>
       <c r="F195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H195">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I195">
+        <v>8</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>rev-0fb90910-dba0-4095-b4cd-b77b0e252668</t>
+          <t>rev-e747c759-0318-47ff-be9a-1f2fe890ccd6</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6703,7 +7291,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Prompte lieferung</t>
+          <t>Schmeckt wie hausgemacht in bis jetzt alles super</t>
         </is>
       </c>
       <c r="D196">
@@ -6720,6 +7308,9 @@
       </c>
       <c r="H196">
         <v>0</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -6747,13 +7338,16 @@
         <v>2</v>
       </c>
       <c r="F197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G197">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H197">
         <v>1</v>
+      </c>
+      <c r="I197">
+        <v>8</v>
       </c>
     </row>
     <row r="198">
@@ -6782,26 +7376,30 @@
         <v>0</v>
       </c>
       <c r="G198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
         <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>rev-1773a3eb-e026-4b3a-bab7-babb05b2fa1e</t>
+          <t>rev-aad82c92-f615-4c8e-b781-6c3613c5cc1b</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Einfache Bedienbarkeit, sehr große Auswahl,  schnelle Lieferung und sehr gute Qualität.</t>
+          <t>Die letzte Lieferung hat anstandslos geklappt. Grundsätzlich ist die Servicehotline auch immer sehr bemüht, alle Probleme wirklich schnell und zuverlässig zu lösen. _x000D_
+Ich finde das Essen wirklich gut, wenn auch es inzwischen doch ziemlich teuer geworden ist und die Auswahl -wenn man es regelmäßig nutzt- dann irgendwann doch immer das selbe ist.</t>
         </is>
       </c>
       <c r="D199">
@@ -6818,12 +7416,15 @@
       </c>
       <c r="H199">
         <v>1</v>
+      </c>
+      <c r="I199">
+        <v>3</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>rev-bcfd909e-e187-43f2-9888-760d6311a666</t>
+          <t>rev-12a512ee-cecc-497d-8de1-fff0861fe1e0</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6833,11 +7434,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Das Essen ist sehr lecker 😋 und vor allem  man das frisch gekocht wird. Das Essen kann man sehr gut genießen.</t>
+          <t>Also ich muss Ihnen sagen einfach lecker lecker lecker und ist sehr zu empfehlen._x000D_
+Mit freundlichen Grüßen, Andreas Irmscher</t>
         </is>
       </c>
       <c r="D200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -6846,16 +7448,19 @@
         <v>0</v>
       </c>
       <c r="G200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H200">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>rev-a00388e4-af61-4b19-b6ff-557b421e5042</t>
+          <t>rev-5717c363-ea35-4c5b-af8c-5ad0d5cf48a7</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6865,18 +7470,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Top, sehr zufrieden!_x000D_
-_x000D_
-Eine kleine Anregung zur Verpackung, es könnten z.B. Perforationen entlang der Kanten des Kartons eingearbeitet werden die dass zerkleinern der Verpackung und die Entsorgung doch enorm vereinfachen würden.(Gesehen bei Amazon Verpackungen). _x000D_
-_x000D_
-Leider habe ich noch keine Möglichkeit für das problemlose Entsorgen des, eigentlich perfekten nachhaltigen Isoliermaterials/Heu gefunden. Für mich als Schwerbehinderten ein echtes Problem.</t>
+          <t xml:space="preserve">Es ist die ideale Idee wenn man Single ist und ohne großen Aufwand ein leckeres Essen genießen möchte. Der einzige Kritikpunkt - das habe ich Ihrem Kundenservice mitgeteilt   dass der Expressversand Schwachstellen aufweist. Es ist kontraproduktiv wenn der Auslieferer die Bestellung vor die Haustür stellt - bei hohen Aussntemperaturen _x000D_
+Zwar klingelt - aber nicht wartet  ob der Empfänger auch die Lieferung entgegen nehmen kann ._x000D_
+Mit freundlichem Gruß Irmtraud Dippel _x000D_
+</t>
         </is>
       </c>
       <c r="D201">
         <v>2</v>
       </c>
       <c r="E201">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F201">
         <v>2</v>
@@ -6886,6 +7490,9 @@
       </c>
       <c r="H201">
         <v>1</v>
+      </c>
+      <c r="I201">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
